--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_costs_by_tretspef-Users_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_costs_by_tretspef-Users_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -398,19 +398,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>346287.5</v>
+        <v>350931.38</v>
       </c>
       <c r="C2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D2">
-        <v>321.36</v>
+        <v>325.67</v>
       </c>
       <c r="E2">
-        <v>180.08</v>
+        <v>182.49</v>
       </c>
       <c r="F2">
-        <v>4862.07</v>
+        <v>4927.27</v>
       </c>
       <c r="G2">
         <v>1062</v>
@@ -423,19 +423,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>357036.97</v>
+        <v>360342.68</v>
       </c>
       <c r="C3">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D3">
-        <v>334.06</v>
+        <v>337.15</v>
       </c>
       <c r="E3">
-        <v>150.77</v>
+        <v>152.16</v>
       </c>
       <c r="F3">
-        <v>4475.13</v>
+        <v>4516.79</v>
       </c>
       <c r="G3">
         <v>1043</v>
@@ -444,176 +444,176 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colorectal Surgery Service</t>
+          <t>Transplant Surgery Service</t>
         </is>
       </c>
       <c r="B4">
-        <v>121465.09</v>
+        <v>14136.8</v>
       </c>
       <c r="C4">
-        <v>223</v>
+        <v>1178</v>
       </c>
       <c r="D4">
-        <v>200.53</v>
+        <v>1124.11</v>
       </c>
       <c r="E4">
-        <v>146.87</v>
+        <v>344.8</v>
       </c>
       <c r="F4">
-        <v>2643.74</v>
+        <v>3103.2</v>
       </c>
       <c r="G4">
-        <v>545</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hepatobiliary and Pancreatic Surgery Service</t>
+          <t>Colorectal Surgery Service</t>
         </is>
       </c>
       <c r="B5">
-        <v>14879.43</v>
+        <v>123061.96</v>
       </c>
       <c r="C5">
-        <v>480</v>
+        <v>226</v>
       </c>
       <c r="D5">
-        <v>344.5</v>
+        <v>203.17</v>
       </c>
       <c r="E5">
-        <v>232.49</v>
+        <v>148.81</v>
       </c>
       <c r="F5">
-        <v>1394.95</v>
+        <v>2678.49</v>
       </c>
       <c r="G5">
-        <v>31</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Upper Gastrointenstinal Surgery Service</t>
+          <t>Hepatobiliary and Pancreatic Surgery Service</t>
         </is>
       </c>
       <c r="B6">
-        <v>25946.11</v>
+        <v>15236.42</v>
       </c>
       <c r="C6">
-        <v>292</v>
+        <v>491</v>
       </c>
       <c r="D6">
-        <v>205.38</v>
+        <v>352.77</v>
       </c>
       <c r="E6">
-        <v>184.01</v>
+        <v>238.07</v>
       </c>
       <c r="F6">
-        <v>1472.12</v>
+        <v>1428.41</v>
       </c>
       <c r="G6">
-        <v>89</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Vascular Surgery Service</t>
+          <t>Upper Gastrointenstinal Surgery Service</t>
         </is>
       </c>
       <c r="B7">
-        <v>124647.52</v>
+        <v>26164.03</v>
       </c>
       <c r="C7">
-        <v>362</v>
+        <v>294</v>
       </c>
       <c r="D7">
-        <v>305.75</v>
+        <v>207.1</v>
       </c>
       <c r="E7">
-        <v>196.6</v>
+        <v>185.56</v>
       </c>
       <c r="F7">
-        <v>2359.26</v>
+        <v>1484.48</v>
       </c>
       <c r="G7">
-        <v>344</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Spinal Surgery Service</t>
+          <t>Vascular Surgery Service</t>
         </is>
       </c>
       <c r="B8">
-        <v>76574.84</v>
+        <v>124651.57</v>
       </c>
       <c r="C8">
-        <v>438</v>
+        <v>362</v>
       </c>
       <c r="D8">
-        <v>404.35</v>
+        <v>305.76</v>
       </c>
       <c r="E8">
-        <v>190.96</v>
+        <v>196.61</v>
       </c>
       <c r="F8">
-        <v>2864.4</v>
+        <v>2359.34</v>
       </c>
       <c r="G8">
-        <v>175</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Trauma and Orthopaedic Service</t>
+          <t>Spinal Surgery Service</t>
         </is>
       </c>
       <c r="B9">
-        <v>10886823.55</v>
+        <v>76673.81</v>
       </c>
       <c r="C9">
-        <v>617</v>
+        <v>438</v>
       </c>
       <c r="D9">
-        <v>817.05</v>
+        <v>404.87</v>
       </c>
       <c r="E9">
-        <v>166.27</v>
+        <v>191.21</v>
       </c>
       <c r="F9">
-        <v>35914.75</v>
+        <v>2868.1</v>
       </c>
       <c r="G9">
-        <v>17633</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ear Nose and Throat Service</t>
+          <t>Trauma and Orthopaedic Service</t>
         </is>
       </c>
       <c r="B10">
-        <v>396501.71</v>
+        <v>10569709.78</v>
       </c>
       <c r="C10">
-        <v>335</v>
+        <v>607</v>
       </c>
       <c r="D10">
-        <v>768.88</v>
+        <v>694.54</v>
       </c>
       <c r="E10">
-        <v>161.9</v>
+        <v>166.42</v>
       </c>
       <c r="F10">
-        <v>24609.33</v>
+        <v>33449.5</v>
       </c>
       <c r="G10">
-        <v>1182</v>
+        <v>17426</v>
       </c>
     </row>
     <row r="11">
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>1639488.7</v>
+        <v>1646870.75</v>
       </c>
       <c r="C11">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D11">
-        <v>571.6</v>
+        <v>574.1799999999999</v>
       </c>
       <c r="E11">
-        <v>139.77</v>
+        <v>140.4</v>
       </c>
       <c r="F11">
-        <v>5590.75</v>
+        <v>5615.93</v>
       </c>
       <c r="G11">
         <v>3308</v>
@@ -648,19 +648,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>137196.29</v>
+        <v>137289.4</v>
       </c>
       <c r="C12">
         <v>392</v>
       </c>
       <c r="D12">
-        <v>290.56</v>
+        <v>290.76</v>
       </c>
       <c r="E12">
-        <v>203.25</v>
+        <v>203.39</v>
       </c>
       <c r="F12">
-        <v>2642.3</v>
+        <v>2644.09</v>
       </c>
       <c r="G12">
         <v>350</v>
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>95255.77</v>
+        <v>94259.49000000001</v>
       </c>
       <c r="C13">
-        <v>1108</v>
+        <v>1096</v>
       </c>
       <c r="D13">
-        <v>1120.69</v>
+        <v>1108.97</v>
       </c>
       <c r="E13">
-        <v>287.78</v>
+        <v>284.77</v>
       </c>
       <c r="F13">
-        <v>4316.73</v>
+        <v>4271.58</v>
       </c>
       <c r="G13">
         <v>86</v>
@@ -698,344 +698,344 @@
         </is>
       </c>
       <c r="B14">
-        <v>94051.59</v>
+        <v>583.54</v>
       </c>
       <c r="C14">
-        <v>369</v>
+        <v>195</v>
       </c>
       <c r="D14">
-        <v>289.4</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>194.32</v>
+        <v>194.51</v>
       </c>
       <c r="F14">
-        <v>2331.86</v>
+        <v>194.51</v>
       </c>
       <c r="G14">
-        <v>255</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Maxillofacial Surgery Service</t>
+          <t>Neurosurgical Service</t>
         </is>
       </c>
       <c r="B15">
-        <v>97623.24000000001</v>
+        <v>156266.63</v>
       </c>
       <c r="C15">
-        <v>378</v>
+        <v>519</v>
       </c>
       <c r="D15">
-        <v>361.5</v>
+        <v>494.29</v>
       </c>
       <c r="E15">
-        <v>182.13</v>
+        <v>236.41</v>
       </c>
       <c r="F15">
-        <v>3096.26</v>
+        <v>5201.01</v>
       </c>
       <c r="G15">
-        <v>258</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Neurosurgical Service</t>
+          <t>Plastic Surgery Service</t>
         </is>
       </c>
       <c r="B16">
-        <v>155493.42</v>
+        <v>170695.73</v>
       </c>
       <c r="C16">
-        <v>517</v>
+        <v>478</v>
       </c>
       <c r="D16">
-        <v>491.84</v>
+        <v>482.93</v>
       </c>
       <c r="E16">
-        <v>235.24</v>
+        <v>160.88</v>
       </c>
       <c r="F16">
-        <v>5175.27</v>
+        <v>3217.64</v>
       </c>
       <c r="G16">
-        <v>301</v>
+        <v>357</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Plastic Surgery Service</t>
+          <t>Cardiothoracic Surgery Service</t>
         </is>
       </c>
       <c r="B17">
-        <v>169723.58</v>
+        <v>14406.88</v>
       </c>
       <c r="C17">
-        <v>475</v>
+        <v>437</v>
       </c>
       <c r="D17">
-        <v>480.18</v>
+        <v>295.74</v>
       </c>
       <c r="E17">
-        <v>159.97</v>
+        <v>271.83</v>
       </c>
       <c r="F17">
-        <v>3199.31</v>
+        <v>1359.14</v>
       </c>
       <c r="G17">
-        <v>357</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Burns Care Service</t>
+          <t>Cardiac Surgery Service</t>
         </is>
       </c>
       <c r="B18">
-        <v>7514.02</v>
+        <v>17300.82</v>
       </c>
       <c r="C18">
-        <v>1252</v>
+        <v>494</v>
       </c>
       <c r="D18">
-        <v>949.63</v>
+        <v>286.47</v>
       </c>
       <c r="E18">
-        <v>156.54</v>
+        <v>283.62</v>
       </c>
       <c r="F18">
-        <v>2348.13</v>
+        <v>1418.1</v>
       </c>
       <c r="G18">
-        <v>6</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cardiothoracic Surgery Service</t>
+          <t>Thoracic Surgery Service</t>
         </is>
       </c>
       <c r="B19">
-        <v>14220.9</v>
+        <v>8230.629999999999</v>
       </c>
       <c r="C19">
-        <v>431</v>
+        <v>392</v>
       </c>
       <c r="D19">
-        <v>291.93</v>
+        <v>201.08</v>
       </c>
       <c r="E19">
-        <v>268.32</v>
+        <v>216.6</v>
       </c>
       <c r="F19">
-        <v>1341.59</v>
+        <v>866.38</v>
       </c>
       <c r="G19">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cardiac Surgery Service</t>
+          <t>Cardiothoracic Transplantation Service</t>
         </is>
       </c>
       <c r="B20">
-        <v>17183.34</v>
+        <v>35021.74</v>
       </c>
       <c r="C20">
-        <v>491</v>
+        <v>11674</v>
       </c>
       <c r="D20">
-        <v>284.52</v>
+        <v>9815.469999999999</v>
       </c>
       <c r="E20">
-        <v>281.69</v>
+        <v>625.39</v>
       </c>
       <c r="F20">
-        <v>1408.47</v>
+        <v>19387.03</v>
       </c>
       <c r="G20">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Thoracic Surgery Service</t>
+          <t>Emergency Medicine Service</t>
         </is>
       </c>
       <c r="B21">
-        <v>7477.2</v>
+        <v>69675.94</v>
       </c>
       <c r="C21">
-        <v>356</v>
+        <v>260</v>
       </c>
       <c r="D21">
-        <v>182.68</v>
+        <v>215.47</v>
       </c>
       <c r="E21">
-        <v>196.77</v>
+        <v>184.33</v>
       </c>
       <c r="F21">
-        <v>787.0700000000001</v>
+        <v>2027.61</v>
       </c>
       <c r="G21">
-        <v>21</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cardiothoracic Transplantation Service</t>
+          <t>Anaesthetic Service</t>
         </is>
       </c>
       <c r="B22">
-        <v>29265.01</v>
+        <v>68126.85000000001</v>
       </c>
       <c r="C22">
-        <v>9755</v>
+        <v>182</v>
       </c>
       <c r="D22">
-        <v>8202.049999999999</v>
+        <v>88.56</v>
       </c>
       <c r="E22">
-        <v>522.59</v>
+        <v>141.93</v>
       </c>
       <c r="F22">
-        <v>16200.28</v>
+        <v>709.65</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>375</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Anaesthetic Service</t>
+          <t>Pain Management Service</t>
         </is>
       </c>
       <c r="B23">
-        <v>68043.50999999999</v>
+        <v>272850.76</v>
       </c>
       <c r="C23">
-        <v>181</v>
+        <v>577</v>
       </c>
       <c r="D23">
-        <v>88.45</v>
+        <v>559.96</v>
       </c>
       <c r="E23">
-        <v>141.76</v>
+        <v>230.06</v>
       </c>
       <c r="F23">
-        <v>708.79</v>
+        <v>3680.95</v>
       </c>
       <c r="G23">
-        <v>375</v>
+        <v>473</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pain Management Service</t>
+          <t>Paediatric Trauma and Orthopaedic Service</t>
         </is>
       </c>
       <c r="B24">
-        <v>267954.53</v>
+        <v>3335.55</v>
       </c>
       <c r="C24">
-        <v>567</v>
+        <v>222</v>
       </c>
       <c r="D24">
-        <v>549.91</v>
+        <v>103.89</v>
       </c>
       <c r="E24">
-        <v>225.93</v>
+        <v>185.31</v>
       </c>
       <c r="F24">
-        <v>3614.9</v>
+        <v>555.9299999999999</v>
       </c>
       <c r="G24">
-        <v>473</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Paediatric Trauma and Orthopaedic Service</t>
+          <t>Paediatric Ear Nose and Throat Service</t>
         </is>
       </c>
       <c r="B25">
-        <v>3339.34</v>
+        <v>166.38</v>
       </c>
       <c r="C25">
-        <v>223</v>
-      </c>
-      <c r="D25">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="E25">
-        <v>185.52</v>
+        <v>166.38</v>
       </c>
       <c r="F25">
-        <v>556.5599999999999</v>
+        <v>166.38</v>
       </c>
       <c r="G25">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Paediatric Ear Nose and Throat Service</t>
+          <t>Paediatric Ophthalmology Service</t>
         </is>
       </c>
       <c r="B26">
-        <v>165.86</v>
+        <v>2222.36</v>
       </c>
       <c r="C26">
-        <v>166</v>
+        <v>317</v>
+      </c>
+      <c r="D26">
+        <v>296.98</v>
       </c>
       <c r="E26">
-        <v>165.86</v>
+        <v>138.9</v>
       </c>
       <c r="F26">
-        <v>165.86</v>
+        <v>972.28</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Paediatric Ophthalmology Service</t>
+          <t>General Internal Medicine Service</t>
         </is>
       </c>
       <c r="B27">
-        <v>2221.54</v>
+        <v>559264.26</v>
       </c>
       <c r="C27">
-        <v>317</v>
+        <v>497</v>
       </c>
       <c r="D27">
-        <v>296.87</v>
+        <v>1624.71</v>
       </c>
       <c r="E27">
-        <v>138.85</v>
+        <v>179.37</v>
       </c>
       <c r="F27">
-        <v>971.92</v>
+        <v>30492.28</v>
       </c>
       <c r="G27">
-        <v>7</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="28">
@@ -1045,19 +1045,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>291101.91</v>
+        <v>295754.48</v>
       </c>
       <c r="C28">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="D28">
-        <v>279.54</v>
+        <v>284.01</v>
       </c>
       <c r="E28">
-        <v>160.56</v>
+        <v>163.13</v>
       </c>
       <c r="F28">
-        <v>3211.27</v>
+        <v>3262.6</v>
       </c>
       <c r="G28">
         <v>949</v>
@@ -1070,19 +1070,19 @@
         </is>
       </c>
       <c r="B29">
-        <v>119658.73</v>
+        <v>120103.32</v>
       </c>
       <c r="C29">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D29">
-        <v>367.37</v>
+        <v>368.73</v>
       </c>
       <c r="E29">
-        <v>204.2</v>
+        <v>204.95</v>
       </c>
       <c r="F29">
-        <v>3062.94</v>
+        <v>3074.32</v>
       </c>
       <c r="G29">
         <v>269</v>
@@ -1095,19 +1095,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>291827.09</v>
+        <v>292626.24</v>
       </c>
       <c r="C30">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D30">
-        <v>739.71</v>
+        <v>741.73</v>
       </c>
       <c r="E30">
-        <v>182.39</v>
+        <v>182.89</v>
       </c>
       <c r="F30">
-        <v>6018.93</v>
+        <v>6035.42</v>
       </c>
       <c r="G30">
         <v>477</v>
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>77432.55</v>
+        <v>76902.41</v>
       </c>
       <c r="C31">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D31">
-        <v>111.9</v>
+        <v>111.14</v>
       </c>
       <c r="E31">
-        <v>103.52</v>
+        <v>102.81</v>
       </c>
       <c r="F31">
-        <v>1138.71</v>
+        <v>1130.92</v>
       </c>
       <c r="G31">
         <v>502</v>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>7804.58</v>
+        <v>7714.61</v>
       </c>
       <c r="C32">
-        <v>1115</v>
+        <v>1102</v>
       </c>
       <c r="D32">
-        <v>986.6799999999999</v>
+        <v>975.3099999999999</v>
       </c>
       <c r="E32">
-        <v>459.09</v>
+        <v>453.8</v>
       </c>
       <c r="F32">
-        <v>3213.65</v>
+        <v>3176.6</v>
       </c>
       <c r="G32">
         <v>7</v>
@@ -1170,19 +1170,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>26820.99</v>
+        <v>26846.86</v>
       </c>
       <c r="C33">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D33">
-        <v>214.8</v>
+        <v>215.01</v>
       </c>
       <c r="E33">
-        <v>186.26</v>
+        <v>186.44</v>
       </c>
       <c r="F33">
-        <v>931.28</v>
+        <v>932.1799999999999</v>
       </c>
       <c r="G33">
         <v>70</v>
@@ -1191,48 +1191,48 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Blood and Marrow Transplantation Service</t>
+          <t>Diabetes Service</t>
         </is>
       </c>
       <c r="B34">
-        <v>409.78</v>
+        <v>184867.16</v>
       </c>
       <c r="C34">
-        <v>410</v>
+        <v>690</v>
+      </c>
+      <c r="D34">
+        <v>1039.43</v>
       </c>
       <c r="E34">
-        <v>409.78</v>
+        <v>199</v>
       </c>
       <c r="F34">
-        <v>409.78</v>
+        <v>10944.77</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Haemophilia Service</t>
+          <t>Blood and Marrow Transplantation Service</t>
         </is>
       </c>
       <c r="B35">
-        <v>8751.219999999999</v>
+        <v>408.86</v>
       </c>
       <c r="C35">
-        <v>1094</v>
-      </c>
-      <c r="D35">
-        <v>698.14</v>
+        <v>409</v>
       </c>
       <c r="E35">
-        <v>514.78</v>
+        <v>408.86</v>
       </c>
       <c r="F35">
-        <v>2573.89</v>
+        <v>408.86</v>
       </c>
       <c r="G35">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1242,19 +1242,19 @@
         </is>
       </c>
       <c r="B36">
-        <v>5301.46</v>
+        <v>5320.18</v>
       </c>
       <c r="C36">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>530.15</v>
+        <v>532.02</v>
       </c>
       <c r="F36">
-        <v>530.15</v>
+        <v>532.02</v>
       </c>
       <c r="G36">
         <v>10</v>
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="B37">
-        <v>9810.190000000001</v>
+        <v>10513.33</v>
       </c>
       <c r="C37">
-        <v>491</v>
+        <v>526</v>
       </c>
       <c r="D37">
-        <v>378.72</v>
+        <v>405.86</v>
       </c>
       <c r="E37">
-        <v>208.73</v>
+        <v>223.69</v>
       </c>
       <c r="F37">
-        <v>1461.09</v>
+        <v>1565.82</v>
       </c>
       <c r="G37">
         <v>20</v>
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="B38">
-        <v>382280.83</v>
+        <v>381130.3</v>
       </c>
       <c r="C38">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="D38">
-        <v>1718.66</v>
+        <v>1713.49</v>
       </c>
       <c r="E38">
-        <v>277.42</v>
+        <v>276.58</v>
       </c>
       <c r="F38">
-        <v>17754.7</v>
+        <v>17701.26</v>
       </c>
       <c r="G38">
         <v>318</v>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="B39">
-        <v>51480.52</v>
+        <v>52560.7</v>
       </c>
       <c r="C39">
-        <v>1514</v>
+        <v>1546</v>
       </c>
       <c r="D39">
-        <v>3023.57</v>
+        <v>3087.01</v>
       </c>
       <c r="E39">
-        <v>242.83</v>
+        <v>247.93</v>
       </c>
       <c r="F39">
-        <v>16269.79</v>
+        <v>16611.17</v>
       </c>
       <c r="G39">
         <v>34</v>
@@ -1342,19 +1342,19 @@
         </is>
       </c>
       <c r="B40">
-        <v>13163.12</v>
+        <v>13183.51</v>
       </c>
       <c r="C40">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="D40">
-        <v>900.08</v>
+        <v>901.47</v>
       </c>
       <c r="E40">
-        <v>411.35</v>
+        <v>411.98</v>
       </c>
       <c r="F40">
-        <v>2879.43</v>
+        <v>2883.89</v>
       </c>
       <c r="G40">
         <v>12</v>
@@ -1363,448 +1363,448 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Allergy Service</t>
+          <t>Intermediate Care Service</t>
         </is>
       </c>
       <c r="B41">
-        <v>19233.52</v>
+        <v>160654.72</v>
       </c>
       <c r="C41">
-        <v>1374</v>
+        <v>956</v>
       </c>
       <c r="D41">
-        <v>3353.74</v>
+        <v>1617.99</v>
       </c>
       <c r="E41">
-        <v>249.79</v>
+        <v>71.78</v>
       </c>
       <c r="F41">
-        <v>12988.87</v>
+        <v>10624.17</v>
       </c>
       <c r="G41">
-        <v>14</v>
+        <v>168</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Intermediate Care Service</t>
+          <t>Cardiology Service</t>
         </is>
       </c>
       <c r="B42">
-        <v>150987</v>
+        <v>717043.51</v>
       </c>
       <c r="C42">
-        <v>1110</v>
+        <v>356</v>
       </c>
       <c r="D42">
-        <v>1758.53</v>
+        <v>341.51</v>
       </c>
       <c r="E42">
-        <v>84.06999999999999</v>
+        <v>166.41</v>
       </c>
       <c r="F42">
-        <v>10172.29</v>
+        <v>4825.77</v>
       </c>
       <c r="G42">
-        <v>136</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cardiology Service</t>
+          <t>Clinical Microbiology Service</t>
         </is>
       </c>
       <c r="B43">
-        <v>719196.0699999999</v>
+        <v>798.98</v>
       </c>
       <c r="C43">
-        <v>357</v>
+        <v>114</v>
       </c>
       <c r="D43">
-        <v>342.53</v>
+        <v>62.86</v>
       </c>
       <c r="E43">
-        <v>166.91</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F43">
-        <v>4840.26</v>
+        <v>239.69</v>
       </c>
       <c r="G43">
-        <v>2015</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Clinical Microbiology Service</t>
+          <t>Spinal Injuries Service</t>
         </is>
       </c>
       <c r="B44">
-        <v>352.81</v>
+        <v>10826.9</v>
       </c>
       <c r="C44">
-        <v>50</v>
+        <v>1083</v>
       </c>
       <c r="D44">
-        <v>27.76</v>
+        <v>838.49</v>
       </c>
       <c r="E44">
-        <v>35.28</v>
+        <v>318.44</v>
       </c>
       <c r="F44">
-        <v>105.84</v>
+        <v>3184.38</v>
       </c>
       <c r="G44">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Spinal Injuries Service</t>
+          <t>Anticoagulant Service</t>
         </is>
       </c>
       <c r="B45">
-        <v>10923.34</v>
+        <v>214282.4</v>
       </c>
       <c r="C45">
-        <v>1092</v>
+        <v>719</v>
       </c>
       <c r="D45">
-        <v>845.96</v>
+        <v>840.8</v>
       </c>
       <c r="E45">
-        <v>321.27</v>
+        <v>72</v>
       </c>
       <c r="F45">
-        <v>3212.75</v>
+        <v>3888.19</v>
       </c>
       <c r="G45">
-        <v>10</v>
+        <v>298</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Anticoagulant Service</t>
+          <t>Sport and Exercise Medicine Service</t>
         </is>
       </c>
       <c r="B46">
-        <v>211077.88</v>
+        <v>846.66</v>
       </c>
       <c r="C46">
-        <v>708</v>
-      </c>
-      <c r="D46">
-        <v>828.22</v>
+        <v>847</v>
       </c>
       <c r="E46">
-        <v>70.93000000000001</v>
+        <v>846.66</v>
       </c>
       <c r="F46">
-        <v>3830.04</v>
+        <v>846.66</v>
       </c>
       <c r="G46">
-        <v>298</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sport and Exercise Medicine Service</t>
+          <t>Cardiac Rehabilitation Service</t>
         </is>
       </c>
       <c r="B47">
-        <v>807.4</v>
+        <v>11906.01</v>
       </c>
       <c r="C47">
-        <v>807</v>
+        <v>1191</v>
+      </c>
+      <c r="D47">
+        <v>901.75</v>
       </c>
       <c r="E47">
-        <v>807.4</v>
+        <v>114.48</v>
       </c>
       <c r="F47">
-        <v>807.4</v>
+        <v>2862.02</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cardiac Rehabilitation Service</t>
+          <t>Stroke Medicine Service</t>
         </is>
       </c>
       <c r="B48">
-        <v>11760.13</v>
+        <v>23590.39</v>
       </c>
       <c r="C48">
-        <v>1176</v>
+        <v>414</v>
       </c>
       <c r="D48">
-        <v>890.7</v>
+        <v>238.94</v>
       </c>
       <c r="E48">
-        <v>113.08</v>
+        <v>314.54</v>
       </c>
       <c r="F48">
-        <v>2826.95</v>
+        <v>1887.23</v>
       </c>
       <c r="G48">
-        <v>10</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Stroke Medicine Service</t>
+          <t>Transient Ischaemic Attack Service</t>
         </is>
       </c>
       <c r="B49">
-        <v>23447.8</v>
+        <v>41758.2</v>
       </c>
       <c r="C49">
-        <v>411</v>
+        <v>360</v>
       </c>
       <c r="D49">
-        <v>237.49</v>
+        <v>150.28</v>
       </c>
       <c r="E49">
-        <v>312.64</v>
+        <v>296.16</v>
       </c>
       <c r="F49">
-        <v>1875.82</v>
+        <v>1184.63</v>
       </c>
       <c r="G49">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Transient Ischaemic Attack Service</t>
+          <t>Dermatology Service</t>
         </is>
       </c>
       <c r="B50">
-        <v>41796.14</v>
+        <v>450026.81</v>
       </c>
       <c r="C50">
-        <v>360</v>
+        <v>403</v>
       </c>
       <c r="D50">
-        <v>150.42</v>
+        <v>664.47</v>
       </c>
       <c r="E50">
-        <v>296.43</v>
+        <v>158.74</v>
       </c>
       <c r="F50">
-        <v>1185.71</v>
+        <v>10953.03</v>
       </c>
       <c r="G50">
-        <v>116</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dermatology Service</t>
+          <t>Congenital Heart Disease Service</t>
         </is>
       </c>
       <c r="B51">
-        <v>447710.52</v>
+        <v>1344.46</v>
       </c>
       <c r="C51">
-        <v>400</v>
+        <v>672</v>
       </c>
       <c r="D51">
-        <v>661.05</v>
+        <v>633.78</v>
       </c>
       <c r="E51">
-        <v>157.92</v>
+        <v>224.08</v>
       </c>
       <c r="F51">
-        <v>10896.66</v>
+        <v>1120.38</v>
       </c>
       <c r="G51">
-        <v>1118</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Congenital Heart Disease Service</t>
+          <t>Respiratory Physiology Service</t>
         </is>
       </c>
       <c r="B52">
-        <v>1350.48</v>
+        <v>32320.77</v>
       </c>
       <c r="C52">
-        <v>675</v>
+        <v>259</v>
       </c>
       <c r="D52">
-        <v>636.62</v>
+        <v>217.39</v>
       </c>
       <c r="E52">
-        <v>225.08</v>
+        <v>143.65</v>
       </c>
       <c r="F52">
-        <v>1125.4</v>
+        <v>1436.48</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Respiratory Medicine Service</t>
+          <t>Pulmonary Rehabilitation Service</t>
         </is>
       </c>
       <c r="B53">
-        <v>481146.26</v>
+        <v>792.04</v>
       </c>
       <c r="C53">
-        <v>555</v>
+        <v>132</v>
       </c>
       <c r="D53">
-        <v>780.77</v>
+        <v>95.92</v>
       </c>
       <c r="E53">
-        <v>192.15</v>
+        <v>79.2</v>
       </c>
       <c r="F53">
-        <v>12874.12</v>
+        <v>316.82</v>
       </c>
       <c r="G53">
-        <v>867</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Respiratory Physiology Service</t>
+          <t>Complex Specialised Rehabilitation Service</t>
         </is>
       </c>
       <c r="B54">
-        <v>32415.8</v>
+        <v>3176.17</v>
       </c>
       <c r="C54">
-        <v>259</v>
+        <v>1059</v>
       </c>
       <c r="D54">
-        <v>218.03</v>
+        <v>1163.17</v>
       </c>
       <c r="E54">
-        <v>144.07</v>
+        <v>198.51</v>
       </c>
       <c r="F54">
-        <v>1440.7</v>
+        <v>2382.13</v>
       </c>
       <c r="G54">
-        <v>125</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Complex Specialised Rehabilitation Service</t>
+          <t>Infectious Diseases Service</t>
         </is>
       </c>
       <c r="B55">
-        <v>3176.17</v>
+        <v>17361.07</v>
       </c>
       <c r="C55">
-        <v>1059</v>
+        <v>668</v>
       </c>
       <c r="D55">
-        <v>1163.17</v>
+        <v>629.63</v>
       </c>
       <c r="E55">
-        <v>198.51</v>
+        <v>299.33</v>
       </c>
       <c r="F55">
-        <v>2382.13</v>
+        <v>2394.63</v>
       </c>
       <c r="G55">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Infectious Diseases Service</t>
+          <t>Tropical Medicine Service</t>
         </is>
       </c>
       <c r="B56">
-        <v>17370.92</v>
+        <v>695.9</v>
       </c>
       <c r="C56">
-        <v>668</v>
+        <v>232</v>
       </c>
       <c r="D56">
-        <v>629.99</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>299.5</v>
+        <v>231.97</v>
       </c>
       <c r="F56">
-        <v>2395.99</v>
+        <v>231.97</v>
       </c>
       <c r="G56">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tropical Medicine Service</t>
+          <t>Genitourinary Medicine Service</t>
         </is>
       </c>
       <c r="B57">
-        <v>684.61</v>
+        <v>3699.53</v>
       </c>
       <c r="C57">
-        <v>228</v>
+        <v>617</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>393.17</v>
       </c>
       <c r="E57">
-        <v>228.2</v>
+        <v>336.32</v>
       </c>
       <c r="F57">
-        <v>228.2</v>
+        <v>1345.29</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Genitourinary Medicine Service</t>
+          <t>Renal Medicine Service</t>
         </is>
       </c>
       <c r="B58">
-        <v>3575.6</v>
+        <v>192899.99</v>
       </c>
       <c r="C58">
-        <v>596</v>
+        <v>745</v>
       </c>
       <c r="D58">
-        <v>380</v>
+        <v>832.38</v>
       </c>
       <c r="E58">
-        <v>325.05</v>
+        <v>201.15</v>
       </c>
       <c r="F58">
-        <v>1300.22</v>
+        <v>5430.97</v>
       </c>
       <c r="G58">
-        <v>6</v>
+        <v>259</v>
       </c>
     </row>
     <row r="59">
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B59">
-        <v>57426.62</v>
+        <v>57774.33</v>
       </c>
       <c r="C59">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="D59">
-        <v>1332.31</v>
+        <v>1340.38</v>
       </c>
       <c r="E59">
-        <v>192.71</v>
+        <v>193.87</v>
       </c>
       <c r="F59">
-        <v>9442.629999999999</v>
+        <v>9499.809999999999</v>
       </c>
       <c r="G59">
         <v>73</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B60">
-        <v>5704.43</v>
+        <v>5864</v>
       </c>
       <c r="C60">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D60">
-        <v>151.86</v>
+        <v>156.1</v>
       </c>
       <c r="E60">
-        <v>103.72</v>
+        <v>106.62</v>
       </c>
       <c r="F60">
-        <v>829.74</v>
+        <v>852.95</v>
       </c>
       <c r="G60">
         <v>30</v>
@@ -1864,619 +1864,694 @@
         </is>
       </c>
       <c r="B61">
-        <v>621127.98</v>
+        <v>404954.85</v>
       </c>
       <c r="C61">
-        <v>616</v>
+        <v>531</v>
       </c>
       <c r="D61">
-        <v>695.11</v>
+        <v>544.58</v>
       </c>
       <c r="E61">
-        <v>233.59</v>
+        <v>238.21</v>
       </c>
       <c r="F61">
-        <v>6307.05</v>
+        <v>6193.43</v>
       </c>
       <c r="G61">
-        <v>1009</v>
+        <v>762</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Clinical Neurophysiology Service</t>
+          <t>Rheumatology Service</t>
         </is>
       </c>
       <c r="B62">
-        <v>93673.66</v>
+        <v>980527.4</v>
       </c>
       <c r="C62">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="D62">
-        <v>186.6</v>
+        <v>537.88</v>
       </c>
       <c r="E62">
-        <v>367.35</v>
+        <v>187.27</v>
       </c>
       <c r="F62">
-        <v>1836.74</v>
+        <v>10861.46</v>
       </c>
       <c r="G62">
-        <v>221</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Rheumatology Service</t>
+          <t>Paediatric Service</t>
         </is>
       </c>
       <c r="B63">
-        <v>947981.14</v>
+        <v>611.47</v>
       </c>
       <c r="C63">
-        <v>432</v>
+        <v>306</v>
       </c>
       <c r="D63">
-        <v>520.03</v>
+        <v>0</v>
       </c>
       <c r="E63">
-        <v>181.05</v>
+        <v>305.73</v>
       </c>
       <c r="F63">
-        <v>10500.94</v>
+        <v>305.73</v>
       </c>
       <c r="G63">
-        <v>2194</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Paediatric Service</t>
+          <t>Elderly Medicine Service</t>
         </is>
       </c>
       <c r="B64">
-        <v>607.53</v>
+        <v>1177878.03</v>
       </c>
       <c r="C64">
-        <v>304</v>
+        <v>876</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>1559.01</v>
       </c>
       <c r="E64">
-        <v>303.77</v>
+        <v>367.17</v>
       </c>
       <c r="F64">
-        <v>303.77</v>
+        <v>33779.54</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Elderly Medicine Service</t>
+          <t>Dental Medicine Service</t>
         </is>
       </c>
       <c r="B65">
-        <v>1512911.87</v>
+        <v>20640.2</v>
       </c>
       <c r="C65">
-        <v>952</v>
+        <v>356</v>
       </c>
       <c r="D65">
-        <v>1649.88</v>
+        <v>338.19</v>
       </c>
       <c r="E65">
-        <v>365.7</v>
+        <v>158.77</v>
       </c>
       <c r="F65">
-        <v>33644.64</v>
+        <v>2064.02</v>
       </c>
       <c r="G65">
-        <v>1589</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Dental Medicine Service</t>
+          <t>Medical Ophthalmology Service</t>
         </is>
       </c>
       <c r="B66">
-        <v>20327.39</v>
+        <v>10987.59</v>
       </c>
       <c r="C66">
-        <v>350</v>
+        <v>193</v>
       </c>
       <c r="D66">
-        <v>333.07</v>
+        <v>335.72</v>
       </c>
       <c r="E66">
-        <v>156.36</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F66">
-        <v>2032.74</v>
+        <v>2549.12</v>
       </c>
       <c r="G66">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Medical Ophthalmology Service</t>
+          <t>Gynaecology Service</t>
         </is>
       </c>
       <c r="B67">
-        <v>14279.08</v>
+        <v>395483.87</v>
       </c>
       <c r="C67">
-        <v>251</v>
+        <v>437</v>
       </c>
       <c r="D67">
-        <v>436.29</v>
+        <v>356.74</v>
       </c>
       <c r="E67">
-        <v>114.23</v>
+        <v>196.17</v>
       </c>
       <c r="F67">
-        <v>3312.75</v>
+        <v>4315.8</v>
       </c>
       <c r="G67">
-        <v>57</v>
+        <v>904</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Obstetrics Service</t>
+          <t>Gynaecological Oncology Service</t>
         </is>
       </c>
       <c r="B68">
-        <v>758.11</v>
+        <v>37797.36</v>
       </c>
       <c r="C68">
-        <v>190</v>
+        <v>329</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>314.54</v>
       </c>
       <c r="E68">
-        <v>189.53</v>
+        <v>189.94</v>
       </c>
       <c r="F68">
-        <v>189.53</v>
+        <v>2659.11</v>
       </c>
       <c r="G68">
-        <v>4</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Gynaecology Service</t>
+          <t>Physiotherapy Service</t>
         </is>
       </c>
       <c r="B69">
-        <v>393881</v>
+        <v>2680196.17</v>
       </c>
       <c r="C69">
-        <v>436</v>
+        <v>501</v>
       </c>
       <c r="D69">
-        <v>355.29</v>
+        <v>515.77</v>
       </c>
       <c r="E69">
-        <v>195.38</v>
+        <v>101.2</v>
       </c>
       <c r="F69">
-        <v>4298.3</v>
+        <v>11030.45</v>
       </c>
       <c r="G69">
-        <v>904</v>
+        <v>5351</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Gynaecological Oncology Service</t>
+          <t>Occupational Therapy Service</t>
         </is>
       </c>
       <c r="B70">
-        <v>37740.56</v>
+        <v>373419.3</v>
       </c>
       <c r="C70">
-        <v>328</v>
+        <v>606</v>
       </c>
       <c r="D70">
-        <v>314.07</v>
+        <v>926.21</v>
       </c>
       <c r="E70">
-        <v>189.65</v>
+        <v>135.94</v>
       </c>
       <c r="F70">
-        <v>2655.11</v>
+        <v>11418.72</v>
       </c>
       <c r="G70">
-        <v>115</v>
+        <v>616</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Physiotherapy Service</t>
+          <t>Podiatry Service</t>
         </is>
       </c>
       <c r="B71">
-        <v>2682393.17</v>
+        <v>154418.29</v>
       </c>
       <c r="C71">
-        <v>501</v>
+        <v>415</v>
       </c>
       <c r="D71">
-        <v>516.1900000000001</v>
+        <v>465.04</v>
       </c>
       <c r="E71">
-        <v>101.28</v>
+        <v>102.33</v>
       </c>
       <c r="F71">
-        <v>11039.49</v>
+        <v>3274.61</v>
       </c>
       <c r="G71">
-        <v>5351</v>
+        <v>372</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Occupational Therapy Service</t>
+          <t>Dietetics Service</t>
         </is>
       </c>
       <c r="B72">
-        <v>373437.21</v>
+        <v>81786.95</v>
       </c>
       <c r="C72">
-        <v>606</v>
+        <v>357</v>
       </c>
       <c r="D72">
-        <v>926.26</v>
+        <v>458.86</v>
       </c>
       <c r="E72">
-        <v>135.94</v>
+        <v>131.49</v>
       </c>
       <c r="F72">
-        <v>11419.27</v>
+        <v>4996.63</v>
       </c>
       <c r="G72">
-        <v>616</v>
+        <v>229</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Speech and Language Therapy Service</t>
+          <t>Orthoptics Service</t>
         </is>
       </c>
       <c r="B73">
-        <v>49555.37</v>
+        <v>33580.08</v>
       </c>
       <c r="C73">
-        <v>570</v>
+        <v>189</v>
       </c>
       <c r="D73">
-        <v>627.17</v>
+        <v>134.08</v>
       </c>
       <c r="E73">
-        <v>234.86</v>
+        <v>102.38</v>
       </c>
       <c r="F73">
-        <v>4697.19</v>
+        <v>819.03</v>
       </c>
       <c r="G73">
-        <v>87</v>
+        <v>178</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Orthoptics Service</t>
+          <t>Clinical Psychology Service</t>
         </is>
       </c>
       <c r="B74">
-        <v>33557.94</v>
+        <v>27266.99</v>
       </c>
       <c r="C74">
-        <v>189</v>
+        <v>1435</v>
       </c>
       <c r="D74">
-        <v>133.99</v>
+        <v>2161.01</v>
       </c>
       <c r="E74">
-        <v>102.31</v>
+        <v>281.1</v>
       </c>
       <c r="F74">
-        <v>818.49</v>
+        <v>9838.6</v>
       </c>
       <c r="G74">
-        <v>178</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Clinical Psychology Service</t>
+          <t>Prosthetics Service</t>
         </is>
       </c>
       <c r="B75">
-        <v>27277.24</v>
+        <v>683.75</v>
       </c>
       <c r="C75">
-        <v>1436</v>
+        <v>171</v>
       </c>
       <c r="D75">
-        <v>2161.82</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="E75">
-        <v>281.21</v>
+        <v>113.96</v>
       </c>
       <c r="F75">
-        <v>9842.299999999999</v>
+        <v>227.92</v>
       </c>
       <c r="G75">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Prosthetics Service</t>
+          <t>Orthotics Service</t>
         </is>
       </c>
       <c r="B76">
-        <v>685.05</v>
+        <v>91235.21000000001</v>
       </c>
       <c r="C76">
-        <v>171</v>
+        <v>362</v>
       </c>
       <c r="D76">
-        <v>65.92</v>
+        <v>283.55</v>
       </c>
       <c r="E76">
-        <v>114.18</v>
+        <v>189.68</v>
       </c>
       <c r="F76">
-        <v>228.35</v>
+        <v>2276.14</v>
       </c>
       <c r="G76">
-        <v>4</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Podiatric Surgery Service</t>
+          <t>Optometry Service</t>
         </is>
       </c>
       <c r="B77">
-        <v>7489.88</v>
+        <v>7136.12</v>
       </c>
       <c r="C77">
-        <v>499</v>
+        <v>193</v>
       </c>
       <c r="D77">
-        <v>404.19</v>
+        <v>118.99</v>
       </c>
       <c r="E77">
-        <v>170.22</v>
+        <v>132.15</v>
       </c>
       <c r="F77">
-        <v>1532.02</v>
+        <v>528.6</v>
       </c>
       <c r="G77">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Learning Disability Service</t>
+          <t>Podiatric Surgery Service</t>
         </is>
       </c>
       <c r="B78">
-        <v>309.08</v>
+        <v>7579.3</v>
       </c>
       <c r="C78">
-        <v>44</v>
+        <v>505</v>
       </c>
       <c r="D78">
-        <v>14.6</v>
+        <v>409.02</v>
       </c>
       <c r="E78">
-        <v>38.64</v>
+        <v>172.26</v>
       </c>
       <c r="F78">
-        <v>77.27</v>
+        <v>1550.31</v>
       </c>
       <c r="G78">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Child and Adolescent Psychiatry Service</t>
+          <t>Learning Disability Service</t>
         </is>
       </c>
       <c r="B79">
-        <v>1421.85</v>
+        <v>64.39</v>
       </c>
       <c r="C79">
-        <v>1422</v>
+        <v>13</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
       </c>
       <c r="E79">
-        <v>1421.85</v>
+        <v>12.88</v>
       </c>
       <c r="F79">
-        <v>1421.85</v>
+        <v>12.88</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Old Age Psychiatry Service</t>
+          <t>Child and Adolescent Psychiatry Service</t>
         </is>
       </c>
       <c r="B80">
-        <v>410097.54</v>
+        <v>1422.12</v>
       </c>
       <c r="C80">
-        <v>884</v>
-      </c>
-      <c r="D80">
-        <v>1594.44</v>
+        <v>1422</v>
       </c>
       <c r="E80">
-        <v>288.39</v>
+        <v>1422.12</v>
       </c>
       <c r="F80">
-        <v>18457.27</v>
+        <v>1422.12</v>
       </c>
       <c r="G80">
-        <v>464</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Liaison Psychiatry Service</t>
+          <t>Medical Psychotherapy Service</t>
         </is>
       </c>
       <c r="B81">
-        <v>24796.68</v>
+        <v>3395.42</v>
       </c>
       <c r="C81">
-        <v>886</v>
+        <v>1132</v>
       </c>
       <c r="D81">
-        <v>963.12</v>
+        <v>980.17</v>
       </c>
       <c r="E81">
-        <v>281.78</v>
+        <v>565.9</v>
       </c>
       <c r="F81">
-        <v>3944.93</v>
+        <v>2263.61</v>
       </c>
       <c r="G81">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Clinical Oncology Service</t>
+          <t>Old Age Psychiatry Service</t>
         </is>
       </c>
       <c r="B82">
-        <v>92337.11</v>
+        <v>405735.49</v>
       </c>
       <c r="C82">
-        <v>694</v>
+        <v>874</v>
       </c>
       <c r="D82">
-        <v>1041.61</v>
+        <v>1577.48</v>
       </c>
       <c r="E82">
-        <v>157.57</v>
+        <v>285.33</v>
       </c>
       <c r="F82">
-        <v>6145.3</v>
+        <v>18260.95</v>
       </c>
       <c r="G82">
-        <v>133</v>
+        <v>464</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Interventional Radiology Service</t>
+          <t>Liaison Psychiatry Service</t>
         </is>
       </c>
       <c r="B83">
-        <v>24923.12</v>
+        <v>24871.78</v>
       </c>
       <c r="C83">
-        <v>145</v>
+        <v>888</v>
       </c>
       <c r="D83">
-        <v>36.52</v>
+        <v>966.03</v>
       </c>
       <c r="E83">
-        <v>136.19</v>
+        <v>282.63</v>
       </c>
       <c r="F83">
-        <v>408.58</v>
+        <v>3956.87</v>
       </c>
       <c r="G83">
-        <v>172</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging Service</t>
+          <t>Clinical Oncology Service</t>
         </is>
       </c>
       <c r="B84">
-        <v>219933.17</v>
+        <v>93787.3</v>
       </c>
       <c r="C84">
-        <v>75</v>
+        <v>705</v>
       </c>
       <c r="D84">
-        <v>70.06</v>
+        <v>1057.97</v>
       </c>
       <c r="E84">
-        <v>38.6</v>
+        <v>160.05</v>
       </c>
       <c r="F84">
-        <v>1582.53</v>
+        <v>6241.82</v>
       </c>
       <c r="G84">
-        <v>2933</v>
+        <v>133</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>Interventional Radiology Service</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>25446.39</v>
+      </c>
+      <c r="C85">
+        <v>148</v>
+      </c>
+      <c r="D85">
+        <v>37.29</v>
+      </c>
+      <c r="E85">
+        <v>139.05</v>
+      </c>
+      <c r="F85">
+        <v>417.15</v>
+      </c>
+      <c r="G85">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Diagnostic Imaging Service</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>227759.72</v>
+      </c>
+      <c r="C86">
+        <v>78</v>
+      </c>
+      <c r="D86">
+        <v>72.56</v>
+      </c>
+      <c r="E86">
+        <v>39.97</v>
+      </c>
+      <c r="F86">
+        <v>1638.85</v>
+      </c>
+      <c r="G86">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>Chemical Pathology Service</t>
         </is>
       </c>
-      <c r="B85">
-        <v>9220.610000000001</v>
-      </c>
-      <c r="C85">
-        <v>249</v>
-      </c>
-      <c r="D85">
-        <v>166.19</v>
-      </c>
-      <c r="E85">
-        <v>91.29000000000001</v>
-      </c>
-      <c r="F85">
-        <v>639.05</v>
-      </c>
-      <c r="G85">
+      <c r="B87">
+        <v>9491.58</v>
+      </c>
+      <c r="C87">
+        <v>257</v>
+      </c>
+      <c r="D87">
+        <v>171.07</v>
+      </c>
+      <c r="E87">
+        <v>93.98</v>
+      </c>
+      <c r="F87">
+        <v>657.83</v>
+      </c>
+      <c r="G87">
         <v>37</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Audiology Service</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>219717.54</v>
+      </c>
+      <c r="C88">
+        <v>279</v>
+      </c>
+      <c r="D88">
+        <v>209.25</v>
+      </c>
+      <c r="E88">
+        <v>116.68</v>
+      </c>
+      <c r="F88">
+        <v>2450.38</v>
+      </c>
+      <c r="G88">
+        <v>787</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_costs_by_tretspef-Users_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_costs_by_tretspef-Users_OMOP.xlsx
@@ -398,19 +398,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>350931.38</v>
+        <v>346287.5</v>
       </c>
       <c r="C2">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D2">
-        <v>325.67</v>
+        <v>321.36</v>
       </c>
       <c r="E2">
-        <v>182.49</v>
+        <v>180.08</v>
       </c>
       <c r="F2">
-        <v>4927.27</v>
+        <v>4862.07</v>
       </c>
       <c r="G2">
         <v>1062</v>
@@ -423,19 +423,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>360342.68</v>
+        <v>357036.97</v>
       </c>
       <c r="C3">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D3">
-        <v>337.15</v>
+        <v>334.06</v>
       </c>
       <c r="E3">
-        <v>152.16</v>
+        <v>150.77</v>
       </c>
       <c r="F3">
-        <v>4516.79</v>
+        <v>4475.13</v>
       </c>
       <c r="G3">
         <v>1043</v>
@@ -448,19 +448,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>14136.8</v>
+        <v>14192.67</v>
       </c>
       <c r="C4">
-        <v>1178</v>
+        <v>1183</v>
       </c>
       <c r="D4">
-        <v>1124.11</v>
+        <v>1128.55</v>
       </c>
       <c r="E4">
-        <v>344.8</v>
+        <v>346.16</v>
       </c>
       <c r="F4">
-        <v>3103.2</v>
+        <v>3115.46</v>
       </c>
       <c r="G4">
         <v>12</v>
@@ -473,19 +473,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>123061.96</v>
+        <v>121465.09</v>
       </c>
       <c r="C5">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D5">
-        <v>203.17</v>
+        <v>200.53</v>
       </c>
       <c r="E5">
-        <v>148.81</v>
+        <v>146.87</v>
       </c>
       <c r="F5">
-        <v>2678.49</v>
+        <v>2643.74</v>
       </c>
       <c r="G5">
         <v>545</v>
@@ -498,19 +498,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>15236.42</v>
+        <v>14879.43</v>
       </c>
       <c r="C6">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="D6">
-        <v>352.77</v>
+        <v>344.5</v>
       </c>
       <c r="E6">
-        <v>238.07</v>
+        <v>232.49</v>
       </c>
       <c r="F6">
-        <v>1428.41</v>
+        <v>1394.95</v>
       </c>
       <c r="G6">
         <v>31</v>
@@ -523,19 +523,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>26164.03</v>
+        <v>25946.11</v>
       </c>
       <c r="C7">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D7">
-        <v>207.1</v>
+        <v>205.38</v>
       </c>
       <c r="E7">
-        <v>185.56</v>
+        <v>184.01</v>
       </c>
       <c r="F7">
-        <v>1484.48</v>
+        <v>1472.12</v>
       </c>
       <c r="G7">
         <v>89</v>
@@ -548,19 +548,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>124651.57</v>
+        <v>124647.52</v>
       </c>
       <c r="C8">
         <v>362</v>
       </c>
       <c r="D8">
-        <v>305.76</v>
+        <v>305.75</v>
       </c>
       <c r="E8">
-        <v>196.61</v>
+        <v>196.6</v>
       </c>
       <c r="F8">
-        <v>2359.34</v>
+        <v>2359.26</v>
       </c>
       <c r="G8">
         <v>344</v>
@@ -573,19 +573,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>76673.81</v>
+        <v>76574.84</v>
       </c>
       <c r="C9">
         <v>438</v>
       </c>
       <c r="D9">
-        <v>404.87</v>
+        <v>404.35</v>
       </c>
       <c r="E9">
-        <v>191.21</v>
+        <v>190.96</v>
       </c>
       <c r="F9">
-        <v>2868.1</v>
+        <v>2864.4</v>
       </c>
       <c r="G9">
         <v>175</v>
@@ -598,19 +598,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>10569709.78</v>
+        <v>10560597.94</v>
       </c>
       <c r="C10">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D10">
-        <v>694.54</v>
+        <v>693.95</v>
       </c>
       <c r="E10">
-        <v>166.42</v>
+        <v>166.27</v>
       </c>
       <c r="F10">
-        <v>33449.5</v>
+        <v>33420.67</v>
       </c>
       <c r="G10">
         <v>17426</v>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>1646870.75</v>
+        <v>1639488.7</v>
       </c>
       <c r="C11">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D11">
-        <v>574.1799999999999</v>
+        <v>571.6</v>
       </c>
       <c r="E11">
-        <v>140.4</v>
+        <v>139.77</v>
       </c>
       <c r="F11">
-        <v>5615.93</v>
+        <v>5590.75</v>
       </c>
       <c r="G11">
         <v>3308</v>
@@ -648,19 +648,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>137289.4</v>
+        <v>137196.29</v>
       </c>
       <c r="C12">
         <v>392</v>
       </c>
       <c r="D12">
-        <v>290.76</v>
+        <v>290.56</v>
       </c>
       <c r="E12">
-        <v>203.39</v>
+        <v>203.25</v>
       </c>
       <c r="F12">
-        <v>2644.09</v>
+        <v>2642.3</v>
       </c>
       <c r="G12">
         <v>350</v>
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>94259.49000000001</v>
+        <v>94247.75</v>
       </c>
       <c r="C13">
         <v>1096</v>
       </c>
       <c r="D13">
-        <v>1108.97</v>
+        <v>1108.83</v>
       </c>
       <c r="E13">
-        <v>284.77</v>
+        <v>284.74</v>
       </c>
       <c r="F13">
-        <v>4271.58</v>
+        <v>4271.05</v>
       </c>
       <c r="G13">
         <v>86</v>
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>583.54</v>
+        <v>582.96</v>
       </c>
       <c r="C14">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>194.51</v>
+        <v>194.32</v>
       </c>
       <c r="F14">
-        <v>194.51</v>
+        <v>194.32</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -723,19 +723,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>156266.63</v>
+        <v>155493.42</v>
       </c>
       <c r="C15">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D15">
-        <v>494.29</v>
+        <v>491.84</v>
       </c>
       <c r="E15">
-        <v>236.41</v>
+        <v>235.24</v>
       </c>
       <c r="F15">
-        <v>5201.01</v>
+        <v>5175.27</v>
       </c>
       <c r="G15">
         <v>301</v>
@@ -748,19 +748,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>170695.73</v>
+        <v>169723.58</v>
       </c>
       <c r="C16">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D16">
-        <v>482.93</v>
+        <v>480.18</v>
       </c>
       <c r="E16">
-        <v>160.88</v>
+        <v>159.97</v>
       </c>
       <c r="F16">
-        <v>3217.64</v>
+        <v>3199.31</v>
       </c>
       <c r="G16">
         <v>357</v>
@@ -773,19 +773,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>14406.88</v>
+        <v>14220.9</v>
       </c>
       <c r="C17">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="D17">
-        <v>295.74</v>
+        <v>291.93</v>
       </c>
       <c r="E17">
-        <v>271.83</v>
+        <v>268.32</v>
       </c>
       <c r="F17">
-        <v>1359.14</v>
+        <v>1341.59</v>
       </c>
       <c r="G17">
         <v>33</v>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>17300.82</v>
+        <v>17183.34</v>
       </c>
       <c r="C18">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D18">
-        <v>286.47</v>
+        <v>284.52</v>
       </c>
       <c r="E18">
-        <v>283.62</v>
+        <v>281.69</v>
       </c>
       <c r="F18">
-        <v>1418.1</v>
+        <v>1408.47</v>
       </c>
       <c r="G18">
         <v>35</v>
@@ -823,19 +823,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>8230.629999999999</v>
+        <v>8201.43</v>
       </c>
       <c r="C19">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D19">
-        <v>201.08</v>
+        <v>200.37</v>
       </c>
       <c r="E19">
-        <v>216.6</v>
+        <v>215.83</v>
       </c>
       <c r="F19">
-        <v>866.38</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="G19">
         <v>21</v>
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>35021.74</v>
+        <v>33955.87</v>
       </c>
       <c r="C20">
-        <v>11674</v>
+        <v>11319</v>
       </c>
       <c r="D20">
-        <v>9815.469999999999</v>
+        <v>9516.75</v>
       </c>
       <c r="E20">
-        <v>625.39</v>
+        <v>606.35</v>
       </c>
       <c r="F20">
-        <v>19387.03</v>
+        <v>18797</v>
       </c>
       <c r="G20">
         <v>3</v>
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>69675.94</v>
+        <v>71304.10000000001</v>
       </c>
       <c r="C21">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D21">
-        <v>215.47</v>
+        <v>220.51</v>
       </c>
       <c r="E21">
-        <v>184.33</v>
+        <v>188.64</v>
       </c>
       <c r="F21">
-        <v>2027.61</v>
+        <v>2074.99</v>
       </c>
       <c r="G21">
         <v>268</v>
@@ -898,19 +898,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>68126.85000000001</v>
+        <v>68043.50999999999</v>
       </c>
       <c r="C22">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D22">
-        <v>88.56</v>
+        <v>88.45</v>
       </c>
       <c r="E22">
-        <v>141.93</v>
+        <v>141.76</v>
       </c>
       <c r="F22">
-        <v>709.65</v>
+        <v>708.79</v>
       </c>
       <c r="G22">
         <v>375</v>
@@ -923,19 +923,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>272850.76</v>
+        <v>267954.53</v>
       </c>
       <c r="C23">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="D23">
-        <v>559.96</v>
+        <v>549.91</v>
       </c>
       <c r="E23">
-        <v>230.06</v>
+        <v>225.93</v>
       </c>
       <c r="F23">
-        <v>3680.95</v>
+        <v>3614.9</v>
       </c>
       <c r="G23">
         <v>473</v>
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="B24">
-        <v>3335.55</v>
+        <v>3339.34</v>
       </c>
       <c r="C24">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D24">
-        <v>103.89</v>
+        <v>104</v>
       </c>
       <c r="E24">
-        <v>185.31</v>
+        <v>185.52</v>
       </c>
       <c r="F24">
-        <v>555.9299999999999</v>
+        <v>556.5599999999999</v>
       </c>
       <c r="G24">
         <v>15</v>
@@ -973,16 +973,16 @@
         </is>
       </c>
       <c r="B25">
-        <v>166.38</v>
+        <v>165.86</v>
       </c>
       <c r="C25">
         <v>166</v>
       </c>
       <c r="E25">
-        <v>166.38</v>
+        <v>165.86</v>
       </c>
       <c r="F25">
-        <v>166.38</v>
+        <v>165.86</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>2222.36</v>
+        <v>2221.54</v>
       </c>
       <c r="C26">
         <v>317</v>
       </c>
       <c r="D26">
-        <v>296.98</v>
+        <v>296.87</v>
       </c>
       <c r="E26">
-        <v>138.9</v>
+        <v>138.85</v>
       </c>
       <c r="F26">
-        <v>972.28</v>
+        <v>971.92</v>
       </c>
       <c r="G26">
         <v>7</v>
@@ -1020,19 +1020,19 @@
         </is>
       </c>
       <c r="B27">
-        <v>559264.26</v>
+        <v>520505.67</v>
       </c>
       <c r="C27">
-        <v>497</v>
+        <v>462</v>
       </c>
       <c r="D27">
-        <v>1624.71</v>
+        <v>1512.11</v>
       </c>
       <c r="E27">
-        <v>179.37</v>
+        <v>166.94</v>
       </c>
       <c r="F27">
-        <v>30492.28</v>
+        <v>28379.08</v>
       </c>
       <c r="G27">
         <v>1126</v>
@@ -1045,19 +1045,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>295754.48</v>
+        <v>291101.91</v>
       </c>
       <c r="C28">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D28">
-        <v>284.01</v>
+        <v>279.54</v>
       </c>
       <c r="E28">
-        <v>163.13</v>
+        <v>160.56</v>
       </c>
       <c r="F28">
-        <v>3262.6</v>
+        <v>3211.27</v>
       </c>
       <c r="G28">
         <v>949</v>
@@ -1070,19 +1070,19 @@
         </is>
       </c>
       <c r="B29">
-        <v>120103.32</v>
+        <v>119658.73</v>
       </c>
       <c r="C29">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D29">
-        <v>368.73</v>
+        <v>367.37</v>
       </c>
       <c r="E29">
-        <v>204.95</v>
+        <v>204.2</v>
       </c>
       <c r="F29">
-        <v>3074.32</v>
+        <v>3062.94</v>
       </c>
       <c r="G29">
         <v>269</v>
@@ -1095,19 +1095,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>292626.24</v>
+        <v>291827.09</v>
       </c>
       <c r="C30">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D30">
-        <v>741.73</v>
+        <v>739.71</v>
       </c>
       <c r="E30">
-        <v>182.89</v>
+        <v>182.39</v>
       </c>
       <c r="F30">
-        <v>6035.42</v>
+        <v>6018.93</v>
       </c>
       <c r="G30">
         <v>477</v>
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>76902.41</v>
+        <v>77432.55</v>
       </c>
       <c r="C31">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D31">
-        <v>111.14</v>
+        <v>111.9</v>
       </c>
       <c r="E31">
-        <v>102.81</v>
+        <v>103.52</v>
       </c>
       <c r="F31">
-        <v>1130.92</v>
+        <v>1138.71</v>
       </c>
       <c r="G31">
         <v>502</v>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>7714.61</v>
+        <v>7804.58</v>
       </c>
       <c r="C32">
-        <v>1102</v>
+        <v>1115</v>
       </c>
       <c r="D32">
-        <v>975.3099999999999</v>
+        <v>986.6799999999999</v>
       </c>
       <c r="E32">
-        <v>453.8</v>
+        <v>459.09</v>
       </c>
       <c r="F32">
-        <v>3176.6</v>
+        <v>3213.65</v>
       </c>
       <c r="G32">
         <v>7</v>
@@ -1170,19 +1170,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>26846.86</v>
+        <v>26820.99</v>
       </c>
       <c r="C33">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D33">
-        <v>215.01</v>
+        <v>214.8</v>
       </c>
       <c r="E33">
-        <v>186.44</v>
+        <v>186.26</v>
       </c>
       <c r="F33">
-        <v>932.1799999999999</v>
+        <v>931.28</v>
       </c>
       <c r="G33">
         <v>70</v>
@@ -1195,19 +1195,19 @@
         </is>
       </c>
       <c r="B34">
-        <v>184867.16</v>
+        <v>183778.68</v>
       </c>
       <c r="C34">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D34">
-        <v>1039.43</v>
+        <v>1033.31</v>
       </c>
       <c r="E34">
-        <v>199</v>
+        <v>197.82</v>
       </c>
       <c r="F34">
-        <v>10944.77</v>
+        <v>10880.33</v>
       </c>
       <c r="G34">
         <v>268</v>
@@ -1220,16 +1220,16 @@
         </is>
       </c>
       <c r="B35">
-        <v>408.86</v>
+        <v>409.78</v>
       </c>
       <c r="C35">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E35">
-        <v>408.86</v>
+        <v>409.78</v>
       </c>
       <c r="F35">
-        <v>408.86</v>
+        <v>409.78</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -1242,19 +1242,19 @@
         </is>
       </c>
       <c r="B36">
-        <v>5320.18</v>
+        <v>5301.46</v>
       </c>
       <c r="C36">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>532.02</v>
+        <v>530.15</v>
       </c>
       <c r="F36">
-        <v>532.02</v>
+        <v>530.15</v>
       </c>
       <c r="G36">
         <v>10</v>
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="B37">
-        <v>10513.33</v>
+        <v>10605.04</v>
       </c>
       <c r="C37">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D37">
-        <v>405.86</v>
+        <v>409.4</v>
       </c>
       <c r="E37">
-        <v>223.69</v>
+        <v>225.64</v>
       </c>
       <c r="F37">
-        <v>1565.82</v>
+        <v>1579.47</v>
       </c>
       <c r="G37">
         <v>20</v>
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="B38">
-        <v>381130.3</v>
+        <v>382280.83</v>
       </c>
       <c r="C38">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="D38">
-        <v>1713.49</v>
+        <v>1718.66</v>
       </c>
       <c r="E38">
-        <v>276.58</v>
+        <v>277.42</v>
       </c>
       <c r="F38">
-        <v>17701.26</v>
+        <v>17754.7</v>
       </c>
       <c r="G38">
         <v>318</v>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="B39">
-        <v>52560.7</v>
+        <v>51480.52</v>
       </c>
       <c r="C39">
-        <v>1546</v>
+        <v>1514</v>
       </c>
       <c r="D39">
-        <v>3087.01</v>
+        <v>3023.57</v>
       </c>
       <c r="E39">
-        <v>247.93</v>
+        <v>242.83</v>
       </c>
       <c r="F39">
-        <v>16611.17</v>
+        <v>16269.79</v>
       </c>
       <c r="G39">
         <v>34</v>
@@ -1342,19 +1342,19 @@
         </is>
       </c>
       <c r="B40">
-        <v>13183.51</v>
+        <v>13163.12</v>
       </c>
       <c r="C40">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="D40">
-        <v>901.47</v>
+        <v>900.08</v>
       </c>
       <c r="E40">
-        <v>411.98</v>
+        <v>411.35</v>
       </c>
       <c r="F40">
-        <v>2883.89</v>
+        <v>2879.43</v>
       </c>
       <c r="G40">
         <v>12</v>
@@ -1367,19 +1367,19 @@
         </is>
       </c>
       <c r="B41">
-        <v>160654.72</v>
+        <v>231260.69</v>
       </c>
       <c r="C41">
-        <v>956</v>
+        <v>1377</v>
       </c>
       <c r="D41">
-        <v>1617.99</v>
+        <v>2329.09</v>
       </c>
       <c r="E41">
-        <v>71.78</v>
+        <v>103.33</v>
       </c>
       <c r="F41">
-        <v>10624.17</v>
+        <v>15293.38</v>
       </c>
       <c r="G41">
         <v>168</v>
@@ -1392,19 +1392,19 @@
         </is>
       </c>
       <c r="B42">
-        <v>717043.51</v>
+        <v>719196.0699999999</v>
       </c>
       <c r="C42">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D42">
-        <v>341.51</v>
+        <v>342.53</v>
       </c>
       <c r="E42">
-        <v>166.41</v>
+        <v>166.91</v>
       </c>
       <c r="F42">
-        <v>4825.77</v>
+        <v>4840.26</v>
       </c>
       <c r="G42">
         <v>2015</v>
@@ -1417,19 +1417,19 @@
         </is>
       </c>
       <c r="B43">
-        <v>798.98</v>
+        <v>352.81</v>
       </c>
       <c r="C43">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="D43">
-        <v>62.86</v>
+        <v>27.76</v>
       </c>
       <c r="E43">
-        <v>79.90000000000001</v>
+        <v>35.28</v>
       </c>
       <c r="F43">
-        <v>239.69</v>
+        <v>105.84</v>
       </c>
       <c r="G43">
         <v>7</v>
@@ -1442,19 +1442,19 @@
         </is>
       </c>
       <c r="B44">
-        <v>10826.9</v>
+        <v>10923.34</v>
       </c>
       <c r="C44">
-        <v>1083</v>
+        <v>1092</v>
       </c>
       <c r="D44">
-        <v>838.49</v>
+        <v>845.96</v>
       </c>
       <c r="E44">
-        <v>318.44</v>
+        <v>321.27</v>
       </c>
       <c r="F44">
-        <v>3184.38</v>
+        <v>3212.75</v>
       </c>
       <c r="G44">
         <v>10</v>
@@ -1467,19 +1467,19 @@
         </is>
       </c>
       <c r="B45">
-        <v>214282.4</v>
+        <v>211077.88</v>
       </c>
       <c r="C45">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="D45">
-        <v>840.8</v>
+        <v>828.22</v>
       </c>
       <c r="E45">
-        <v>72</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="F45">
-        <v>3888.19</v>
+        <v>3830.04</v>
       </c>
       <c r="G45">
         <v>298</v>
@@ -1492,16 +1492,16 @@
         </is>
       </c>
       <c r="B46">
-        <v>846.66</v>
+        <v>856.37</v>
       </c>
       <c r="C46">
-        <v>847</v>
+        <v>856</v>
       </c>
       <c r="E46">
-        <v>846.66</v>
+        <v>856.37</v>
       </c>
       <c r="F46">
-        <v>846.66</v>
+        <v>856.37</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B47">
-        <v>11906.01</v>
+        <v>11760.13</v>
       </c>
       <c r="C47">
-        <v>1191</v>
+        <v>1176</v>
       </c>
       <c r="D47">
-        <v>901.75</v>
+        <v>890.7</v>
       </c>
       <c r="E47">
-        <v>114.48</v>
+        <v>113.08</v>
       </c>
       <c r="F47">
-        <v>2862.02</v>
+        <v>2826.95</v>
       </c>
       <c r="G47">
         <v>10</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B48">
-        <v>23590.39</v>
+        <v>23447.8</v>
       </c>
       <c r="C48">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D48">
-        <v>238.94</v>
+        <v>237.49</v>
       </c>
       <c r="E48">
-        <v>314.54</v>
+        <v>312.64</v>
       </c>
       <c r="F48">
-        <v>1887.23</v>
+        <v>1875.82</v>
       </c>
       <c r="G48">
         <v>57</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B49">
-        <v>41758.2</v>
+        <v>41796.14</v>
       </c>
       <c r="C49">
         <v>360</v>
       </c>
       <c r="D49">
-        <v>150.28</v>
+        <v>150.42</v>
       </c>
       <c r="E49">
-        <v>296.16</v>
+        <v>296.43</v>
       </c>
       <c r="F49">
-        <v>1184.63</v>
+        <v>1185.71</v>
       </c>
       <c r="G49">
         <v>116</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B50">
-        <v>450026.81</v>
+        <v>447710.52</v>
       </c>
       <c r="C50">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D50">
-        <v>664.47</v>
+        <v>661.05</v>
       </c>
       <c r="E50">
-        <v>158.74</v>
+        <v>157.92</v>
       </c>
       <c r="F50">
-        <v>10953.03</v>
+        <v>10896.66</v>
       </c>
       <c r="G50">
         <v>1118</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B51">
-        <v>1344.46</v>
+        <v>1350.48</v>
       </c>
       <c r="C51">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="D51">
-        <v>633.78</v>
+        <v>636.62</v>
       </c>
       <c r="E51">
-        <v>224.08</v>
+        <v>225.08</v>
       </c>
       <c r="F51">
-        <v>1120.38</v>
+        <v>1125.4</v>
       </c>
       <c r="G51">
         <v>2</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B52">
-        <v>32320.77</v>
+        <v>32415.8</v>
       </c>
       <c r="C52">
         <v>259</v>
       </c>
       <c r="D52">
-        <v>217.39</v>
+        <v>218.03</v>
       </c>
       <c r="E52">
-        <v>143.65</v>
+        <v>144.07</v>
       </c>
       <c r="F52">
-        <v>1436.48</v>
+        <v>1440.7</v>
       </c>
       <c r="G52">
         <v>125</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B53">
-        <v>792.04</v>
+        <v>744.8099999999999</v>
       </c>
       <c r="C53">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D53">
-        <v>95.92</v>
+        <v>90.2</v>
       </c>
       <c r="E53">
-        <v>79.2</v>
+        <v>74.48</v>
       </c>
       <c r="F53">
-        <v>316.82</v>
+        <v>297.92</v>
       </c>
       <c r="G53">
         <v>6</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B55">
-        <v>17361.07</v>
+        <v>17370.92</v>
       </c>
       <c r="C55">
         <v>668</v>
       </c>
       <c r="D55">
-        <v>629.63</v>
+        <v>629.99</v>
       </c>
       <c r="E55">
-        <v>299.33</v>
+        <v>299.5</v>
       </c>
       <c r="F55">
-        <v>2394.63</v>
+        <v>2395.99</v>
       </c>
       <c r="G55">
         <v>26</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B56">
-        <v>695.9</v>
+        <v>674.33</v>
       </c>
       <c r="C56">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>231.97</v>
+        <v>224.78</v>
       </c>
       <c r="F56">
-        <v>231.97</v>
+        <v>224.78</v>
       </c>
       <c r="G56">
         <v>3</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B57">
-        <v>3699.53</v>
+        <v>3575.6</v>
       </c>
       <c r="C57">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="D57">
-        <v>393.17</v>
+        <v>380</v>
       </c>
       <c r="E57">
-        <v>336.32</v>
+        <v>325.05</v>
       </c>
       <c r="F57">
-        <v>1345.29</v>
+        <v>1300.22</v>
       </c>
       <c r="G57">
         <v>6</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B58">
-        <v>192899.99</v>
+        <v>192077.17</v>
       </c>
       <c r="C58">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="D58">
-        <v>832.38</v>
+        <v>828.83</v>
       </c>
       <c r="E58">
-        <v>201.15</v>
+        <v>200.29</v>
       </c>
       <c r="F58">
-        <v>5430.97</v>
+        <v>5407.8</v>
       </c>
       <c r="G58">
         <v>259</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B59">
-        <v>57774.33</v>
+        <v>57426.62</v>
       </c>
       <c r="C59">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="D59">
-        <v>1340.38</v>
+        <v>1332.31</v>
       </c>
       <c r="E59">
-        <v>193.87</v>
+        <v>192.71</v>
       </c>
       <c r="F59">
-        <v>9499.809999999999</v>
+        <v>9442.629999999999</v>
       </c>
       <c r="G59">
         <v>73</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B60">
-        <v>5864</v>
+        <v>5704.43</v>
       </c>
       <c r="C60">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D60">
-        <v>156.1</v>
+        <v>151.86</v>
       </c>
       <c r="E60">
-        <v>106.62</v>
+        <v>103.72</v>
       </c>
       <c r="F60">
-        <v>852.95</v>
+        <v>829.74</v>
       </c>
       <c r="G60">
         <v>30</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B61">
-        <v>404954.85</v>
+        <v>397110.78</v>
       </c>
       <c r="C61">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="D61">
-        <v>544.58</v>
+        <v>534.03</v>
       </c>
       <c r="E61">
-        <v>238.21</v>
+        <v>233.59</v>
       </c>
       <c r="F61">
-        <v>6193.43</v>
+        <v>6073.46</v>
       </c>
       <c r="G61">
         <v>762</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B62">
-        <v>980527.4</v>
+        <v>947981.14</v>
       </c>
       <c r="C62">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="D62">
-        <v>537.88</v>
+        <v>520.03</v>
       </c>
       <c r="E62">
-        <v>187.27</v>
+        <v>181.05</v>
       </c>
       <c r="F62">
-        <v>10861.46</v>
+        <v>10500.94</v>
       </c>
       <c r="G62">
         <v>2194</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B63">
-        <v>611.47</v>
+        <v>607.53</v>
       </c>
       <c r="C63">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>305.73</v>
+        <v>303.77</v>
       </c>
       <c r="F63">
-        <v>305.73</v>
+        <v>303.77</v>
       </c>
       <c r="G63">
         <v>2</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B64">
-        <v>1177878.03</v>
+        <v>1173174.1</v>
       </c>
       <c r="C64">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="D64">
-        <v>1559.01</v>
+        <v>1552.78</v>
       </c>
       <c r="E64">
-        <v>367.17</v>
+        <v>365.7</v>
       </c>
       <c r="F64">
-        <v>33779.54</v>
+        <v>33644.64</v>
       </c>
       <c r="G64">
         <v>1345</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B65">
-        <v>20640.2</v>
+        <v>20327.39</v>
       </c>
       <c r="C65">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D65">
-        <v>338.19</v>
+        <v>333.07</v>
       </c>
       <c r="E65">
-        <v>158.77</v>
+        <v>156.36</v>
       </c>
       <c r="F65">
-        <v>2064.02</v>
+        <v>2032.74</v>
       </c>
       <c r="G65">
         <v>58</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B66">
-        <v>10987.59</v>
+        <v>10990.1</v>
       </c>
       <c r="C66">
         <v>193</v>
       </c>
       <c r="D66">
-        <v>335.72</v>
+        <v>335.8</v>
       </c>
       <c r="E66">
-        <v>87.90000000000001</v>
+        <v>87.92</v>
       </c>
       <c r="F66">
-        <v>2549.12</v>
+        <v>2549.7</v>
       </c>
       <c r="G66">
         <v>57</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B67">
-        <v>395483.87</v>
+        <v>393881</v>
       </c>
       <c r="C67">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D67">
-        <v>356.74</v>
+        <v>355.29</v>
       </c>
       <c r="E67">
-        <v>196.17</v>
+        <v>195.38</v>
       </c>
       <c r="F67">
-        <v>4315.8</v>
+        <v>4298.3</v>
       </c>
       <c r="G67">
         <v>904</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B68">
-        <v>37797.36</v>
+        <v>37740.56</v>
       </c>
       <c r="C68">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D68">
-        <v>314.54</v>
+        <v>314.07</v>
       </c>
       <c r="E68">
-        <v>189.94</v>
+        <v>189.65</v>
       </c>
       <c r="F68">
-        <v>2659.11</v>
+        <v>2655.11</v>
       </c>
       <c r="G68">
         <v>115</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B69">
-        <v>2680196.17</v>
+        <v>2682393.17</v>
       </c>
       <c r="C69">
         <v>501</v>
       </c>
       <c r="D69">
-        <v>515.77</v>
+        <v>516.1900000000001</v>
       </c>
       <c r="E69">
-        <v>101.2</v>
+        <v>101.28</v>
       </c>
       <c r="F69">
-        <v>11030.45</v>
+        <v>11039.49</v>
       </c>
       <c r="G69">
         <v>5351</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B70">
-        <v>373419.3</v>
+        <v>373437.21</v>
       </c>
       <c r="C70">
         <v>606</v>
       </c>
       <c r="D70">
-        <v>926.21</v>
+        <v>926.26</v>
       </c>
       <c r="E70">
         <v>135.94</v>
       </c>
       <c r="F70">
-        <v>11418.72</v>
+        <v>11419.27</v>
       </c>
       <c r="G70">
         <v>616</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B71">
-        <v>154418.29</v>
+        <v>155776.46</v>
       </c>
       <c r="C71">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D71">
-        <v>465.04</v>
+        <v>469.13</v>
       </c>
       <c r="E71">
-        <v>102.33</v>
+        <v>103.23</v>
       </c>
       <c r="F71">
-        <v>3274.61</v>
+        <v>3303.41</v>
       </c>
       <c r="G71">
         <v>372</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B72">
-        <v>81786.95</v>
+        <v>82582.75999999999</v>
       </c>
       <c r="C72">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D72">
-        <v>458.86</v>
+        <v>463.32</v>
       </c>
       <c r="E72">
-        <v>131.49</v>
+        <v>132.77</v>
       </c>
       <c r="F72">
-        <v>4996.63</v>
+        <v>5045.25</v>
       </c>
       <c r="G72">
         <v>229</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B73">
-        <v>33580.08</v>
+        <v>33557.94</v>
       </c>
       <c r="C73">
         <v>189</v>
       </c>
       <c r="D73">
-        <v>134.08</v>
+        <v>133.99</v>
       </c>
       <c r="E73">
-        <v>102.38</v>
+        <v>102.31</v>
       </c>
       <c r="F73">
-        <v>819.03</v>
+        <v>818.49</v>
       </c>
       <c r="G73">
         <v>178</v>
@@ -2189,19 +2189,19 @@
         </is>
       </c>
       <c r="B74">
-        <v>27266.99</v>
+        <v>27277.24</v>
       </c>
       <c r="C74">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="D74">
-        <v>2161.01</v>
+        <v>2161.82</v>
       </c>
       <c r="E74">
-        <v>281.1</v>
+        <v>281.21</v>
       </c>
       <c r="F74">
-        <v>9838.6</v>
+        <v>9842.299999999999</v>
       </c>
       <c r="G74">
         <v>19</v>
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="B75">
-        <v>683.75</v>
+        <v>685.05</v>
       </c>
       <c r="C75">
         <v>171</v>
       </c>
       <c r="D75">
-        <v>65.79000000000001</v>
+        <v>65.92</v>
       </c>
       <c r="E75">
-        <v>113.96</v>
+        <v>114.18</v>
       </c>
       <c r="F75">
-        <v>227.92</v>
+        <v>228.35</v>
       </c>
       <c r="G75">
         <v>4</v>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="B76">
-        <v>91235.21000000001</v>
+        <v>90469.87</v>
       </c>
       <c r="C76">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D76">
-        <v>283.55</v>
+        <v>281.17</v>
       </c>
       <c r="E76">
-        <v>189.68</v>
+        <v>188.09</v>
       </c>
       <c r="F76">
-        <v>2276.14</v>
+        <v>2257.04</v>
       </c>
       <c r="G76">
         <v>252</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B77">
-        <v>7136.12</v>
+        <v>7057.45</v>
       </c>
       <c r="C77">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D77">
-        <v>118.99</v>
+        <v>117.68</v>
       </c>
       <c r="E77">
-        <v>132.15</v>
+        <v>130.69</v>
       </c>
       <c r="F77">
-        <v>528.6</v>
+        <v>522.77</v>
       </c>
       <c r="G77">
         <v>37</v>
@@ -2289,19 +2289,19 @@
         </is>
       </c>
       <c r="B78">
-        <v>7579.3</v>
+        <v>7489.88</v>
       </c>
       <c r="C78">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D78">
-        <v>409.02</v>
+        <v>404.19</v>
       </c>
       <c r="E78">
-        <v>172.26</v>
+        <v>170.22</v>
       </c>
       <c r="F78">
-        <v>1550.31</v>
+        <v>1532.02</v>
       </c>
       <c r="G78">
         <v>15</v>
@@ -2339,16 +2339,16 @@
         </is>
       </c>
       <c r="B80">
-        <v>1422.12</v>
+        <v>1421.85</v>
       </c>
       <c r="C80">
         <v>1422</v>
       </c>
       <c r="E80">
-        <v>1422.12</v>
+        <v>1421.85</v>
       </c>
       <c r="F80">
-        <v>1422.12</v>
+        <v>1421.85</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -2361,19 +2361,19 @@
         </is>
       </c>
       <c r="B81">
-        <v>3395.42</v>
+        <v>3366.95</v>
       </c>
       <c r="C81">
-        <v>1132</v>
+        <v>1122</v>
       </c>
       <c r="D81">
-        <v>980.17</v>
+        <v>971.95</v>
       </c>
       <c r="E81">
-        <v>565.9</v>
+        <v>561.16</v>
       </c>
       <c r="F81">
-        <v>2263.61</v>
+        <v>2244.63</v>
       </c>
       <c r="G81">
         <v>3</v>
@@ -2386,19 +2386,19 @@
         </is>
       </c>
       <c r="B82">
-        <v>405735.49</v>
+        <v>410097.54</v>
       </c>
       <c r="C82">
-        <v>874</v>
+        <v>884</v>
       </c>
       <c r="D82">
-        <v>1577.48</v>
+        <v>1594.44</v>
       </c>
       <c r="E82">
-        <v>285.33</v>
+        <v>288.39</v>
       </c>
       <c r="F82">
-        <v>18260.95</v>
+        <v>18457.27</v>
       </c>
       <c r="G82">
         <v>464</v>
@@ -2411,19 +2411,19 @@
         </is>
       </c>
       <c r="B83">
-        <v>24871.78</v>
+        <v>24796.68</v>
       </c>
       <c r="C83">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="D83">
-        <v>966.03</v>
+        <v>963.12</v>
       </c>
       <c r="E83">
-        <v>282.63</v>
+        <v>281.78</v>
       </c>
       <c r="F83">
-        <v>3956.87</v>
+        <v>3944.93</v>
       </c>
       <c r="G83">
         <v>28</v>
@@ -2436,19 +2436,19 @@
         </is>
       </c>
       <c r="B84">
-        <v>93787.3</v>
+        <v>92337.11</v>
       </c>
       <c r="C84">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D84">
-        <v>1057.97</v>
+        <v>1041.61</v>
       </c>
       <c r="E84">
-        <v>160.05</v>
+        <v>157.57</v>
       </c>
       <c r="F84">
-        <v>6241.82</v>
+        <v>6145.3</v>
       </c>
       <c r="G84">
         <v>133</v>
@@ -2461,19 +2461,19 @@
         </is>
       </c>
       <c r="B85">
-        <v>25446.39</v>
+        <v>24923.12</v>
       </c>
       <c r="C85">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D85">
-        <v>37.29</v>
+        <v>36.52</v>
       </c>
       <c r="E85">
-        <v>139.05</v>
+        <v>136.19</v>
       </c>
       <c r="F85">
-        <v>417.15</v>
+        <v>408.58</v>
       </c>
       <c r="G85">
         <v>172</v>
@@ -2486,19 +2486,19 @@
         </is>
       </c>
       <c r="B86">
-        <v>227759.72</v>
+        <v>219933.17</v>
       </c>
       <c r="C86">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D86">
-        <v>72.56</v>
+        <v>70.06</v>
       </c>
       <c r="E86">
-        <v>39.97</v>
+        <v>38.6</v>
       </c>
       <c r="F86">
-        <v>1638.85</v>
+        <v>1582.53</v>
       </c>
       <c r="G86">
         <v>2933</v>
@@ -2511,19 +2511,19 @@
         </is>
       </c>
       <c r="B87">
-        <v>9491.58</v>
+        <v>9220.610000000001</v>
       </c>
       <c r="C87">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="D87">
-        <v>171.07</v>
+        <v>166.19</v>
       </c>
       <c r="E87">
-        <v>93.98</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="F87">
-        <v>657.83</v>
+        <v>639.05</v>
       </c>
       <c r="G87">
         <v>37</v>
@@ -2536,19 +2536,19 @@
         </is>
       </c>
       <c r="B88">
-        <v>219717.54</v>
+        <v>219386.77</v>
       </c>
       <c r="C88">
         <v>279</v>
       </c>
       <c r="D88">
-        <v>209.25</v>
+        <v>208.93</v>
       </c>
       <c r="E88">
-        <v>116.68</v>
+        <v>116.51</v>
       </c>
       <c r="F88">
-        <v>2450.38</v>
+        <v>2446.69</v>
       </c>
       <c r="G88">
         <v>787</v>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_costs_by_tretspef-Users_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_costs_by_tretspef-Users_OMOP.xlsx
@@ -2314,19 +2314,19 @@
         </is>
       </c>
       <c r="B79">
-        <v>64.39</v>
+        <v>4301.37</v>
       </c>
       <c r="C79">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>180.72</v>
       </c>
       <c r="E79">
         <v>12.88</v>
       </c>
       <c r="F79">
-        <v>12.88</v>
+        <v>888.61</v>
       </c>
       <c r="G79">
         <v>41</v>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_costs_by_tretspef-Users_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_costs_by_tretspef-Users_OMOP.xlsx
@@ -398,19 +398,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>346287.5</v>
+        <v>333588.15</v>
       </c>
       <c r="C2">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="D2">
-        <v>321.36</v>
+        <v>309.57</v>
       </c>
       <c r="E2">
-        <v>180.08</v>
+        <v>173.47</v>
       </c>
       <c r="F2">
-        <v>4862.07</v>
+        <v>4683.76</v>
       </c>
       <c r="G2">
         <v>1062</v>
@@ -423,19 +423,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>357036.97</v>
+        <v>362016.53</v>
       </c>
       <c r="C3">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D3">
-        <v>334.06</v>
+        <v>337.9</v>
       </c>
       <c r="E3">
-        <v>150.77</v>
+        <v>149.62</v>
       </c>
       <c r="F3">
-        <v>4475.13</v>
+        <v>4640.78</v>
       </c>
       <c r="G3">
         <v>1043</v>
@@ -448,19 +448,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>14192.67</v>
+        <v>13648.22</v>
       </c>
       <c r="C4">
-        <v>1183</v>
+        <v>1137</v>
       </c>
       <c r="D4">
-        <v>1128.55</v>
+        <v>1085.26</v>
       </c>
       <c r="E4">
-        <v>346.16</v>
+        <v>332.88</v>
       </c>
       <c r="F4">
-        <v>3115.46</v>
+        <v>2995.95</v>
       </c>
       <c r="G4">
         <v>12</v>
@@ -473,19 +473,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>121465.09</v>
+        <v>126749.25</v>
       </c>
       <c r="C5">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="D5">
-        <v>200.53</v>
+        <v>209.26</v>
       </c>
       <c r="E5">
-        <v>146.87</v>
+        <v>153.26</v>
       </c>
       <c r="F5">
-        <v>2643.74</v>
+        <v>2758.75</v>
       </c>
       <c r="G5">
         <v>545</v>
@@ -498,19 +498,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>14879.43</v>
+        <v>15165.32</v>
       </c>
       <c r="C6">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="D6">
-        <v>344.5</v>
+        <v>351.12</v>
       </c>
       <c r="E6">
-        <v>232.49</v>
+        <v>236.96</v>
       </c>
       <c r="F6">
-        <v>1394.95</v>
+        <v>1421.75</v>
       </c>
       <c r="G6">
         <v>31</v>
@@ -523,19 +523,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>25946.11</v>
+        <v>25694.87</v>
       </c>
       <c r="C7">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D7">
-        <v>205.38</v>
+        <v>203.39</v>
       </c>
       <c r="E7">
-        <v>184.01</v>
+        <v>182.23</v>
       </c>
       <c r="F7">
-        <v>1472.12</v>
+        <v>1457.87</v>
       </c>
       <c r="G7">
         <v>89</v>
@@ -548,19 +548,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>124647.52</v>
+        <v>118884.78</v>
       </c>
       <c r="C8">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="D8">
-        <v>305.75</v>
+        <v>291.61</v>
       </c>
       <c r="E8">
-        <v>196.6</v>
+        <v>187.52</v>
       </c>
       <c r="F8">
-        <v>2359.26</v>
+        <v>2250.19</v>
       </c>
       <c r="G8">
         <v>344</v>
@@ -573,19 +573,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>76574.84</v>
+        <v>79482.73</v>
       </c>
       <c r="C9">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="D9">
-        <v>404.35</v>
+        <v>419.7</v>
       </c>
       <c r="E9">
-        <v>190.96</v>
+        <v>198.21</v>
       </c>
       <c r="F9">
-        <v>2864.4</v>
+        <v>2973.17</v>
       </c>
       <c r="G9">
         <v>175</v>
@@ -598,19 +598,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>10560597.94</v>
+        <v>10575945.53</v>
       </c>
       <c r="C10">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D10">
-        <v>693.95</v>
+        <v>694.95</v>
       </c>
       <c r="E10">
-        <v>166.27</v>
+        <v>166.51</v>
       </c>
       <c r="F10">
-        <v>33420.67</v>
+        <v>33469.24</v>
       </c>
       <c r="G10">
         <v>17426</v>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>1639488.7</v>
+        <v>1755825.96</v>
       </c>
       <c r="C11">
-        <v>496</v>
+        <v>531</v>
       </c>
       <c r="D11">
-        <v>571.6</v>
+        <v>612.16</v>
       </c>
       <c r="E11">
-        <v>139.77</v>
+        <v>149.69</v>
       </c>
       <c r="F11">
-        <v>5590.75</v>
+        <v>5987.47</v>
       </c>
       <c r="G11">
         <v>3308</v>
@@ -648,19 +648,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>137196.29</v>
+        <v>147842.09</v>
       </c>
       <c r="C12">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="D12">
-        <v>290.56</v>
+        <v>313.11</v>
       </c>
       <c r="E12">
-        <v>203.25</v>
+        <v>219.03</v>
       </c>
       <c r="F12">
-        <v>2642.3</v>
+        <v>2847.33</v>
       </c>
       <c r="G12">
         <v>350</v>
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>94247.75</v>
+        <v>102574.71</v>
       </c>
       <c r="C13">
-        <v>1096</v>
+        <v>1193</v>
       </c>
       <c r="D13">
-        <v>1108.83</v>
+        <v>1206.8</v>
       </c>
       <c r="E13">
-        <v>284.74</v>
+        <v>309.89</v>
       </c>
       <c r="F13">
-        <v>4271.05</v>
+        <v>4648.4</v>
       </c>
       <c r="G13">
         <v>86</v>
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>582.96</v>
+        <v>647.3200000000001</v>
       </c>
       <c r="C14">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>194.32</v>
+        <v>215.77</v>
       </c>
       <c r="F14">
-        <v>194.32</v>
+        <v>215.77</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -723,19 +723,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>155493.42</v>
+        <v>143525.49</v>
       </c>
       <c r="C15">
-        <v>517</v>
+        <v>477</v>
       </c>
       <c r="D15">
-        <v>491.84</v>
+        <v>453.98</v>
       </c>
       <c r="E15">
-        <v>235.24</v>
+        <v>217.13</v>
       </c>
       <c r="F15">
-        <v>5175.27</v>
+        <v>4776.95</v>
       </c>
       <c r="G15">
         <v>301</v>
@@ -748,19 +748,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>169723.58</v>
+        <v>173178.68</v>
       </c>
       <c r="C16">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="D16">
-        <v>480.18</v>
+        <v>489.95</v>
       </c>
       <c r="E16">
-        <v>159.97</v>
+        <v>163.22</v>
       </c>
       <c r="F16">
-        <v>3199.31</v>
+        <v>3264.44</v>
       </c>
       <c r="G16">
         <v>357</v>
@@ -773,19 +773,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>14220.9</v>
+        <v>16243.37</v>
       </c>
       <c r="C17">
-        <v>431</v>
+        <v>492</v>
       </c>
       <c r="D17">
-        <v>291.93</v>
+        <v>333.44</v>
       </c>
       <c r="E17">
-        <v>268.32</v>
+        <v>306.48</v>
       </c>
       <c r="F17">
-        <v>1341.59</v>
+        <v>1532.39</v>
       </c>
       <c r="G17">
         <v>33</v>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>17183.34</v>
+        <v>16616.76</v>
       </c>
       <c r="C18">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="D18">
-        <v>284.52</v>
+        <v>275.14</v>
       </c>
       <c r="E18">
-        <v>281.69</v>
+        <v>272.41</v>
       </c>
       <c r="F18">
-        <v>1408.47</v>
+        <v>1362.03</v>
       </c>
       <c r="G18">
         <v>35</v>
@@ -823,19 +823,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>8201.43</v>
+        <v>8521.469999999999</v>
       </c>
       <c r="C19">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="D19">
-        <v>200.37</v>
+        <v>208.19</v>
       </c>
       <c r="E19">
-        <v>215.83</v>
+        <v>224.25</v>
       </c>
       <c r="F19">
-        <v>863.3099999999999</v>
+        <v>897</v>
       </c>
       <c r="G19">
         <v>21</v>
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>33955.87</v>
+        <v>30273.54</v>
       </c>
       <c r="C20">
-        <v>11319</v>
+        <v>10091</v>
       </c>
       <c r="D20">
-        <v>9516.75</v>
+        <v>8484.709999999999</v>
       </c>
       <c r="E20">
-        <v>606.35</v>
+        <v>540.6</v>
       </c>
       <c r="F20">
-        <v>18797</v>
+        <v>16758.57</v>
       </c>
       <c r="G20">
         <v>3</v>
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>71304.10000000001</v>
+        <v>55300.41</v>
       </c>
       <c r="C21">
-        <v>266</v>
+        <v>206</v>
       </c>
       <c r="D21">
-        <v>220.51</v>
+        <v>171.02</v>
       </c>
       <c r="E21">
-        <v>188.64</v>
+        <v>146.3</v>
       </c>
       <c r="F21">
-        <v>2074.99</v>
+        <v>1609.27</v>
       </c>
       <c r="G21">
         <v>268</v>
@@ -898,19 +898,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>68043.50999999999</v>
+        <v>72269.62</v>
       </c>
       <c r="C22">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D22">
-        <v>88.45</v>
+        <v>93.94</v>
       </c>
       <c r="E22">
-        <v>141.76</v>
+        <v>150.56</v>
       </c>
       <c r="F22">
-        <v>708.79</v>
+        <v>752.8099999999999</v>
       </c>
       <c r="G22">
         <v>375</v>
@@ -923,19 +923,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>267954.53</v>
+        <v>260631.76</v>
       </c>
       <c r="C23">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="D23">
-        <v>549.91</v>
+        <v>534.88</v>
       </c>
       <c r="E23">
-        <v>225.93</v>
+        <v>219.76</v>
       </c>
       <c r="F23">
-        <v>3614.9</v>
+        <v>3516.11</v>
       </c>
       <c r="G23">
         <v>473</v>
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="B24">
-        <v>3339.34</v>
+        <v>3637.93</v>
       </c>
       <c r="C24">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="D24">
-        <v>104</v>
+        <v>113.3</v>
       </c>
       <c r="E24">
-        <v>185.52</v>
+        <v>202.11</v>
       </c>
       <c r="F24">
-        <v>556.5599999999999</v>
+        <v>606.3200000000001</v>
       </c>
       <c r="G24">
         <v>15</v>
@@ -973,16 +973,16 @@
         </is>
       </c>
       <c r="B25">
-        <v>165.86</v>
+        <v>168.99</v>
       </c>
       <c r="C25">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E25">
-        <v>165.86</v>
+        <v>168.99</v>
       </c>
       <c r="F25">
-        <v>165.86</v>
+        <v>168.99</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>2221.54</v>
+        <v>2505</v>
       </c>
       <c r="C26">
-        <v>317</v>
+        <v>358</v>
       </c>
       <c r="D26">
-        <v>296.87</v>
+        <v>334.74</v>
       </c>
       <c r="E26">
-        <v>138.85</v>
+        <v>156.56</v>
       </c>
       <c r="F26">
-        <v>971.92</v>
+        <v>1095.94</v>
       </c>
       <c r="G26">
         <v>7</v>
@@ -1020,19 +1020,19 @@
         </is>
       </c>
       <c r="B27">
-        <v>520505.67</v>
+        <v>519003.32</v>
       </c>
       <c r="C27">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D27">
-        <v>1512.11</v>
+        <v>1507.75</v>
       </c>
       <c r="E27">
-        <v>166.94</v>
+        <v>166.45</v>
       </c>
       <c r="F27">
-        <v>28379.08</v>
+        <v>28297.17</v>
       </c>
       <c r="G27">
         <v>1126</v>
@@ -1045,19 +1045,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>291101.91</v>
+        <v>311605.05</v>
       </c>
       <c r="C28">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="D28">
-        <v>279.54</v>
+        <v>299.23</v>
       </c>
       <c r="E28">
-        <v>160.56</v>
+        <v>171.87</v>
       </c>
       <c r="F28">
-        <v>3211.27</v>
+        <v>3437.45</v>
       </c>
       <c r="G28">
         <v>949</v>
@@ -1070,19 +1070,19 @@
         </is>
       </c>
       <c r="B29">
-        <v>119658.73</v>
+        <v>125108.89</v>
       </c>
       <c r="C29">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="D29">
-        <v>367.37</v>
+        <v>384.1</v>
       </c>
       <c r="E29">
-        <v>204.2</v>
+        <v>213.5</v>
       </c>
       <c r="F29">
-        <v>3062.94</v>
+        <v>3202.45</v>
       </c>
       <c r="G29">
         <v>269</v>
@@ -1095,19 +1095,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>291827.09</v>
+        <v>303949.98</v>
       </c>
       <c r="C30">
-        <v>612</v>
+        <v>637</v>
       </c>
       <c r="D30">
-        <v>739.71</v>
+        <v>770.4299999999999</v>
       </c>
       <c r="E30">
-        <v>182.39</v>
+        <v>189.97</v>
       </c>
       <c r="F30">
-        <v>6018.93</v>
+        <v>6268.97</v>
       </c>
       <c r="G30">
         <v>477</v>
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>77432.55</v>
+        <v>67310.17</v>
       </c>
       <c r="C31">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="D31">
-        <v>111.9</v>
+        <v>97.28</v>
       </c>
       <c r="E31">
-        <v>103.52</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F31">
-        <v>1138.71</v>
+        <v>989.86</v>
       </c>
       <c r="G31">
         <v>502</v>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>7804.58</v>
+        <v>8800.27</v>
       </c>
       <c r="C32">
-        <v>1115</v>
+        <v>1257</v>
       </c>
       <c r="D32">
-        <v>986.6799999999999</v>
+        <v>1112.56</v>
       </c>
       <c r="E32">
-        <v>459.09</v>
+        <v>517.66</v>
       </c>
       <c r="F32">
-        <v>3213.65</v>
+        <v>3623.64</v>
       </c>
       <c r="G32">
         <v>7</v>
@@ -1170,19 +1170,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>26820.99</v>
+        <v>25934.04</v>
       </c>
       <c r="C33">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="D33">
-        <v>214.8</v>
+        <v>207.7</v>
       </c>
       <c r="E33">
-        <v>186.26</v>
+        <v>180.1</v>
       </c>
       <c r="F33">
-        <v>931.28</v>
+        <v>900.49</v>
       </c>
       <c r="G33">
         <v>70</v>
@@ -1195,19 +1195,19 @@
         </is>
       </c>
       <c r="B34">
-        <v>183778.68</v>
+        <v>194559.64</v>
       </c>
       <c r="C34">
-        <v>686</v>
+        <v>726</v>
       </c>
       <c r="D34">
-        <v>1033.31</v>
+        <v>1093.92</v>
       </c>
       <c r="E34">
-        <v>197.82</v>
+        <v>209.43</v>
       </c>
       <c r="F34">
-        <v>10880.33</v>
+        <v>11518.6</v>
       </c>
       <c r="G34">
         <v>268</v>
@@ -1220,16 +1220,16 @@
         </is>
       </c>
       <c r="B35">
-        <v>409.78</v>
+        <v>376.38</v>
       </c>
       <c r="C35">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="E35">
-        <v>409.78</v>
+        <v>376.38</v>
       </c>
       <c r="F35">
-        <v>409.78</v>
+        <v>376.38</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -1242,19 +1242,19 @@
         </is>
       </c>
       <c r="B36">
-        <v>5301.46</v>
+        <v>5006.43</v>
       </c>
       <c r="C36">
-        <v>530</v>
+        <v>501</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>530.15</v>
+        <v>500.64</v>
       </c>
       <c r="F36">
-        <v>530.15</v>
+        <v>500.64</v>
       </c>
       <c r="G36">
         <v>10</v>
@@ -1267,19 +1267,19 @@
         </is>
       </c>
       <c r="B37">
-        <v>10605.04</v>
+        <v>12488.84</v>
       </c>
       <c r="C37">
-        <v>530</v>
+        <v>624</v>
       </c>
       <c r="D37">
-        <v>409.4</v>
+        <v>482.13</v>
       </c>
       <c r="E37">
-        <v>225.64</v>
+        <v>265.72</v>
       </c>
       <c r="F37">
-        <v>1579.47</v>
+        <v>1860.04</v>
       </c>
       <c r="G37">
         <v>20</v>
@@ -1292,19 +1292,19 @@
         </is>
       </c>
       <c r="B38">
-        <v>382280.83</v>
+        <v>400658.39</v>
       </c>
       <c r="C38">
-        <v>1202</v>
+        <v>1260</v>
       </c>
       <c r="D38">
-        <v>1718.66</v>
+        <v>1801.28</v>
       </c>
       <c r="E38">
-        <v>277.42</v>
+        <v>290.75</v>
       </c>
       <c r="F38">
-        <v>17754.7</v>
+        <v>18608.23</v>
       </c>
       <c r="G38">
         <v>318</v>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="B39">
-        <v>51480.52</v>
+        <v>51818.04</v>
       </c>
       <c r="C39">
-        <v>1514</v>
+        <v>1524</v>
       </c>
       <c r="D39">
-        <v>3023.57</v>
+        <v>3043.4</v>
       </c>
       <c r="E39">
-        <v>242.83</v>
+        <v>244.42</v>
       </c>
       <c r="F39">
-        <v>16269.79</v>
+        <v>16376.46</v>
       </c>
       <c r="G39">
         <v>34</v>
@@ -1342,19 +1342,19 @@
         </is>
       </c>
       <c r="B40">
-        <v>13163.12</v>
+        <v>10011.77</v>
       </c>
       <c r="C40">
-        <v>1097</v>
+        <v>834</v>
       </c>
       <c r="D40">
-        <v>900.08</v>
+        <v>684.59</v>
       </c>
       <c r="E40">
-        <v>411.35</v>
+        <v>312.87</v>
       </c>
       <c r="F40">
-        <v>2879.43</v>
+        <v>2190.07</v>
       </c>
       <c r="G40">
         <v>12</v>
@@ -1367,19 +1367,19 @@
         </is>
       </c>
       <c r="B41">
-        <v>231260.69</v>
+        <v>272785.14</v>
       </c>
       <c r="C41">
-        <v>1377</v>
+        <v>1624</v>
       </c>
       <c r="D41">
-        <v>2329.09</v>
+        <v>2747.29</v>
       </c>
       <c r="E41">
-        <v>103.33</v>
+        <v>121.89</v>
       </c>
       <c r="F41">
-        <v>15293.38</v>
+        <v>18039.41</v>
       </c>
       <c r="G41">
         <v>168</v>
@@ -1392,19 +1392,19 @@
         </is>
       </c>
       <c r="B42">
-        <v>719196.0699999999</v>
+        <v>747392.24</v>
       </c>
       <c r="C42">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="D42">
-        <v>342.53</v>
+        <v>355.96</v>
       </c>
       <c r="E42">
-        <v>166.91</v>
+        <v>173.45</v>
       </c>
       <c r="F42">
-        <v>4840.26</v>
+        <v>5030.02</v>
       </c>
       <c r="G42">
         <v>2015</v>
@@ -1417,19 +1417,19 @@
         </is>
       </c>
       <c r="B43">
-        <v>352.81</v>
+        <v>319.64</v>
       </c>
       <c r="C43">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D43">
-        <v>27.76</v>
+        <v>25.15</v>
       </c>
       <c r="E43">
-        <v>35.28</v>
+        <v>31.96</v>
       </c>
       <c r="F43">
-        <v>105.84</v>
+        <v>95.89</v>
       </c>
       <c r="G43">
         <v>7</v>
@@ -1442,19 +1442,19 @@
         </is>
       </c>
       <c r="B44">
-        <v>10923.34</v>
+        <v>10199.72</v>
       </c>
       <c r="C44">
-        <v>1092</v>
+        <v>1020</v>
       </c>
       <c r="D44">
-        <v>845.96</v>
+        <v>789.92</v>
       </c>
       <c r="E44">
-        <v>321.27</v>
+        <v>299.99</v>
       </c>
       <c r="F44">
-        <v>3212.75</v>
+        <v>2999.92</v>
       </c>
       <c r="G44">
         <v>10</v>
@@ -1467,19 +1467,19 @@
         </is>
       </c>
       <c r="B45">
-        <v>211077.88</v>
+        <v>236453.98</v>
       </c>
       <c r="C45">
-        <v>708</v>
+        <v>793</v>
       </c>
       <c r="D45">
-        <v>828.22</v>
+        <v>927.79</v>
       </c>
       <c r="E45">
-        <v>70.93000000000001</v>
+        <v>79.45</v>
       </c>
       <c r="F45">
-        <v>3830.04</v>
+        <v>4290.5</v>
       </c>
       <c r="G45">
         <v>298</v>
@@ -1492,16 +1492,16 @@
         </is>
       </c>
       <c r="B46">
-        <v>856.37</v>
+        <v>683.71</v>
       </c>
       <c r="C46">
-        <v>856</v>
+        <v>684</v>
       </c>
       <c r="E46">
-        <v>856.37</v>
+        <v>683.71</v>
       </c>
       <c r="F46">
-        <v>856.37</v>
+        <v>683.71</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B47">
-        <v>11760.13</v>
+        <v>10961.17</v>
       </c>
       <c r="C47">
-        <v>1176</v>
+        <v>1096</v>
       </c>
       <c r="D47">
-        <v>890.7</v>
+        <v>830.1900000000001</v>
       </c>
       <c r="E47">
-        <v>113.08</v>
+        <v>105.4</v>
       </c>
       <c r="F47">
-        <v>2826.95</v>
+        <v>2634.9</v>
       </c>
       <c r="G47">
         <v>10</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B48">
-        <v>23447.8</v>
+        <v>21021.96</v>
       </c>
       <c r="C48">
-        <v>411</v>
+        <v>369</v>
       </c>
       <c r="D48">
-        <v>237.49</v>
+        <v>212.92</v>
       </c>
       <c r="E48">
-        <v>312.64</v>
+        <v>280.29</v>
       </c>
       <c r="F48">
-        <v>1875.82</v>
+        <v>1681.76</v>
       </c>
       <c r="G48">
         <v>57</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B49">
-        <v>41796.14</v>
+        <v>38769.37</v>
       </c>
       <c r="C49">
-        <v>360</v>
+        <v>334</v>
       </c>
       <c r="D49">
-        <v>150.42</v>
+        <v>139.53</v>
       </c>
       <c r="E49">
-        <v>296.43</v>
+        <v>274.96</v>
       </c>
       <c r="F49">
-        <v>1185.71</v>
+        <v>1099.84</v>
       </c>
       <c r="G49">
         <v>116</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B50">
-        <v>447710.52</v>
+        <v>466519.09</v>
       </c>
       <c r="C50">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="D50">
-        <v>661.05</v>
+        <v>688.8200000000001</v>
       </c>
       <c r="E50">
-        <v>157.92</v>
+        <v>164.56</v>
       </c>
       <c r="F50">
-        <v>10896.66</v>
+        <v>11354.43</v>
       </c>
       <c r="G50">
         <v>1118</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B51">
-        <v>1350.48</v>
+        <v>966.65</v>
       </c>
       <c r="C51">
-        <v>675</v>
+        <v>483</v>
       </c>
       <c r="D51">
-        <v>636.62</v>
+        <v>455.68</v>
       </c>
       <c r="E51">
-        <v>225.08</v>
+        <v>161.11</v>
       </c>
       <c r="F51">
-        <v>1125.4</v>
+        <v>805.54</v>
       </c>
       <c r="G51">
         <v>2</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B52">
-        <v>32415.8</v>
+        <v>29088.77</v>
       </c>
       <c r="C52">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="D52">
-        <v>218.03</v>
+        <v>195.66</v>
       </c>
       <c r="E52">
-        <v>144.07</v>
+        <v>129.28</v>
       </c>
       <c r="F52">
-        <v>1440.7</v>
+        <v>1292.83</v>
       </c>
       <c r="G52">
         <v>125</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B53">
-        <v>744.8099999999999</v>
+        <v>750.76</v>
       </c>
       <c r="C53">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D53">
-        <v>90.2</v>
+        <v>90.92</v>
       </c>
       <c r="E53">
-        <v>74.48</v>
+        <v>75.08</v>
       </c>
       <c r="F53">
-        <v>297.92</v>
+        <v>300.3</v>
       </c>
       <c r="G53">
         <v>6</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B54">
-        <v>3176.17</v>
+        <v>4103.04</v>
       </c>
       <c r="C54">
-        <v>1059</v>
+        <v>1368</v>
       </c>
       <c r="D54">
-        <v>1163.17</v>
+        <v>1502.6</v>
       </c>
       <c r="E54">
-        <v>198.51</v>
+        <v>256.44</v>
       </c>
       <c r="F54">
-        <v>2382.13</v>
+        <v>3077.28</v>
       </c>
       <c r="G54">
         <v>3</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B55">
-        <v>17370.92</v>
+        <v>17343.71</v>
       </c>
       <c r="C55">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D55">
-        <v>629.99</v>
+        <v>629</v>
       </c>
       <c r="E55">
-        <v>299.5</v>
+        <v>299.03</v>
       </c>
       <c r="F55">
-        <v>2395.99</v>
+        <v>2392.24</v>
       </c>
       <c r="G55">
         <v>26</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B56">
-        <v>674.33</v>
+        <v>811.04</v>
       </c>
       <c r="C56">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>224.78</v>
+        <v>270.35</v>
       </c>
       <c r="F56">
-        <v>224.78</v>
+        <v>270.35</v>
       </c>
       <c r="G56">
         <v>3</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B57">
-        <v>3575.6</v>
+        <v>2330.95</v>
       </c>
       <c r="C57">
-        <v>596</v>
+        <v>388</v>
       </c>
       <c r="D57">
-        <v>380</v>
+        <v>247.73</v>
       </c>
       <c r="E57">
-        <v>325.05</v>
+        <v>211.9</v>
       </c>
       <c r="F57">
-        <v>1300.22</v>
+        <v>847.62</v>
       </c>
       <c r="G57">
         <v>6</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B58">
-        <v>192077.17</v>
+        <v>209139.02</v>
       </c>
       <c r="C58">
-        <v>742</v>
+        <v>807</v>
       </c>
       <c r="D58">
-        <v>828.83</v>
+        <v>902.45</v>
       </c>
       <c r="E58">
-        <v>200.29</v>
+        <v>218.08</v>
       </c>
       <c r="F58">
-        <v>5407.8</v>
+        <v>5888.17</v>
       </c>
       <c r="G58">
         <v>259</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B59">
-        <v>57426.62</v>
+        <v>54519.22</v>
       </c>
       <c r="C59">
-        <v>787</v>
+        <v>747</v>
       </c>
       <c r="D59">
-        <v>1332.31</v>
+        <v>1264.86</v>
       </c>
       <c r="E59">
-        <v>192.71</v>
+        <v>182.95</v>
       </c>
       <c r="F59">
-        <v>9442.629999999999</v>
+        <v>8964.57</v>
       </c>
       <c r="G59">
         <v>73</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B60">
-        <v>5704.43</v>
+        <v>9033.6</v>
       </c>
       <c r="C60">
-        <v>190</v>
+        <v>301</v>
       </c>
       <c r="D60">
-        <v>151.86</v>
+        <v>240.48</v>
       </c>
       <c r="E60">
-        <v>103.72</v>
+        <v>164.25</v>
       </c>
       <c r="F60">
-        <v>829.74</v>
+        <v>1313.98</v>
       </c>
       <c r="G60">
         <v>30</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B61">
-        <v>397110.78</v>
+        <v>393597.39</v>
       </c>
       <c r="C61">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="D61">
-        <v>534.03</v>
+        <v>529.3099999999999</v>
       </c>
       <c r="E61">
-        <v>233.59</v>
+        <v>231.53</v>
       </c>
       <c r="F61">
-        <v>6073.46</v>
+        <v>6019.72</v>
       </c>
       <c r="G61">
         <v>762</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B62">
-        <v>947981.14</v>
+        <v>995267.64</v>
       </c>
       <c r="C62">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="D62">
-        <v>520.03</v>
+        <v>545.97</v>
       </c>
       <c r="E62">
-        <v>181.05</v>
+        <v>190.08</v>
       </c>
       <c r="F62">
-        <v>10500.94</v>
+        <v>11024.74</v>
       </c>
       <c r="G62">
         <v>2194</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B63">
-        <v>607.53</v>
+        <v>627.46</v>
       </c>
       <c r="C63">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>303.77</v>
+        <v>313.73</v>
       </c>
       <c r="F63">
-        <v>303.77</v>
+        <v>313.73</v>
       </c>
       <c r="G63">
         <v>2</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B64">
-        <v>1173174.1</v>
+        <v>1155383.12</v>
       </c>
       <c r="C64">
-        <v>872</v>
+        <v>859</v>
       </c>
       <c r="D64">
-        <v>1552.78</v>
+        <v>1529.23</v>
       </c>
       <c r="E64">
-        <v>365.7</v>
+        <v>360.16</v>
       </c>
       <c r="F64">
-        <v>33644.64</v>
+        <v>33134.43</v>
       </c>
       <c r="G64">
         <v>1345</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B65">
-        <v>20327.39</v>
+        <v>26904.46</v>
       </c>
       <c r="C65">
-        <v>350</v>
+        <v>464</v>
       </c>
       <c r="D65">
-        <v>333.07</v>
+        <v>440.83</v>
       </c>
       <c r="E65">
-        <v>156.36</v>
+        <v>206.96</v>
       </c>
       <c r="F65">
-        <v>2032.74</v>
+        <v>2690.45</v>
       </c>
       <c r="G65">
         <v>58</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B66">
-        <v>10990.1</v>
+        <v>10596.72</v>
       </c>
       <c r="C66">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D66">
-        <v>335.8</v>
+        <v>323.78</v>
       </c>
       <c r="E66">
-        <v>87.92</v>
+        <v>84.77</v>
       </c>
       <c r="F66">
-        <v>2549.7</v>
+        <v>2458.44</v>
       </c>
       <c r="G66">
         <v>57</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B67">
-        <v>393881</v>
+        <v>412862.62</v>
       </c>
       <c r="C67">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="D67">
-        <v>355.29</v>
+        <v>372.41</v>
       </c>
       <c r="E67">
-        <v>195.38</v>
+        <v>204.79</v>
       </c>
       <c r="F67">
-        <v>4298.3</v>
+        <v>4505.45</v>
       </c>
       <c r="G67">
         <v>904</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B68">
-        <v>37740.56</v>
+        <v>37050.31</v>
       </c>
       <c r="C68">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D68">
-        <v>314.07</v>
+        <v>308.33</v>
       </c>
       <c r="E68">
-        <v>189.65</v>
+        <v>186.18</v>
       </c>
       <c r="F68">
-        <v>2655.11</v>
+        <v>2606.55</v>
       </c>
       <c r="G68">
         <v>115</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B69">
-        <v>2682393.17</v>
+        <v>2891056.79</v>
       </c>
       <c r="C69">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="D69">
-        <v>516.1900000000001</v>
+        <v>556.35</v>
       </c>
       <c r="E69">
-        <v>101.28</v>
+        <v>109.16</v>
       </c>
       <c r="F69">
-        <v>11039.49</v>
+        <v>11898.25</v>
       </c>
       <c r="G69">
         <v>5351</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B70">
-        <v>373437.21</v>
+        <v>385444.31</v>
       </c>
       <c r="C70">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="D70">
-        <v>926.26</v>
+        <v>956.04</v>
       </c>
       <c r="E70">
-        <v>135.94</v>
+        <v>140.31</v>
       </c>
       <c r="F70">
-        <v>11419.27</v>
+        <v>11786.43</v>
       </c>
       <c r="G70">
         <v>616</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B71">
-        <v>155776.46</v>
+        <v>149527.09</v>
       </c>
       <c r="C71">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="D71">
-        <v>469.13</v>
+        <v>450.31</v>
       </c>
       <c r="E71">
-        <v>103.23</v>
+        <v>99.09</v>
       </c>
       <c r="F71">
-        <v>3303.41</v>
+        <v>3170.89</v>
       </c>
       <c r="G71">
         <v>372</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B72">
-        <v>82582.75999999999</v>
+        <v>93077.5</v>
       </c>
       <c r="C72">
-        <v>361</v>
+        <v>406</v>
       </c>
       <c r="D72">
-        <v>463.32</v>
+        <v>522.2</v>
       </c>
       <c r="E72">
-        <v>132.77</v>
+        <v>149.64</v>
       </c>
       <c r="F72">
-        <v>5045.25</v>
+        <v>5686.41</v>
       </c>
       <c r="G72">
         <v>229</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B73">
-        <v>33557.94</v>
+        <v>35717.58</v>
       </c>
       <c r="C73">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="D73">
-        <v>133.99</v>
+        <v>142.62</v>
       </c>
       <c r="E73">
-        <v>102.31</v>
+        <v>108.9</v>
       </c>
       <c r="F73">
-        <v>818.49</v>
+        <v>871.16</v>
       </c>
       <c r="G73">
         <v>178</v>
@@ -2189,19 +2189,19 @@
         </is>
       </c>
       <c r="B74">
-        <v>27277.24</v>
+        <v>31724.2</v>
       </c>
       <c r="C74">
-        <v>1436</v>
+        <v>1670</v>
       </c>
       <c r="D74">
-        <v>2161.82</v>
+        <v>2514.26</v>
       </c>
       <c r="E74">
-        <v>281.21</v>
+        <v>327.05</v>
       </c>
       <c r="F74">
-        <v>9842.299999999999</v>
+        <v>11446.88</v>
       </c>
       <c r="G74">
         <v>19</v>
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="B75">
-        <v>685.05</v>
+        <v>644.63</v>
       </c>
       <c r="C75">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D75">
-        <v>65.92</v>
+        <v>62.03</v>
       </c>
       <c r="E75">
-        <v>114.18</v>
+        <v>107.44</v>
       </c>
       <c r="F75">
-        <v>228.35</v>
+        <v>214.88</v>
       </c>
       <c r="G75">
         <v>4</v>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="B76">
-        <v>90469.87</v>
+        <v>88005.89</v>
       </c>
       <c r="C76">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D76">
-        <v>281.17</v>
+        <v>273.51</v>
       </c>
       <c r="E76">
-        <v>188.09</v>
+        <v>182.96</v>
       </c>
       <c r="F76">
-        <v>2257.04</v>
+        <v>2195.57</v>
       </c>
       <c r="G76">
         <v>252</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B77">
-        <v>7057.45</v>
+        <v>7548.23</v>
       </c>
       <c r="C77">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="D77">
-        <v>117.68</v>
+        <v>125.87</v>
       </c>
       <c r="E77">
-        <v>130.69</v>
+        <v>139.78</v>
       </c>
       <c r="F77">
-        <v>522.77</v>
+        <v>559.13</v>
       </c>
       <c r="G77">
         <v>37</v>
@@ -2289,19 +2289,19 @@
         </is>
       </c>
       <c r="B78">
-        <v>7489.88</v>
+        <v>6885.15</v>
       </c>
       <c r="C78">
-        <v>499</v>
+        <v>459</v>
       </c>
       <c r="D78">
-        <v>404.19</v>
+        <v>371.56</v>
       </c>
       <c r="E78">
-        <v>170.22</v>
+        <v>156.48</v>
       </c>
       <c r="F78">
-        <v>1532.02</v>
+        <v>1408.33</v>
       </c>
       <c r="G78">
         <v>15</v>
@@ -2339,16 +2339,16 @@
         </is>
       </c>
       <c r="B80">
-        <v>1421.85</v>
+        <v>1082.16</v>
       </c>
       <c r="C80">
-        <v>1422</v>
+        <v>1082</v>
       </c>
       <c r="E80">
-        <v>1421.85</v>
+        <v>1082.16</v>
       </c>
       <c r="F80">
-        <v>1421.85</v>
+        <v>1082.16</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -2361,19 +2361,19 @@
         </is>
       </c>
       <c r="B81">
-        <v>3366.95</v>
+        <v>5037.57</v>
       </c>
       <c r="C81">
-        <v>1122</v>
+        <v>1679</v>
       </c>
       <c r="D81">
-        <v>971.95</v>
+        <v>1454.22</v>
       </c>
       <c r="E81">
-        <v>561.16</v>
+        <v>839.59</v>
       </c>
       <c r="F81">
-        <v>2244.63</v>
+        <v>3358.38</v>
       </c>
       <c r="G81">
         <v>3</v>
@@ -2386,19 +2386,19 @@
         </is>
       </c>
       <c r="B82">
-        <v>410097.54</v>
+        <v>495031.22</v>
       </c>
       <c r="C82">
-        <v>884</v>
+        <v>1067</v>
       </c>
       <c r="D82">
-        <v>1594.44</v>
+        <v>1924.65</v>
       </c>
       <c r="E82">
-        <v>288.39</v>
+        <v>348.12</v>
       </c>
       <c r="F82">
-        <v>18457.27</v>
+        <v>22279.89</v>
       </c>
       <c r="G82">
         <v>464</v>
@@ -2411,19 +2411,19 @@
         </is>
       </c>
       <c r="B83">
-        <v>24796.68</v>
+        <v>32896.14</v>
       </c>
       <c r="C83">
-        <v>886</v>
+        <v>1175</v>
       </c>
       <c r="D83">
-        <v>963.12</v>
+        <v>1277.71</v>
       </c>
       <c r="E83">
-        <v>281.78</v>
+        <v>373.82</v>
       </c>
       <c r="F83">
-        <v>3944.93</v>
+        <v>5233.48</v>
       </c>
       <c r="G83">
         <v>28</v>
@@ -2436,19 +2436,19 @@
         </is>
       </c>
       <c r="B84">
-        <v>92337.11</v>
+        <v>86292.23</v>
       </c>
       <c r="C84">
-        <v>694</v>
+        <v>649</v>
       </c>
       <c r="D84">
-        <v>1041.61</v>
+        <v>973.4299999999999</v>
       </c>
       <c r="E84">
-        <v>157.57</v>
+        <v>147.26</v>
       </c>
       <c r="F84">
-        <v>6145.3</v>
+        <v>5743</v>
       </c>
       <c r="G84">
         <v>133</v>
@@ -2461,19 +2461,19 @@
         </is>
       </c>
       <c r="B85">
-        <v>24923.12</v>
+        <v>25587.09</v>
       </c>
       <c r="C85">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D85">
-        <v>36.52</v>
+        <v>37.49</v>
       </c>
       <c r="E85">
-        <v>136.19</v>
+        <v>139.82</v>
       </c>
       <c r="F85">
-        <v>408.58</v>
+        <v>419.46</v>
       </c>
       <c r="G85">
         <v>172</v>
@@ -2486,19 +2486,19 @@
         </is>
       </c>
       <c r="B86">
-        <v>219933.17</v>
+        <v>320865.39</v>
       </c>
       <c r="C86">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="D86">
-        <v>70.06</v>
+        <v>102.22</v>
       </c>
       <c r="E86">
-        <v>38.6</v>
+        <v>56.31</v>
       </c>
       <c r="F86">
-        <v>1582.53</v>
+        <v>2308.79</v>
       </c>
       <c r="G86">
         <v>2933</v>
@@ -2511,19 +2511,19 @@
         </is>
       </c>
       <c r="B87">
-        <v>9220.610000000001</v>
+        <v>12605.24</v>
       </c>
       <c r="C87">
-        <v>249</v>
+        <v>341</v>
       </c>
       <c r="D87">
-        <v>166.19</v>
+        <v>227.19</v>
       </c>
       <c r="E87">
-        <v>91.29000000000001</v>
+        <v>124.8</v>
       </c>
       <c r="F87">
-        <v>639.05</v>
+        <v>873.63</v>
       </c>
       <c r="G87">
         <v>37</v>
@@ -2536,19 +2536,19 @@
         </is>
       </c>
       <c r="B88">
-        <v>219386.77</v>
+        <v>227761.62</v>
       </c>
       <c r="C88">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="D88">
-        <v>208.93</v>
+        <v>216.91</v>
       </c>
       <c r="E88">
-        <v>116.51</v>
+        <v>120.96</v>
       </c>
       <c r="F88">
-        <v>2446.69</v>
+        <v>2540.09</v>
       </c>
       <c r="G88">
         <v>787</v>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_costs_by_tretspef-Users_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_costs_by_tretspef-Users_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -598,13 +598,13 @@
         </is>
       </c>
       <c r="B10">
-        <v>10575945.53</v>
+        <v>9468296.99</v>
       </c>
       <c r="C10">
-        <v>607</v>
+        <v>563</v>
       </c>
       <c r="D10">
-        <v>694.95</v>
+        <v>580.29</v>
       </c>
       <c r="E10">
         <v>166.51</v>
@@ -613,1944 +613,2144 @@
         <v>33469.24</v>
       </c>
       <c r="G10">
-        <v>17426</v>
+        <v>16816</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ophthalmology Service</t>
+          <t>Ear Nose and Throat Service</t>
         </is>
       </c>
       <c r="B11">
-        <v>1755825.96</v>
+        <v>394012.57</v>
       </c>
       <c r="C11">
-        <v>531</v>
+        <v>333</v>
       </c>
       <c r="D11">
-        <v>612.16</v>
+        <v>764.05</v>
       </c>
       <c r="E11">
-        <v>149.69</v>
+        <v>160.89</v>
       </c>
       <c r="F11">
-        <v>5987.47</v>
+        <v>24454.84</v>
       </c>
       <c r="G11">
-        <v>3308</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Oral Surgery Service</t>
+          <t>Ophthalmology Service</t>
         </is>
       </c>
       <c r="B12">
-        <v>147842.09</v>
+        <v>1755825.96</v>
       </c>
       <c r="C12">
-        <v>422</v>
+        <v>531</v>
       </c>
       <c r="D12">
-        <v>313.11</v>
+        <v>612.16</v>
       </c>
       <c r="E12">
-        <v>219.03</v>
+        <v>149.69</v>
       </c>
       <c r="F12">
-        <v>2847.33</v>
+        <v>5987.47</v>
       </c>
       <c r="G12">
-        <v>350</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Restorative Dentistry Service</t>
+          <t>Oral Surgery Service</t>
         </is>
       </c>
       <c r="B13">
-        <v>102574.71</v>
+        <v>147842.09</v>
       </c>
       <c r="C13">
-        <v>1193</v>
+        <v>422</v>
       </c>
       <c r="D13">
-        <v>1206.8</v>
+        <v>313.11</v>
       </c>
       <c r="E13">
-        <v>309.89</v>
+        <v>219.03</v>
       </c>
       <c r="F13">
-        <v>4648.4</v>
+        <v>2847.33</v>
       </c>
       <c r="G13">
-        <v>86</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Orthodontic Service</t>
+          <t>Restorative Dentistry Service</t>
         </is>
       </c>
       <c r="B14">
-        <v>647.3200000000001</v>
+        <v>102574.71</v>
       </c>
       <c r="C14">
-        <v>216</v>
+        <v>1193</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1206.8</v>
       </c>
       <c r="E14">
-        <v>215.77</v>
+        <v>309.89</v>
       </c>
       <c r="F14">
-        <v>215.77</v>
+        <v>4648.4</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Neurosurgical Service</t>
+          <t>Orthodontic Service</t>
         </is>
       </c>
       <c r="B15">
-        <v>143525.49</v>
+        <v>647.3200000000001</v>
       </c>
       <c r="C15">
-        <v>477</v>
+        <v>216</v>
       </c>
       <c r="D15">
-        <v>453.98</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>217.13</v>
+        <v>215.77</v>
       </c>
       <c r="F15">
-        <v>4776.95</v>
+        <v>215.77</v>
       </c>
       <c r="G15">
-        <v>301</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Plastic Surgery Service</t>
+          <t>Maxillofacial Surgery Service</t>
         </is>
       </c>
       <c r="B16">
-        <v>173178.68</v>
+        <v>102923.73</v>
       </c>
       <c r="C16">
-        <v>485</v>
+        <v>399</v>
       </c>
       <c r="D16">
-        <v>489.95</v>
+        <v>381.13</v>
       </c>
       <c r="E16">
-        <v>163.22</v>
+        <v>192.02</v>
       </c>
       <c r="F16">
-        <v>3264.44</v>
+        <v>3264.37</v>
       </c>
       <c r="G16">
-        <v>357</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cardiothoracic Surgery Service</t>
+          <t>Neurosurgical Service</t>
         </is>
       </c>
       <c r="B17">
-        <v>16243.37</v>
+        <v>143525.49</v>
       </c>
       <c r="C17">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="D17">
-        <v>333.44</v>
+        <v>453.98</v>
       </c>
       <c r="E17">
-        <v>306.48</v>
+        <v>217.13</v>
       </c>
       <c r="F17">
-        <v>1532.39</v>
+        <v>4776.95</v>
       </c>
       <c r="G17">
-        <v>33</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cardiac Surgery Service</t>
+          <t>Plastic Surgery Service</t>
         </is>
       </c>
       <c r="B18">
-        <v>16616.76</v>
+        <v>173178.68</v>
       </c>
       <c r="C18">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="D18">
-        <v>275.14</v>
+        <v>489.95</v>
       </c>
       <c r="E18">
-        <v>272.41</v>
+        <v>163.22</v>
       </c>
       <c r="F18">
-        <v>1362.03</v>
+        <v>3264.44</v>
       </c>
       <c r="G18">
-        <v>35</v>
+        <v>357</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Thoracic Surgery Service</t>
+          <t>Burns Care Service</t>
         </is>
       </c>
       <c r="B19">
-        <v>8521.469999999999</v>
+        <v>7434.08</v>
       </c>
       <c r="C19">
-        <v>406</v>
+        <v>1239</v>
       </c>
       <c r="D19">
-        <v>208.19</v>
+        <v>939.53</v>
       </c>
       <c r="E19">
-        <v>224.25</v>
+        <v>154.88</v>
       </c>
       <c r="F19">
-        <v>897</v>
+        <v>2323.15</v>
       </c>
       <c r="G19">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cardiothoracic Transplantation Service</t>
+          <t>Cardiothoracic Surgery Service</t>
         </is>
       </c>
       <c r="B20">
-        <v>30273.54</v>
+        <v>16243.37</v>
       </c>
       <c r="C20">
-        <v>10091</v>
+        <v>492</v>
       </c>
       <c r="D20">
-        <v>8484.709999999999</v>
+        <v>333.44</v>
       </c>
       <c r="E20">
-        <v>540.6</v>
+        <v>306.48</v>
       </c>
       <c r="F20">
-        <v>16758.57</v>
+        <v>1532.39</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Emergency Medicine Service</t>
+          <t>Cardiac Surgery Service</t>
         </is>
       </c>
       <c r="B21">
-        <v>55300.41</v>
+        <v>16616.76</v>
       </c>
       <c r="C21">
-        <v>206</v>
+        <v>475</v>
       </c>
       <c r="D21">
-        <v>171.02</v>
+        <v>275.14</v>
       </c>
       <c r="E21">
-        <v>146.3</v>
+        <v>272.41</v>
       </c>
       <c r="F21">
-        <v>1609.27</v>
+        <v>1362.03</v>
       </c>
       <c r="G21">
-        <v>268</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Anaesthetic Service</t>
+          <t>Thoracic Surgery Service</t>
         </is>
       </c>
       <c r="B22">
-        <v>72269.62</v>
+        <v>8521.469999999999</v>
       </c>
       <c r="C22">
-        <v>193</v>
+        <v>406</v>
       </c>
       <c r="D22">
-        <v>93.94</v>
+        <v>208.19</v>
       </c>
       <c r="E22">
-        <v>150.56</v>
+        <v>224.25</v>
       </c>
       <c r="F22">
-        <v>752.8099999999999</v>
+        <v>897</v>
       </c>
       <c r="G22">
-        <v>375</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pain Management Service</t>
+          <t>Cardiothoracic Transplantation Service</t>
         </is>
       </c>
       <c r="B23">
-        <v>260631.76</v>
+        <v>30273.54</v>
       </c>
       <c r="C23">
-        <v>551</v>
+        <v>10091</v>
       </c>
       <c r="D23">
-        <v>534.88</v>
+        <v>8484.709999999999</v>
       </c>
       <c r="E23">
-        <v>219.76</v>
+        <v>540.6</v>
       </c>
       <c r="F23">
-        <v>3516.11</v>
+        <v>16758.57</v>
       </c>
       <c r="G23">
-        <v>473</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Paediatric Trauma and Orthopaedic Service</t>
+          <t>Emergency Medicine Service</t>
         </is>
       </c>
       <c r="B24">
-        <v>3637.93</v>
+        <v>55300.41</v>
       </c>
       <c r="C24">
-        <v>243</v>
+        <v>206</v>
       </c>
       <c r="D24">
-        <v>113.3</v>
+        <v>171.02</v>
       </c>
       <c r="E24">
-        <v>202.11</v>
+        <v>146.3</v>
       </c>
       <c r="F24">
-        <v>606.3200000000001</v>
+        <v>1609.27</v>
       </c>
       <c r="G24">
-        <v>15</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Paediatric Ear Nose and Throat Service</t>
+          <t>Anaesthetic Service</t>
         </is>
       </c>
       <c r="B25">
-        <v>168.99</v>
+        <v>72269.62</v>
       </c>
       <c r="C25">
-        <v>169</v>
+        <v>193</v>
+      </c>
+      <c r="D25">
+        <v>93.94</v>
       </c>
       <c r="E25">
-        <v>168.99</v>
+        <v>150.56</v>
       </c>
       <c r="F25">
-        <v>168.99</v>
+        <v>752.8099999999999</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>375</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Paediatric Ophthalmology Service</t>
+          <t>Pain Management Service</t>
         </is>
       </c>
       <c r="B26">
-        <v>2505</v>
+        <v>260631.76</v>
       </c>
       <c r="C26">
-        <v>358</v>
+        <v>551</v>
       </c>
       <c r="D26">
-        <v>334.74</v>
+        <v>534.88</v>
       </c>
       <c r="E26">
-        <v>156.56</v>
+        <v>219.76</v>
       </c>
       <c r="F26">
-        <v>1095.94</v>
+        <v>3516.11</v>
       </c>
       <c r="G26">
-        <v>7</v>
+        <v>473</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>General Internal Medicine Service</t>
+          <t>Paediatric Trauma and Orthopaedic Service</t>
         </is>
       </c>
       <c r="B27">
-        <v>519003.32</v>
+        <v>3637.93</v>
       </c>
       <c r="C27">
-        <v>461</v>
+        <v>243</v>
       </c>
       <c r="D27">
-        <v>1507.75</v>
+        <v>113.3</v>
       </c>
       <c r="E27">
-        <v>166.45</v>
+        <v>202.11</v>
       </c>
       <c r="F27">
-        <v>28297.17</v>
+        <v>606.3200000000001</v>
       </c>
       <c r="G27">
-        <v>1126</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Gastroenterology Service</t>
+          <t>Paediatric Ear Nose and Throat Service</t>
         </is>
       </c>
       <c r="B28">
-        <v>311605.05</v>
+        <v>168.99</v>
       </c>
       <c r="C28">
-        <v>328</v>
-      </c>
-      <c r="D28">
-        <v>299.23</v>
+        <v>169</v>
       </c>
       <c r="E28">
-        <v>171.87</v>
+        <v>168.99</v>
       </c>
       <c r="F28">
-        <v>3437.45</v>
+        <v>168.99</v>
       </c>
       <c r="G28">
-        <v>949</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Endocrinology Service</t>
+          <t>Paediatric Ophthalmology Service</t>
         </is>
       </c>
       <c r="B29">
-        <v>125108.89</v>
+        <v>2505</v>
       </c>
       <c r="C29">
-        <v>465</v>
+        <v>358</v>
       </c>
       <c r="D29">
-        <v>384.1</v>
+        <v>334.74</v>
       </c>
       <c r="E29">
-        <v>213.5</v>
+        <v>156.56</v>
       </c>
       <c r="F29">
-        <v>3202.45</v>
+        <v>1095.94</v>
       </c>
       <c r="G29">
-        <v>269</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Clinical Haematology Service</t>
+          <t>General Internal Medicine Service</t>
         </is>
       </c>
       <c r="B30">
-        <v>303949.98</v>
+        <v>519003.32</v>
       </c>
       <c r="C30">
-        <v>637</v>
+        <v>461</v>
       </c>
       <c r="D30">
-        <v>770.4299999999999</v>
+        <v>1507.75</v>
       </c>
       <c r="E30">
-        <v>189.97</v>
+        <v>166.45</v>
       </c>
       <c r="F30">
-        <v>6268.97</v>
+        <v>28297.17</v>
       </c>
       <c r="G30">
-        <v>477</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Clinical Physiology Service</t>
+          <t>Gastroenterology Service</t>
         </is>
       </c>
       <c r="B31">
-        <v>67310.17</v>
+        <v>311605.05</v>
       </c>
       <c r="C31">
-        <v>134</v>
+        <v>328</v>
       </c>
       <c r="D31">
-        <v>97.28</v>
+        <v>299.23</v>
       </c>
       <c r="E31">
-        <v>89.98999999999999</v>
+        <v>171.87</v>
       </c>
       <c r="F31">
-        <v>989.86</v>
+        <v>3437.45</v>
       </c>
       <c r="G31">
-        <v>502</v>
+        <v>949</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Clinical Pharmacology Service</t>
+          <t>Endocrinology Service</t>
         </is>
       </c>
       <c r="B32">
-        <v>8800.27</v>
+        <v>125108.89</v>
       </c>
       <c r="C32">
-        <v>1257</v>
+        <v>465</v>
       </c>
       <c r="D32">
-        <v>1112.56</v>
+        <v>384.1</v>
       </c>
       <c r="E32">
-        <v>517.66</v>
+        <v>213.5</v>
       </c>
       <c r="F32">
-        <v>3623.64</v>
+        <v>3202.45</v>
       </c>
       <c r="G32">
-        <v>7</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Hepatology Service</t>
+          <t>Clinical Haematology Service</t>
         </is>
       </c>
       <c r="B33">
-        <v>25934.04</v>
+        <v>303949.98</v>
       </c>
       <c r="C33">
-        <v>370</v>
+        <v>637</v>
       </c>
       <c r="D33">
-        <v>207.7</v>
+        <v>770.4299999999999</v>
       </c>
       <c r="E33">
-        <v>180.1</v>
+        <v>189.97</v>
       </c>
       <c r="F33">
-        <v>900.49</v>
+        <v>6268.97</v>
       </c>
       <c r="G33">
-        <v>70</v>
+        <v>477</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Diabetes Service</t>
+          <t>Clinical Physiology Service</t>
         </is>
       </c>
       <c r="B34">
-        <v>194559.64</v>
+        <v>67310.17</v>
       </c>
       <c r="C34">
-        <v>726</v>
+        <v>134</v>
       </c>
       <c r="D34">
-        <v>1093.92</v>
+        <v>97.28</v>
       </c>
       <c r="E34">
-        <v>209.43</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F34">
-        <v>11518.6</v>
+        <v>989.86</v>
       </c>
       <c r="G34">
-        <v>268</v>
+        <v>502</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Blood and Marrow Transplantation Service</t>
+          <t>Clinical Pharmacology Service</t>
         </is>
       </c>
       <c r="B35">
-        <v>376.38</v>
+        <v>8800.27</v>
       </c>
       <c r="C35">
-        <v>376</v>
+        <v>1257</v>
+      </c>
+      <c r="D35">
+        <v>1112.56</v>
       </c>
       <c r="E35">
-        <v>376.38</v>
+        <v>517.66</v>
       </c>
       <c r="F35">
-        <v>376.38</v>
+        <v>3623.64</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Clinical Genetics Service</t>
+          <t>Hepatology Service</t>
         </is>
       </c>
       <c r="B36">
-        <v>5006.43</v>
+        <v>25934.04</v>
       </c>
       <c r="C36">
-        <v>501</v>
+        <v>370</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>207.7</v>
       </c>
       <c r="E36">
-        <v>500.64</v>
+        <v>180.1</v>
       </c>
       <c r="F36">
-        <v>500.64</v>
+        <v>900.49</v>
       </c>
       <c r="G36">
-        <v>10</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Clinical Immunology and Allergy Service</t>
+          <t>Diabetes Service</t>
         </is>
       </c>
       <c r="B37">
-        <v>12488.84</v>
+        <v>194559.64</v>
       </c>
       <c r="C37">
-        <v>624</v>
+        <v>726</v>
       </c>
       <c r="D37">
-        <v>482.13</v>
+        <v>1093.92</v>
       </c>
       <c r="E37">
-        <v>265.72</v>
+        <v>209.43</v>
       </c>
       <c r="F37">
-        <v>1860.04</v>
+        <v>11518.6</v>
       </c>
       <c r="G37">
-        <v>20</v>
+        <v>268</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Rehabilitation Medicine Service</t>
+          <t>Blood and Marrow Transplantation Service</t>
         </is>
       </c>
       <c r="B38">
-        <v>400658.39</v>
+        <v>376.38</v>
       </c>
       <c r="C38">
-        <v>1260</v>
-      </c>
-      <c r="D38">
-        <v>1801.28</v>
+        <v>376</v>
       </c>
       <c r="E38">
-        <v>290.75</v>
+        <v>376.38</v>
       </c>
       <c r="F38">
-        <v>18608.23</v>
+        <v>376.38</v>
       </c>
       <c r="G38">
-        <v>318</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Palliative Medicine Service</t>
+          <t>Clinical Genetics Service</t>
         </is>
       </c>
       <c r="B39">
-        <v>51818.04</v>
+        <v>5006.43</v>
       </c>
       <c r="C39">
-        <v>1524</v>
+        <v>501</v>
       </c>
       <c r="D39">
-        <v>3043.4</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>244.42</v>
+        <v>500.64</v>
       </c>
       <c r="F39">
-        <v>16376.46</v>
+        <v>500.64</v>
       </c>
       <c r="G39">
-        <v>34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Clinical Immunology Service</t>
+          <t>Clinical Immunology and Allergy Service</t>
         </is>
       </c>
       <c r="B40">
-        <v>10011.77</v>
+        <v>12488.84</v>
       </c>
       <c r="C40">
-        <v>834</v>
+        <v>624</v>
       </c>
       <c r="D40">
-        <v>684.59</v>
+        <v>482.13</v>
       </c>
       <c r="E40">
-        <v>312.87</v>
+        <v>265.72</v>
       </c>
       <c r="F40">
-        <v>2190.07</v>
+        <v>1860.04</v>
       </c>
       <c r="G40">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Intermediate Care Service</t>
+          <t>Rehabilitation Medicine Service</t>
         </is>
       </c>
       <c r="B41">
-        <v>272785.14</v>
+        <v>400658.39</v>
       </c>
       <c r="C41">
-        <v>1624</v>
+        <v>1260</v>
       </c>
       <c r="D41">
-        <v>2747.29</v>
+        <v>1801.28</v>
       </c>
       <c r="E41">
-        <v>121.89</v>
+        <v>290.75</v>
       </c>
       <c r="F41">
-        <v>18039.41</v>
+        <v>18608.23</v>
       </c>
       <c r="G41">
-        <v>168</v>
+        <v>318</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cardiology Service</t>
+          <t>Palliative Medicine Service</t>
         </is>
       </c>
       <c r="B42">
-        <v>747392.24</v>
+        <v>51818.04</v>
       </c>
       <c r="C42">
-        <v>371</v>
+        <v>1524</v>
       </c>
       <c r="D42">
-        <v>355.96</v>
+        <v>3043.4</v>
       </c>
       <c r="E42">
-        <v>173.45</v>
+        <v>244.42</v>
       </c>
       <c r="F42">
-        <v>5030.02</v>
+        <v>16376.46</v>
       </c>
       <c r="G42">
-        <v>2015</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Clinical Microbiology Service</t>
+          <t>Clinical Immunology Service</t>
         </is>
       </c>
       <c r="B43">
-        <v>319.64</v>
+        <v>10011.77</v>
       </c>
       <c r="C43">
-        <v>46</v>
+        <v>834</v>
       </c>
       <c r="D43">
-        <v>25.15</v>
+        <v>684.59</v>
       </c>
       <c r="E43">
-        <v>31.96</v>
+        <v>312.87</v>
       </c>
       <c r="F43">
-        <v>95.89</v>
+        <v>2190.07</v>
       </c>
       <c r="G43">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Spinal Injuries Service</t>
+          <t>Allergy Service</t>
         </is>
       </c>
       <c r="B44">
-        <v>10199.72</v>
+        <v>20138.74</v>
       </c>
       <c r="C44">
-        <v>1020</v>
+        <v>1438</v>
       </c>
       <c r="D44">
-        <v>789.92</v>
+        <v>3511.58</v>
       </c>
       <c r="E44">
-        <v>299.99</v>
+        <v>261.54</v>
       </c>
       <c r="F44">
-        <v>2999.92</v>
+        <v>13600.19</v>
       </c>
       <c r="G44">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Anticoagulant Service</t>
+          <t>Intermediate Care Service</t>
         </is>
       </c>
       <c r="B45">
-        <v>236453.98</v>
+        <v>272785.14</v>
       </c>
       <c r="C45">
-        <v>793</v>
+        <v>1624</v>
       </c>
       <c r="D45">
-        <v>927.79</v>
+        <v>2747.29</v>
       </c>
       <c r="E45">
-        <v>79.45</v>
+        <v>121.89</v>
       </c>
       <c r="F45">
-        <v>4290.5</v>
+        <v>18039.41</v>
       </c>
       <c r="G45">
-        <v>298</v>
+        <v>168</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sport and Exercise Medicine Service</t>
+          <t>Cardiology Service</t>
         </is>
       </c>
       <c r="B46">
-        <v>683.71</v>
+        <v>747392.24</v>
       </c>
       <c r="C46">
-        <v>684</v>
+        <v>371</v>
+      </c>
+      <c r="D46">
+        <v>355.96</v>
       </c>
       <c r="E46">
-        <v>683.71</v>
+        <v>173.45</v>
       </c>
       <c r="F46">
-        <v>683.71</v>
+        <v>5030.02</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cardiac Rehabilitation Service</t>
+          <t>Clinical Microbiology Service</t>
         </is>
       </c>
       <c r="B47">
-        <v>10961.17</v>
+        <v>319.64</v>
       </c>
       <c r="C47">
-        <v>1096</v>
+        <v>46</v>
       </c>
       <c r="D47">
-        <v>830.1900000000001</v>
+        <v>25.15</v>
       </c>
       <c r="E47">
-        <v>105.4</v>
+        <v>31.96</v>
       </c>
       <c r="F47">
-        <v>2634.9</v>
+        <v>95.89</v>
       </c>
       <c r="G47">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Stroke Medicine Service</t>
+          <t>Spinal Injuries Service</t>
         </is>
       </c>
       <c r="B48">
-        <v>21021.96</v>
+        <v>10199.72</v>
       </c>
       <c r="C48">
-        <v>369</v>
+        <v>1020</v>
       </c>
       <c r="D48">
-        <v>212.92</v>
+        <v>789.92</v>
       </c>
       <c r="E48">
-        <v>280.29</v>
+        <v>299.99</v>
       </c>
       <c r="F48">
-        <v>1681.76</v>
+        <v>2999.92</v>
       </c>
       <c r="G48">
-        <v>57</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Transient Ischaemic Attack Service</t>
+          <t>Anticoagulant Service</t>
         </is>
       </c>
       <c r="B49">
-        <v>38769.37</v>
+        <v>236453.98</v>
       </c>
       <c r="C49">
-        <v>334</v>
+        <v>793</v>
       </c>
       <c r="D49">
-        <v>139.53</v>
+        <v>927.79</v>
       </c>
       <c r="E49">
-        <v>274.96</v>
+        <v>79.45</v>
       </c>
       <c r="F49">
-        <v>1099.84</v>
+        <v>4290.5</v>
       </c>
       <c r="G49">
-        <v>116</v>
+        <v>298</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Dermatology Service</t>
+          <t>Sport and Exercise Medicine Service</t>
         </is>
       </c>
       <c r="B50">
-        <v>466519.09</v>
+        <v>683.71</v>
       </c>
       <c r="C50">
-        <v>417</v>
-      </c>
-      <c r="D50">
-        <v>688.8200000000001</v>
+        <v>684</v>
       </c>
       <c r="E50">
-        <v>164.56</v>
+        <v>683.71</v>
       </c>
       <c r="F50">
-        <v>11354.43</v>
+        <v>683.71</v>
       </c>
       <c r="G50">
-        <v>1118</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Congenital Heart Disease Service</t>
+          <t>Cardiac Rehabilitation Service</t>
         </is>
       </c>
       <c r="B51">
-        <v>966.65</v>
+        <v>10961.17</v>
       </c>
       <c r="C51">
-        <v>483</v>
+        <v>1096</v>
       </c>
       <c r="D51">
-        <v>455.68</v>
+        <v>830.1900000000001</v>
       </c>
       <c r="E51">
-        <v>161.11</v>
+        <v>105.4</v>
       </c>
       <c r="F51">
-        <v>805.54</v>
+        <v>2634.9</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Respiratory Physiology Service</t>
+          <t>Stroke Medicine Service</t>
         </is>
       </c>
       <c r="B52">
-        <v>29088.77</v>
+        <v>21021.96</v>
       </c>
       <c r="C52">
-        <v>233</v>
+        <v>369</v>
       </c>
       <c r="D52">
-        <v>195.66</v>
+        <v>212.92</v>
       </c>
       <c r="E52">
-        <v>129.28</v>
+        <v>280.29</v>
       </c>
       <c r="F52">
-        <v>1292.83</v>
+        <v>1681.76</v>
       </c>
       <c r="G52">
-        <v>125</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Pulmonary Rehabilitation Service</t>
+          <t>Transient Ischaemic Attack Service</t>
         </is>
       </c>
       <c r="B53">
-        <v>750.76</v>
+        <v>38769.37</v>
       </c>
       <c r="C53">
-        <v>125</v>
+        <v>334</v>
       </c>
       <c r="D53">
-        <v>90.92</v>
+        <v>139.53</v>
       </c>
       <c r="E53">
-        <v>75.08</v>
+        <v>274.96</v>
       </c>
       <c r="F53">
-        <v>300.3</v>
+        <v>1099.84</v>
       </c>
       <c r="G53">
-        <v>6</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Complex Specialised Rehabilitation Service</t>
+          <t>Dermatology Service</t>
         </is>
       </c>
       <c r="B54">
-        <v>4103.04</v>
+        <v>466519.09</v>
       </c>
       <c r="C54">
-        <v>1368</v>
+        <v>417</v>
       </c>
       <c r="D54">
-        <v>1502.6</v>
+        <v>688.8200000000001</v>
       </c>
       <c r="E54">
-        <v>256.44</v>
+        <v>164.56</v>
       </c>
       <c r="F54">
-        <v>3077.28</v>
+        <v>11354.43</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Infectious Diseases Service</t>
+          <t>Congenital Heart Disease Service</t>
         </is>
       </c>
       <c r="B55">
-        <v>17343.71</v>
+        <v>966.65</v>
       </c>
       <c r="C55">
-        <v>667</v>
+        <v>483</v>
       </c>
       <c r="D55">
-        <v>629</v>
+        <v>455.68</v>
       </c>
       <c r="E55">
-        <v>299.03</v>
+        <v>161.11</v>
       </c>
       <c r="F55">
-        <v>2392.24</v>
+        <v>805.54</v>
       </c>
       <c r="G55">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tropical Medicine Service</t>
+          <t>Respiratory Medicine Service</t>
         </is>
       </c>
       <c r="B56">
-        <v>811.04</v>
+        <v>496405.91</v>
       </c>
       <c r="C56">
-        <v>270</v>
+        <v>573</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>805.53</v>
       </c>
       <c r="E56">
-        <v>270.35</v>
+        <v>198.25</v>
       </c>
       <c r="F56">
-        <v>270.35</v>
+        <v>13282.43</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>867</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Genitourinary Medicine Service</t>
+          <t>Respiratory Physiology Service</t>
         </is>
       </c>
       <c r="B57">
-        <v>2330.95</v>
+        <v>29088.77</v>
       </c>
       <c r="C57">
-        <v>388</v>
+        <v>233</v>
       </c>
       <c r="D57">
-        <v>247.73</v>
+        <v>195.66</v>
       </c>
       <c r="E57">
-        <v>211.9</v>
+        <v>129.28</v>
       </c>
       <c r="F57">
-        <v>847.62</v>
+        <v>1292.83</v>
       </c>
       <c r="G57">
-        <v>6</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Renal Medicine Service</t>
+          <t>Pulmonary Rehabilitation Service</t>
         </is>
       </c>
       <c r="B58">
-        <v>209139.02</v>
+        <v>750.76</v>
       </c>
       <c r="C58">
-        <v>807</v>
+        <v>125</v>
       </c>
       <c r="D58">
-        <v>902.45</v>
+        <v>90.92</v>
       </c>
       <c r="E58">
-        <v>218.08</v>
+        <v>75.08</v>
       </c>
       <c r="F58">
-        <v>5888.17</v>
+        <v>300.3</v>
       </c>
       <c r="G58">
-        <v>259</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Medical Oncology Service</t>
+          <t>Complex Specialised Rehabilitation Service</t>
         </is>
       </c>
       <c r="B59">
-        <v>54519.22</v>
+        <v>4103.04</v>
       </c>
       <c r="C59">
-        <v>747</v>
+        <v>1368</v>
       </c>
       <c r="D59">
-        <v>1264.86</v>
+        <v>1502.6</v>
       </c>
       <c r="E59">
-        <v>182.95</v>
+        <v>256.44</v>
       </c>
       <c r="F59">
-        <v>8964.57</v>
+        <v>3077.28</v>
       </c>
       <c r="G59">
-        <v>73</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Nuclear Medicine Service</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B60">
-        <v>9033.6</v>
+        <v>373.87</v>
       </c>
       <c r="C60">
-        <v>301</v>
+        <v>187</v>
       </c>
       <c r="D60">
-        <v>240.48</v>
+        <v>132.18</v>
       </c>
       <c r="E60">
-        <v>164.25</v>
+        <v>93.47</v>
       </c>
       <c r="F60">
-        <v>1313.98</v>
+        <v>280.4</v>
       </c>
       <c r="G60">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Neurology Service</t>
+          <t>Infectious Diseases Service</t>
         </is>
       </c>
       <c r="B61">
-        <v>393597.39</v>
+        <v>17343.71</v>
       </c>
       <c r="C61">
-        <v>517</v>
+        <v>667</v>
       </c>
       <c r="D61">
-        <v>529.3099999999999</v>
+        <v>629</v>
       </c>
       <c r="E61">
-        <v>231.53</v>
+        <v>299.03</v>
       </c>
       <c r="F61">
-        <v>6019.72</v>
+        <v>2392.24</v>
       </c>
       <c r="G61">
-        <v>762</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Rheumatology Service</t>
+          <t>Tropical Medicine Service</t>
         </is>
       </c>
       <c r="B62">
-        <v>995267.64</v>
+        <v>811.04</v>
       </c>
       <c r="C62">
-        <v>454</v>
+        <v>270</v>
       </c>
       <c r="D62">
-        <v>545.97</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>190.08</v>
+        <v>270.35</v>
       </c>
       <c r="F62">
-        <v>11024.74</v>
+        <v>270.35</v>
       </c>
       <c r="G62">
-        <v>2194</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Paediatric Service</t>
+          <t>Genitourinary Medicine Service</t>
         </is>
       </c>
       <c r="B63">
-        <v>627.46</v>
+        <v>2330.95</v>
       </c>
       <c r="C63">
-        <v>314</v>
+        <v>388</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>247.73</v>
       </c>
       <c r="E63">
-        <v>313.73</v>
+        <v>211.9</v>
       </c>
       <c r="F63">
-        <v>313.73</v>
+        <v>847.62</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Elderly Medicine Service</t>
+          <t>Renal Medicine Service</t>
         </is>
       </c>
       <c r="B64">
-        <v>1155383.12</v>
+        <v>209139.02</v>
       </c>
       <c r="C64">
-        <v>859</v>
+        <v>807</v>
       </c>
       <c r="D64">
-        <v>1529.23</v>
+        <v>902.45</v>
       </c>
       <c r="E64">
-        <v>360.16</v>
+        <v>218.08</v>
       </c>
       <c r="F64">
-        <v>33134.43</v>
+        <v>5888.17</v>
       </c>
       <c r="G64">
-        <v>1345</v>
+        <v>259</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dental Medicine Service</t>
+          <t>Medical Oncology Service</t>
         </is>
       </c>
       <c r="B65">
-        <v>26904.46</v>
+        <v>54519.22</v>
       </c>
       <c r="C65">
-        <v>464</v>
+        <v>747</v>
       </c>
       <c r="D65">
-        <v>440.83</v>
+        <v>1264.86</v>
       </c>
       <c r="E65">
-        <v>206.96</v>
+        <v>182.95</v>
       </c>
       <c r="F65">
-        <v>2690.45</v>
+        <v>8964.57</v>
       </c>
       <c r="G65">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Medical Ophthalmology Service</t>
+          <t>Nuclear Medicine Service</t>
         </is>
       </c>
       <c r="B66">
-        <v>10596.72</v>
+        <v>9033.6</v>
       </c>
       <c r="C66">
-        <v>186</v>
+        <v>301</v>
       </c>
       <c r="D66">
-        <v>323.78</v>
+        <v>240.48</v>
       </c>
       <c r="E66">
-        <v>84.77</v>
+        <v>164.25</v>
       </c>
       <c r="F66">
-        <v>2458.44</v>
+        <v>1313.98</v>
       </c>
       <c r="G66">
-        <v>57</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Gynaecology Service</t>
+          <t>Neurology Service</t>
         </is>
       </c>
       <c r="B67">
-        <v>412862.62</v>
+        <v>393597.39</v>
       </c>
       <c r="C67">
-        <v>457</v>
+        <v>517</v>
       </c>
       <c r="D67">
-        <v>372.41</v>
+        <v>529.3099999999999</v>
       </c>
       <c r="E67">
-        <v>204.79</v>
+        <v>231.53</v>
       </c>
       <c r="F67">
-        <v>4505.45</v>
+        <v>6019.72</v>
       </c>
       <c r="G67">
-        <v>904</v>
+        <v>762</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Gynaecological Oncology Service</t>
+          <t>Rheumatology Service</t>
         </is>
       </c>
       <c r="B68">
-        <v>37050.31</v>
+        <v>995267.64</v>
       </c>
       <c r="C68">
-        <v>322</v>
+        <v>454</v>
       </c>
       <c r="D68">
-        <v>308.33</v>
+        <v>545.97</v>
       </c>
       <c r="E68">
-        <v>186.18</v>
+        <v>190.08</v>
       </c>
       <c r="F68">
-        <v>2606.55</v>
+        <v>11024.74</v>
       </c>
       <c r="G68">
-        <v>115</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Physiotherapy Service</t>
+          <t>Paediatric Service</t>
         </is>
       </c>
       <c r="B69">
-        <v>2891056.79</v>
+        <v>627.46</v>
       </c>
       <c r="C69">
-        <v>540</v>
+        <v>314</v>
       </c>
       <c r="D69">
-        <v>556.35</v>
+        <v>0</v>
       </c>
       <c r="E69">
-        <v>109.16</v>
+        <v>313.73</v>
       </c>
       <c r="F69">
-        <v>11898.25</v>
+        <v>313.73</v>
       </c>
       <c r="G69">
-        <v>5351</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Occupational Therapy Service</t>
+          <t>Elderly Medicine Service</t>
         </is>
       </c>
       <c r="B70">
-        <v>385444.31</v>
+        <v>1155383.12</v>
       </c>
       <c r="C70">
-        <v>626</v>
+        <v>859</v>
       </c>
       <c r="D70">
-        <v>956.04</v>
+        <v>1529.23</v>
       </c>
       <c r="E70">
-        <v>140.31</v>
+        <v>360.16</v>
       </c>
       <c r="F70">
-        <v>11786.43</v>
+        <v>33134.43</v>
       </c>
       <c r="G70">
-        <v>616</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Podiatry Service</t>
+          <t>Dental Medicine Service</t>
         </is>
       </c>
       <c r="B71">
-        <v>149527.09</v>
+        <v>26904.46</v>
       </c>
       <c r="C71">
-        <v>402</v>
+        <v>464</v>
       </c>
       <c r="D71">
-        <v>450.31</v>
+        <v>440.83</v>
       </c>
       <c r="E71">
-        <v>99.09</v>
+        <v>206.96</v>
       </c>
       <c r="F71">
-        <v>3170.89</v>
+        <v>2690.45</v>
       </c>
       <c r="G71">
-        <v>372</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Dietetics Service</t>
+          <t>Medical Ophthalmology Service</t>
         </is>
       </c>
       <c r="B72">
-        <v>93077.5</v>
+        <v>10596.72</v>
       </c>
       <c r="C72">
-        <v>406</v>
+        <v>186</v>
       </c>
       <c r="D72">
-        <v>522.2</v>
+        <v>323.78</v>
       </c>
       <c r="E72">
-        <v>149.64</v>
+        <v>84.77</v>
       </c>
       <c r="F72">
-        <v>5686.41</v>
+        <v>2458.44</v>
       </c>
       <c r="G72">
-        <v>229</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Orthoptics Service</t>
+          <t>Obstetrics Service</t>
         </is>
       </c>
       <c r="B73">
-        <v>35717.58</v>
+        <v>774.02</v>
       </c>
       <c r="C73">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D73">
-        <v>142.62</v>
+        <v>0</v>
       </c>
       <c r="E73">
-        <v>108.9</v>
+        <v>193.51</v>
       </c>
       <c r="F73">
-        <v>871.16</v>
+        <v>193.51</v>
       </c>
       <c r="G73">
-        <v>178</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Clinical Psychology Service</t>
+          <t>Gynaecology Service</t>
         </is>
       </c>
       <c r="B74">
-        <v>31724.2</v>
+        <v>412862.62</v>
       </c>
       <c r="C74">
-        <v>1670</v>
+        <v>457</v>
       </c>
       <c r="D74">
-        <v>2514.26</v>
+        <v>372.41</v>
       </c>
       <c r="E74">
-        <v>327.05</v>
+        <v>204.79</v>
       </c>
       <c r="F74">
-        <v>11446.88</v>
+        <v>4505.45</v>
       </c>
       <c r="G74">
-        <v>19</v>
+        <v>904</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Prosthetics Service</t>
+          <t>Gynaecological Oncology Service</t>
         </is>
       </c>
       <c r="B75">
-        <v>644.63</v>
+        <v>37050.31</v>
       </c>
       <c r="C75">
-        <v>161</v>
+        <v>322</v>
       </c>
       <c r="D75">
-        <v>62.03</v>
+        <v>308.33</v>
       </c>
       <c r="E75">
-        <v>107.44</v>
+        <v>186.18</v>
       </c>
       <c r="F75">
-        <v>214.88</v>
+        <v>2606.55</v>
       </c>
       <c r="G75">
-        <v>4</v>
+        <v>115</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Orthotics Service</t>
+          <t>Physiotherapy Service</t>
         </is>
       </c>
       <c r="B76">
-        <v>88005.89</v>
+        <v>2891056.79</v>
       </c>
       <c r="C76">
-        <v>349</v>
+        <v>540</v>
       </c>
       <c r="D76">
-        <v>273.51</v>
+        <v>556.35</v>
       </c>
       <c r="E76">
-        <v>182.96</v>
+        <v>109.16</v>
       </c>
       <c r="F76">
-        <v>2195.57</v>
+        <v>11898.25</v>
       </c>
       <c r="G76">
-        <v>252</v>
+        <v>5351</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Optometry Service</t>
+          <t>Occupational Therapy Service</t>
         </is>
       </c>
       <c r="B77">
-        <v>7548.23</v>
+        <v>385444.31</v>
       </c>
       <c r="C77">
-        <v>204</v>
+        <v>626</v>
       </c>
       <c r="D77">
-        <v>125.87</v>
+        <v>956.04</v>
       </c>
       <c r="E77">
-        <v>139.78</v>
+        <v>140.31</v>
       </c>
       <c r="F77">
-        <v>559.13</v>
+        <v>11786.43</v>
       </c>
       <c r="G77">
-        <v>37</v>
+        <v>616</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Podiatric Surgery Service</t>
+          <t>Podiatry Service</t>
         </is>
       </c>
       <c r="B78">
-        <v>6885.15</v>
+        <v>149527.09</v>
       </c>
       <c r="C78">
-        <v>459</v>
+        <v>402</v>
       </c>
       <c r="D78">
-        <v>371.56</v>
+        <v>450.31</v>
       </c>
       <c r="E78">
-        <v>156.48</v>
+        <v>99.09</v>
       </c>
       <c r="F78">
-        <v>1408.33</v>
+        <v>3170.89</v>
       </c>
       <c r="G78">
-        <v>15</v>
+        <v>372</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Learning Disability Service</t>
+          <t>Dietetics Service</t>
         </is>
       </c>
       <c r="B79">
-        <v>4301.37</v>
+        <v>93077.5</v>
       </c>
       <c r="C79">
-        <v>105</v>
+        <v>406</v>
       </c>
       <c r="D79">
-        <v>180.72</v>
+        <v>522.2</v>
       </c>
       <c r="E79">
-        <v>12.88</v>
+        <v>149.64</v>
       </c>
       <c r="F79">
-        <v>888.61</v>
+        <v>5686.41</v>
       </c>
       <c r="G79">
-        <v>41</v>
+        <v>229</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Child and Adolescent Psychiatry Service</t>
+          <t>Orthoptics Service</t>
         </is>
       </c>
       <c r="B80">
-        <v>1082.16</v>
+        <v>35717.58</v>
       </c>
       <c r="C80">
-        <v>1082</v>
+        <v>201</v>
+      </c>
+      <c r="D80">
+        <v>142.62</v>
       </c>
       <c r="E80">
-        <v>1082.16</v>
+        <v>108.9</v>
       </c>
       <c r="F80">
-        <v>1082.16</v>
+        <v>871.16</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>178</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Medical Psychotherapy Service</t>
+          <t>Clinical Psychology Service</t>
         </is>
       </c>
       <c r="B81">
-        <v>5037.57</v>
+        <v>31724.2</v>
       </c>
       <c r="C81">
-        <v>1679</v>
+        <v>1670</v>
       </c>
       <c r="D81">
-        <v>1454.22</v>
+        <v>2514.26</v>
       </c>
       <c r="E81">
-        <v>839.59</v>
+        <v>327.05</v>
       </c>
       <c r="F81">
-        <v>3358.38</v>
+        <v>11446.88</v>
       </c>
       <c r="G81">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Old Age Psychiatry Service</t>
+          <t>Prosthetics Service</t>
         </is>
       </c>
       <c r="B82">
-        <v>495031.22</v>
+        <v>644.63</v>
       </c>
       <c r="C82">
-        <v>1067</v>
+        <v>161</v>
       </c>
       <c r="D82">
-        <v>1924.65</v>
+        <v>62.03</v>
       </c>
       <c r="E82">
-        <v>348.12</v>
+        <v>107.44</v>
       </c>
       <c r="F82">
-        <v>22279.89</v>
+        <v>214.88</v>
       </c>
       <c r="G82">
-        <v>464</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Liaison Psychiatry Service</t>
+          <t>Orthotics Service</t>
         </is>
       </c>
       <c r="B83">
-        <v>32896.14</v>
+        <v>88005.89</v>
       </c>
       <c r="C83">
-        <v>1175</v>
+        <v>349</v>
       </c>
       <c r="D83">
-        <v>1277.71</v>
+        <v>273.51</v>
       </c>
       <c r="E83">
-        <v>373.82</v>
+        <v>182.96</v>
       </c>
       <c r="F83">
-        <v>5233.48</v>
+        <v>2195.57</v>
       </c>
       <c r="G83">
-        <v>28</v>
+        <v>252</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Clinical Oncology Service</t>
+          <t>Optometry Service</t>
         </is>
       </c>
       <c r="B84">
-        <v>86292.23</v>
+        <v>7548.23</v>
       </c>
       <c r="C84">
-        <v>649</v>
+        <v>204</v>
       </c>
       <c r="D84">
-        <v>973.4299999999999</v>
+        <v>125.87</v>
       </c>
       <c r="E84">
-        <v>147.26</v>
+        <v>139.78</v>
       </c>
       <c r="F84">
-        <v>5743</v>
+        <v>559.13</v>
       </c>
       <c r="G84">
-        <v>133</v>
+        <v>37</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Interventional Radiology Service</t>
+          <t>Podiatric Surgery Service</t>
         </is>
       </c>
       <c r="B85">
-        <v>25587.09</v>
+        <v>6885.15</v>
       </c>
       <c r="C85">
-        <v>149</v>
+        <v>459</v>
       </c>
       <c r="D85">
-        <v>37.49</v>
+        <v>371.56</v>
       </c>
       <c r="E85">
-        <v>139.82</v>
+        <v>156.48</v>
       </c>
       <c r="F85">
-        <v>419.46</v>
+        <v>1408.33</v>
       </c>
       <c r="G85">
-        <v>172</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging Service</t>
+          <t>Learning Disability Service</t>
         </is>
       </c>
       <c r="B86">
-        <v>320865.39</v>
+        <v>4301.37</v>
       </c>
       <c r="C86">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D86">
-        <v>102.22</v>
+        <v>180.72</v>
       </c>
       <c r="E86">
-        <v>56.31</v>
+        <v>12.88</v>
       </c>
       <c r="F86">
-        <v>2308.79</v>
+        <v>888.61</v>
       </c>
       <c r="G86">
-        <v>2933</v>
+        <v>41</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Chemical Pathology Service</t>
+          <t>Adult Mental Health Service</t>
         </is>
       </c>
       <c r="B87">
-        <v>12605.24</v>
+        <v>496483.6</v>
       </c>
       <c r="C87">
-        <v>341</v>
+        <v>2586</v>
       </c>
       <c r="D87">
-        <v>227.19</v>
+        <v>5754.38</v>
       </c>
       <c r="E87">
-        <v>124.8</v>
+        <v>482.02</v>
       </c>
       <c r="F87">
-        <v>873.63</v>
+        <v>54468.59</v>
       </c>
       <c r="G87">
-        <v>37</v>
+        <v>192</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>Child and Adolescent Psychiatry Service</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>1082.16</v>
+      </c>
+      <c r="C88">
+        <v>1082</v>
+      </c>
+      <c r="E88">
+        <v>1082.16</v>
+      </c>
+      <c r="F88">
+        <v>1082.16</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Medical Psychotherapy Service</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>5037.57</v>
+      </c>
+      <c r="C89">
+        <v>1679</v>
+      </c>
+      <c r="D89">
+        <v>1454.22</v>
+      </c>
+      <c r="E89">
+        <v>839.59</v>
+      </c>
+      <c r="F89">
+        <v>3358.38</v>
+      </c>
+      <c r="G89">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Old Age Psychiatry Service</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>495031.22</v>
+      </c>
+      <c r="C90">
+        <v>1067</v>
+      </c>
+      <c r="D90">
+        <v>1924.65</v>
+      </c>
+      <c r="E90">
+        <v>348.12</v>
+      </c>
+      <c r="F90">
+        <v>22279.89</v>
+      </c>
+      <c r="G90">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Liaison Psychiatry Service</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>32896.14</v>
+      </c>
+      <c r="C91">
+        <v>1175</v>
+      </c>
+      <c r="D91">
+        <v>1277.71</v>
+      </c>
+      <c r="E91">
+        <v>373.82</v>
+      </c>
+      <c r="F91">
+        <v>5233.48</v>
+      </c>
+      <c r="G91">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Clinical Oncology Service</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>86292.23</v>
+      </c>
+      <c r="C92">
+        <v>649</v>
+      </c>
+      <c r="D92">
+        <v>973.4299999999999</v>
+      </c>
+      <c r="E92">
+        <v>147.26</v>
+      </c>
+      <c r="F92">
+        <v>5743</v>
+      </c>
+      <c r="G92">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Interventional Radiology Service</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>25587.09</v>
+      </c>
+      <c r="C93">
+        <v>149</v>
+      </c>
+      <c r="D93">
+        <v>37.49</v>
+      </c>
+      <c r="E93">
+        <v>139.82</v>
+      </c>
+      <c r="F93">
+        <v>419.46</v>
+      </c>
+      <c r="G93">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Diagnostic Imaging Service</t>
+        </is>
+      </c>
+      <c r="B94">
+        <v>320865.39</v>
+      </c>
+      <c r="C94">
+        <v>109</v>
+      </c>
+      <c r="D94">
+        <v>102.22</v>
+      </c>
+      <c r="E94">
+        <v>56.31</v>
+      </c>
+      <c r="F94">
+        <v>2308.79</v>
+      </c>
+      <c r="G94">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Chemical Pathology Service</t>
+        </is>
+      </c>
+      <c r="B95">
+        <v>12605.24</v>
+      </c>
+      <c r="C95">
+        <v>341</v>
+      </c>
+      <c r="D95">
+        <v>227.19</v>
+      </c>
+      <c r="E95">
+        <v>124.8</v>
+      </c>
+      <c r="F95">
+        <v>873.63</v>
+      </c>
+      <c r="G95">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
           <t>Audiology Service</t>
         </is>
       </c>
-      <c r="B88">
+      <c r="B96">
         <v>227761.62</v>
       </c>
-      <c r="C88">
+      <c r="C96">
         <v>289</v>
       </c>
-      <c r="D88">
+      <c r="D96">
         <v>216.91</v>
       </c>
-      <c r="E88">
+      <c r="E96">
         <v>120.96</v>
       </c>
-      <c r="F88">
+      <c r="F96">
         <v>2540.09</v>
       </c>
-      <c r="G88">
+      <c r="G96">
         <v>787</v>
       </c>
     </row>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_costs_by_tretspef-Users_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_costs_by_tretspef-Users_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -569,1117 +569,2139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ophthalmology Service</t>
+          <t>Trauma and Orthopaedic Service</t>
         </is>
       </c>
       <c r="B9">
-        <v>18377345.64</v>
+        <v>9047683.6</v>
       </c>
       <c r="C9">
-        <v>943</v>
+        <v>544</v>
       </c>
       <c r="D9">
-        <v>1121.51</v>
+        <v>418.54</v>
       </c>
       <c r="E9">
-        <v>149.69</v>
+        <v>166.51</v>
       </c>
       <c r="F9">
-        <v>31883.28</v>
+        <v>16984.39</v>
       </c>
       <c r="G9">
-        <v>19478</v>
+        <v>16624</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Oral Surgery Service</t>
+          <t>Ear Nose and Throat Service</t>
         </is>
       </c>
       <c r="B10">
-        <v>147842.09</v>
+        <v>394012.57</v>
       </c>
       <c r="C10">
-        <v>422</v>
+        <v>333</v>
       </c>
       <c r="D10">
-        <v>313.11</v>
+        <v>764.05</v>
       </c>
       <c r="E10">
-        <v>219.03</v>
+        <v>160.89</v>
       </c>
       <c r="F10">
-        <v>2847.33</v>
+        <v>24454.84</v>
       </c>
       <c r="G10">
-        <v>350</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Restorative Dentistry Service</t>
+          <t>Ophthalmology Service</t>
         </is>
       </c>
       <c r="B11">
-        <v>102574.71</v>
+        <v>1774536.8</v>
       </c>
       <c r="C11">
-        <v>1193</v>
+        <v>532</v>
       </c>
       <c r="D11">
-        <v>1206.8</v>
+        <v>621.86</v>
       </c>
       <c r="E11">
-        <v>309.89</v>
+        <v>149.69</v>
       </c>
       <c r="F11">
-        <v>4648.4</v>
+        <v>5987.47</v>
       </c>
       <c r="G11">
-        <v>86</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Orthodontic Service</t>
+          <t>Oral Surgery Service</t>
         </is>
       </c>
       <c r="B12">
-        <v>647.3200000000001</v>
+        <v>147842.09</v>
       </c>
       <c r="C12">
-        <v>216</v>
+        <v>422</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>313.11</v>
       </c>
       <c r="E12">
-        <v>215.77</v>
+        <v>219.03</v>
       </c>
       <c r="F12">
-        <v>215.77</v>
+        <v>2847.33</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Maxillofacial Surgery Service</t>
+          <t>Restorative Dentistry Service</t>
         </is>
       </c>
       <c r="B13">
-        <v>102923.73</v>
+        <v>102574.71</v>
       </c>
       <c r="C13">
-        <v>399</v>
+        <v>1193</v>
       </c>
       <c r="D13">
-        <v>381.13</v>
+        <v>1206.8</v>
       </c>
       <c r="E13">
-        <v>192.02</v>
+        <v>309.89</v>
       </c>
       <c r="F13">
-        <v>3264.37</v>
+        <v>4648.4</v>
       </c>
       <c r="G13">
-        <v>258</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Neurosurgical Service</t>
+          <t>Orthodontic Service</t>
         </is>
       </c>
       <c r="B14">
-        <v>143525.49</v>
+        <v>647.3200000000001</v>
       </c>
       <c r="C14">
-        <v>477</v>
+        <v>216</v>
       </c>
       <c r="D14">
-        <v>453.98</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>217.13</v>
+        <v>215.77</v>
       </c>
       <c r="F14">
-        <v>4776.95</v>
+        <v>215.77</v>
       </c>
       <c r="G14">
-        <v>301</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cardiac Surgery Service</t>
+          <t>Maxillofacial Surgery Service</t>
         </is>
       </c>
       <c r="B15">
-        <v>16616.76</v>
+        <v>102923.73</v>
       </c>
       <c r="C15">
-        <v>475</v>
+        <v>399</v>
       </c>
       <c r="D15">
-        <v>275.14</v>
+        <v>381.13</v>
       </c>
       <c r="E15">
-        <v>272.41</v>
+        <v>192.02</v>
       </c>
       <c r="F15">
-        <v>1362.03</v>
+        <v>3264.37</v>
       </c>
       <c r="G15">
-        <v>35</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Thoracic Surgery Service</t>
+          <t>Neurosurgical Service</t>
         </is>
       </c>
       <c r="B16">
-        <v>8521.469999999999</v>
+        <v>143525.49</v>
       </c>
       <c r="C16">
-        <v>406</v>
+        <v>477</v>
       </c>
       <c r="D16">
-        <v>208.19</v>
+        <v>453.98</v>
       </c>
       <c r="E16">
-        <v>224.25</v>
+        <v>217.13</v>
       </c>
       <c r="F16">
-        <v>897</v>
+        <v>4776.95</v>
       </c>
       <c r="G16">
-        <v>21</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cardiothoracic Transplantation Service</t>
+          <t>Plastic Surgery Service</t>
         </is>
       </c>
       <c r="B17">
-        <v>30273.54</v>
+        <v>173178.68</v>
       </c>
       <c r="C17">
-        <v>10091</v>
+        <v>485</v>
       </c>
       <c r="D17">
-        <v>8484.709999999999</v>
+        <v>489.95</v>
       </c>
       <c r="E17">
-        <v>540.6</v>
+        <v>163.22</v>
       </c>
       <c r="F17">
-        <v>16758.57</v>
+        <v>3264.44</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>357</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pain Management Service</t>
+          <t>Burns Care Service</t>
         </is>
       </c>
       <c r="B18">
-        <v>260631.76</v>
+        <v>7434.08</v>
       </c>
       <c r="C18">
-        <v>551</v>
+        <v>1239</v>
       </c>
       <c r="D18">
-        <v>534.88</v>
+        <v>939.53</v>
       </c>
       <c r="E18">
-        <v>219.76</v>
+        <v>154.88</v>
       </c>
       <c r="F18">
-        <v>3516.11</v>
+        <v>2323.15</v>
       </c>
       <c r="G18">
-        <v>473</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Paediatric Trauma and Orthopaedic Service</t>
+          <t>Cardiothoracic Surgery Service</t>
         </is>
       </c>
       <c r="B19">
-        <v>3637.93</v>
+        <v>16243.37</v>
       </c>
       <c r="C19">
-        <v>243</v>
+        <v>492</v>
       </c>
       <c r="D19">
-        <v>113.3</v>
+        <v>333.44</v>
       </c>
       <c r="E19">
-        <v>202.11</v>
+        <v>306.48</v>
       </c>
       <c r="F19">
-        <v>606.3200000000001</v>
+        <v>1532.39</v>
       </c>
       <c r="G19">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Paediatric Ophthalmology Service</t>
+          <t>Cardiac Surgery Service</t>
         </is>
       </c>
       <c r="B20">
-        <v>2505</v>
+        <v>16616.76</v>
       </c>
       <c r="C20">
-        <v>358</v>
+        <v>475</v>
       </c>
       <c r="D20">
-        <v>334.74</v>
+        <v>275.14</v>
       </c>
       <c r="E20">
-        <v>156.56</v>
+        <v>272.41</v>
       </c>
       <c r="F20">
-        <v>1095.94</v>
+        <v>1362.03</v>
       </c>
       <c r="G20">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gastroenterology Service</t>
+          <t>Thoracic Surgery Service</t>
         </is>
       </c>
       <c r="B21">
-        <v>311605.05</v>
+        <v>8521.469999999999</v>
       </c>
       <c r="C21">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="D21">
-        <v>299.23</v>
+        <v>208.19</v>
       </c>
       <c r="E21">
-        <v>171.87</v>
+        <v>224.25</v>
       </c>
       <c r="F21">
-        <v>3437.45</v>
+        <v>897</v>
       </c>
       <c r="G21">
-        <v>949</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Endocrinology Service</t>
+          <t>Cardiothoracic Transplantation Service</t>
         </is>
       </c>
       <c r="B22">
-        <v>125108.89</v>
+        <v>30273.54</v>
       </c>
       <c r="C22">
-        <v>465</v>
+        <v>10091</v>
       </c>
       <c r="D22">
-        <v>384.1</v>
+        <v>8484.709999999999</v>
       </c>
       <c r="E22">
-        <v>213.5</v>
+        <v>540.6</v>
       </c>
       <c r="F22">
-        <v>3202.45</v>
+        <v>16758.57</v>
       </c>
       <c r="G22">
-        <v>269</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Clinical Pharmacology Service</t>
+          <t>Emergency Medicine Service</t>
         </is>
       </c>
       <c r="B23">
-        <v>8800.27</v>
+        <v>55300.41</v>
       </c>
       <c r="C23">
-        <v>1257</v>
+        <v>206</v>
       </c>
       <c r="D23">
-        <v>1112.56</v>
+        <v>171.02</v>
       </c>
       <c r="E23">
-        <v>517.66</v>
+        <v>146.3</v>
       </c>
       <c r="F23">
-        <v>3623.64</v>
+        <v>1609.27</v>
       </c>
       <c r="G23">
-        <v>7</v>
+        <v>268</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hepatology Service</t>
+          <t>Anaesthetic Service</t>
         </is>
       </c>
       <c r="B24">
-        <v>25934.04</v>
+        <v>72269.62</v>
       </c>
       <c r="C24">
-        <v>370</v>
+        <v>193</v>
       </c>
       <c r="D24">
-        <v>207.7</v>
+        <v>93.94</v>
       </c>
       <c r="E24">
-        <v>180.1</v>
+        <v>150.56</v>
       </c>
       <c r="F24">
-        <v>900.49</v>
+        <v>752.8099999999999</v>
       </c>
       <c r="G24">
-        <v>70</v>
+        <v>375</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Diabetes Service</t>
+          <t>Pain Management Service</t>
         </is>
       </c>
       <c r="B25">
-        <v>194559.64</v>
+        <v>260631.76</v>
       </c>
       <c r="C25">
-        <v>726</v>
+        <v>551</v>
       </c>
       <c r="D25">
-        <v>1093.92</v>
+        <v>534.88</v>
       </c>
       <c r="E25">
-        <v>209.43</v>
+        <v>219.76</v>
       </c>
       <c r="F25">
-        <v>11518.6</v>
+        <v>3516.11</v>
       </c>
       <c r="G25">
-        <v>268</v>
+        <v>473</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Blood and Marrow Transplantation Service</t>
+          <t>Paediatric Trauma and Orthopaedic Service</t>
         </is>
       </c>
       <c r="B26">
-        <v>376.38</v>
+        <v>3637.93</v>
       </c>
       <c r="C26">
-        <v>376</v>
+        <v>243</v>
+      </c>
+      <c r="D26">
+        <v>113.3</v>
       </c>
       <c r="E26">
-        <v>376.38</v>
+        <v>202.11</v>
       </c>
       <c r="F26">
-        <v>376.38</v>
+        <v>606.3200000000001</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Clinical Genetics Service</t>
+          <t>Paediatric Ear Nose and Throat Service</t>
         </is>
       </c>
       <c r="B27">
-        <v>5006.43</v>
+        <v>168.99</v>
       </c>
       <c r="C27">
-        <v>501</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="E27">
-        <v>500.64</v>
+        <v>168.99</v>
       </c>
       <c r="F27">
-        <v>500.64</v>
+        <v>168.99</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Clinical Immunology Service</t>
+          <t>Paediatric Ophthalmology Service</t>
         </is>
       </c>
       <c r="B28">
-        <v>10011.77</v>
+        <v>2505</v>
       </c>
       <c r="C28">
-        <v>834</v>
+        <v>358</v>
       </c>
       <c r="D28">
-        <v>684.59</v>
+        <v>334.74</v>
       </c>
       <c r="E28">
-        <v>312.87</v>
+        <v>156.56</v>
       </c>
       <c r="F28">
-        <v>2190.07</v>
+        <v>1095.94</v>
       </c>
       <c r="G28">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Intermediate Care Service</t>
+          <t>General Internal Medicine Service</t>
         </is>
       </c>
       <c r="B29">
-        <v>272785.14</v>
+        <v>746212.92</v>
       </c>
       <c r="C29">
-        <v>1624</v>
+        <v>621</v>
       </c>
       <c r="D29">
-        <v>2747.29</v>
+        <v>2061.1</v>
       </c>
       <c r="E29">
-        <v>121.89</v>
+        <v>166.45</v>
       </c>
       <c r="F29">
-        <v>18039.41</v>
+        <v>33457.24</v>
       </c>
       <c r="G29">
-        <v>168</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cardiology Service</t>
+          <t>Gastroenterology Service</t>
         </is>
       </c>
       <c r="B30">
-        <v>747392.24</v>
+        <v>311605.05</v>
       </c>
       <c r="C30">
-        <v>371</v>
+        <v>328</v>
       </c>
       <c r="D30">
-        <v>355.96</v>
+        <v>299.23</v>
       </c>
       <c r="E30">
-        <v>173.45</v>
+        <v>171.87</v>
       </c>
       <c r="F30">
-        <v>5030.02</v>
+        <v>3437.45</v>
       </c>
       <c r="G30">
-        <v>2015</v>
+        <v>949</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Clinical Microbiology Service</t>
+          <t>Endocrinology Service</t>
         </is>
       </c>
       <c r="B31">
-        <v>319.64</v>
+        <v>125108.89</v>
       </c>
       <c r="C31">
-        <v>46</v>
+        <v>465</v>
       </c>
       <c r="D31">
-        <v>25.15</v>
+        <v>384.1</v>
       </c>
       <c r="E31">
-        <v>31.96</v>
+        <v>213.5</v>
       </c>
       <c r="F31">
-        <v>95.89</v>
+        <v>3202.45</v>
       </c>
       <c r="G31">
-        <v>7</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Anticoagulant Service</t>
+          <t>Clinical Haematology Service</t>
         </is>
       </c>
       <c r="B32">
-        <v>236453.98</v>
+        <v>303949.98</v>
       </c>
       <c r="C32">
-        <v>793</v>
+        <v>637</v>
       </c>
       <c r="D32">
-        <v>927.79</v>
+        <v>770.4299999999999</v>
       </c>
       <c r="E32">
-        <v>79.45</v>
+        <v>189.97</v>
       </c>
       <c r="F32">
-        <v>4290.5</v>
+        <v>6268.97</v>
       </c>
       <c r="G32">
-        <v>298</v>
+        <v>477</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sport and Exercise Medicine Service</t>
+          <t>Clinical Pharmacology Service</t>
         </is>
       </c>
       <c r="B33">
-        <v>683.71</v>
+        <v>8800.27</v>
       </c>
       <c r="C33">
-        <v>684</v>
+        <v>1257</v>
+      </c>
+      <c r="D33">
+        <v>1112.56</v>
       </c>
       <c r="E33">
-        <v>683.71</v>
+        <v>517.66</v>
       </c>
       <c r="F33">
-        <v>683.71</v>
+        <v>3623.64</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Stroke Medicine Service</t>
+          <t>Hepatology Service</t>
         </is>
       </c>
       <c r="B34">
-        <v>21021.96</v>
+        <v>25934.04</v>
       </c>
       <c r="C34">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D34">
-        <v>212.92</v>
+        <v>207.7</v>
       </c>
       <c r="E34">
-        <v>280.29</v>
+        <v>180.1</v>
       </c>
       <c r="F34">
-        <v>1681.76</v>
+        <v>900.49</v>
       </c>
       <c r="G34">
-        <v>57</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Dermatology Service</t>
+          <t>Diabetes Service</t>
         </is>
       </c>
       <c r="B35">
-        <v>466519.09</v>
+        <v>194559.64</v>
       </c>
       <c r="C35">
-        <v>417</v>
+        <v>726</v>
       </c>
       <c r="D35">
-        <v>688.8200000000001</v>
+        <v>1093.92</v>
       </c>
       <c r="E35">
-        <v>164.56</v>
+        <v>209.43</v>
       </c>
       <c r="F35">
-        <v>11354.43</v>
+        <v>11518.6</v>
       </c>
       <c r="G35">
-        <v>1118</v>
+        <v>268</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Respiratory Physiology Service</t>
+          <t>Blood and Marrow Transplantation Service</t>
         </is>
       </c>
       <c r="B36">
-        <v>29088.77</v>
+        <v>376.38</v>
       </c>
       <c r="C36">
-        <v>233</v>
-      </c>
-      <c r="D36">
-        <v>195.66</v>
+        <v>376</v>
       </c>
       <c r="E36">
-        <v>129.28</v>
+        <v>376.38</v>
       </c>
       <c r="F36">
-        <v>1292.83</v>
+        <v>376.38</v>
       </c>
       <c r="G36">
-        <v>125</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tropical Medicine Service</t>
+          <t>Haemophilia Service</t>
         </is>
       </c>
       <c r="B37">
-        <v>811.04</v>
+        <v>6826.55</v>
       </c>
       <c r="C37">
-        <v>270</v>
+        <v>853</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>544.6</v>
       </c>
       <c r="E37">
-        <v>270.35</v>
+        <v>401.56</v>
       </c>
       <c r="F37">
-        <v>270.35</v>
+        <v>2007.81</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Genitourinary Medicine Service</t>
+          <t>Clinical Genetics Service</t>
         </is>
       </c>
       <c r="B38">
-        <v>2330.95</v>
+        <v>5006.43</v>
       </c>
       <c r="C38">
-        <v>388</v>
+        <v>501</v>
       </c>
       <c r="D38">
-        <v>247.73</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>211.9</v>
+        <v>500.64</v>
       </c>
       <c r="F38">
-        <v>847.62</v>
+        <v>500.64</v>
       </c>
       <c r="G38">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Renal Medicine Service</t>
+          <t>Clinical Immunology and Allergy Service</t>
         </is>
       </c>
       <c r="B39">
-        <v>209139.02</v>
+        <v>12488.84</v>
       </c>
       <c r="C39">
-        <v>807</v>
+        <v>624</v>
       </c>
       <c r="D39">
-        <v>902.45</v>
+        <v>482.13</v>
       </c>
       <c r="E39">
-        <v>218.08</v>
+        <v>265.72</v>
       </c>
       <c r="F39">
-        <v>5888.17</v>
+        <v>1860.04</v>
       </c>
       <c r="G39">
-        <v>259</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Medical Oncology Service</t>
+          <t>Rehabilitation Medicine Service</t>
         </is>
       </c>
       <c r="B40">
-        <v>54519.22</v>
+        <v>400658.39</v>
       </c>
       <c r="C40">
-        <v>747</v>
+        <v>1260</v>
       </c>
       <c r="D40">
-        <v>1264.86</v>
+        <v>1801.28</v>
       </c>
       <c r="E40">
-        <v>182.95</v>
+        <v>290.75</v>
       </c>
       <c r="F40">
-        <v>8964.57</v>
+        <v>18608.23</v>
       </c>
       <c r="G40">
-        <v>73</v>
+        <v>318</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nuclear Medicine Service</t>
+          <t>Palliative Medicine Service</t>
         </is>
       </c>
       <c r="B41">
-        <v>9033.6</v>
+        <v>51818.04</v>
       </c>
       <c r="C41">
-        <v>301</v>
+        <v>1524</v>
       </c>
       <c r="D41">
-        <v>240.48</v>
+        <v>3043.4</v>
       </c>
       <c r="E41">
-        <v>164.25</v>
+        <v>244.42</v>
       </c>
       <c r="F41">
-        <v>1313.98</v>
+        <v>16376.46</v>
       </c>
       <c r="G41">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Neurology Service</t>
+          <t>Clinical Immunology Service</t>
         </is>
       </c>
       <c r="B42">
-        <v>393597.39</v>
+        <v>10011.77</v>
       </c>
       <c r="C42">
-        <v>517</v>
+        <v>834</v>
       </c>
       <c r="D42">
-        <v>529.3099999999999</v>
+        <v>684.59</v>
       </c>
       <c r="E42">
-        <v>231.53</v>
+        <v>312.87</v>
       </c>
       <c r="F42">
-        <v>6019.72</v>
+        <v>2190.07</v>
       </c>
       <c r="G42">
-        <v>762</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Rheumatology Service</t>
+          <t>Allergy Service</t>
         </is>
       </c>
       <c r="B43">
-        <v>995267.64</v>
+        <v>20138.74</v>
       </c>
       <c r="C43">
-        <v>454</v>
+        <v>1438</v>
       </c>
       <c r="D43">
-        <v>545.97</v>
+        <v>3511.58</v>
       </c>
       <c r="E43">
-        <v>190.08</v>
+        <v>261.54</v>
       </c>
       <c r="F43">
-        <v>11024.74</v>
+        <v>13600.19</v>
       </c>
       <c r="G43">
-        <v>2194</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Elderly Medicine Service</t>
+          <t>Intermediate Care Service</t>
         </is>
       </c>
       <c r="B44">
-        <v>1155383.12</v>
+        <v>274004.02</v>
       </c>
       <c r="C44">
-        <v>859</v>
+        <v>1557</v>
       </c>
       <c r="D44">
-        <v>1529.23</v>
+        <v>2701.36</v>
       </c>
       <c r="E44">
-        <v>360.16</v>
+        <v>121.89</v>
       </c>
       <c r="F44">
-        <v>33134.43</v>
+        <v>18039.41</v>
       </c>
       <c r="G44">
-        <v>1345</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Occupational Therapy Service</t>
+          <t>Cardiology Service</t>
         </is>
       </c>
       <c r="B45">
-        <v>385444.31</v>
+        <v>747392.24</v>
       </c>
       <c r="C45">
-        <v>626</v>
+        <v>371</v>
       </c>
       <c r="D45">
-        <v>956.04</v>
+        <v>355.96</v>
       </c>
       <c r="E45">
-        <v>140.31</v>
+        <v>173.45</v>
       </c>
       <c r="F45">
-        <v>11786.43</v>
+        <v>5030.02</v>
       </c>
       <c r="G45">
-        <v>616</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Podiatry Service</t>
+          <t>Clinical Microbiology Service</t>
         </is>
       </c>
       <c r="B46">
-        <v>149527.09</v>
+        <v>319.64</v>
       </c>
       <c r="C46">
-        <v>402</v>
+        <v>46</v>
       </c>
       <c r="D46">
-        <v>450.31</v>
+        <v>25.15</v>
       </c>
       <c r="E46">
-        <v>99.09</v>
+        <v>31.96</v>
       </c>
       <c r="F46">
-        <v>3170.89</v>
+        <v>95.89</v>
       </c>
       <c r="G46">
-        <v>372</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Orthoptics Service</t>
+          <t>Spinal Injuries Service</t>
         </is>
       </c>
       <c r="B47">
-        <v>35717.58</v>
+        <v>130496.43</v>
       </c>
       <c r="C47">
-        <v>201</v>
+        <v>713</v>
       </c>
       <c r="D47">
-        <v>142.62</v>
+        <v>647.92</v>
       </c>
       <c r="E47">
-        <v>108.9</v>
+        <v>299.99</v>
       </c>
       <c r="F47">
-        <v>871.16</v>
+        <v>4499.88</v>
       </c>
       <c r="G47">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Clinical Psychology Service</t>
+          <t>Anticoagulant Service</t>
         </is>
       </c>
       <c r="B48">
-        <v>31724.2</v>
+        <v>236453.98</v>
       </c>
       <c r="C48">
-        <v>1670</v>
+        <v>793</v>
       </c>
       <c r="D48">
-        <v>2514.26</v>
+        <v>927.79</v>
       </c>
       <c r="E48">
-        <v>327.05</v>
+        <v>79.45</v>
       </c>
       <c r="F48">
-        <v>11446.88</v>
+        <v>4290.5</v>
       </c>
       <c r="G48">
-        <v>19</v>
+        <v>298</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Optometry Service</t>
+          <t>Sport and Exercise Medicine Service</t>
         </is>
       </c>
       <c r="B49">
-        <v>7548.23</v>
+        <v>683.71</v>
       </c>
       <c r="C49">
-        <v>204</v>
-      </c>
-      <c r="D49">
-        <v>125.87</v>
+        <v>684</v>
       </c>
       <c r="E49">
-        <v>139.78</v>
+        <v>683.71</v>
       </c>
       <c r="F49">
-        <v>559.13</v>
+        <v>683.71</v>
       </c>
       <c r="G49">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Child and Adolescent Psychiatry Service</t>
+          <t>Cardiac Rehabilitation Service</t>
         </is>
       </c>
       <c r="B50">
-        <v>1082.16</v>
+        <v>10961.17</v>
       </c>
       <c r="C50">
-        <v>1082</v>
+        <v>1096</v>
+      </c>
+      <c r="D50">
+        <v>830.1900000000001</v>
       </c>
       <c r="E50">
-        <v>1082.16</v>
+        <v>105.4</v>
       </c>
       <c r="F50">
-        <v>1082.16</v>
+        <v>2634.9</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Medical Psychotherapy Service</t>
+          <t>Stroke Medicine Service</t>
         </is>
       </c>
       <c r="B51">
-        <v>5037.57</v>
+        <v>21021.96</v>
       </c>
       <c r="C51">
-        <v>1679</v>
+        <v>369</v>
       </c>
       <c r="D51">
-        <v>1454.22</v>
+        <v>212.92</v>
       </c>
       <c r="E51">
-        <v>839.59</v>
+        <v>280.29</v>
       </c>
       <c r="F51">
-        <v>3358.38</v>
+        <v>1681.76</v>
       </c>
       <c r="G51">
-        <v>3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Interventional Radiology Service</t>
+          <t>Transient Ischaemic Attack Service</t>
         </is>
       </c>
       <c r="B52">
-        <v>42505.33</v>
+        <v>38769.37</v>
       </c>
       <c r="C52">
-        <v>169</v>
+        <v>334</v>
       </c>
       <c r="D52">
-        <v>79</v>
+        <v>139.53</v>
       </c>
       <c r="E52">
-        <v>139.82</v>
+        <v>274.96</v>
       </c>
       <c r="F52">
-        <v>559.28</v>
+        <v>1099.84</v>
       </c>
       <c r="G52">
-        <v>251</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Dermatology Service</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>466519.09</v>
+      </c>
+      <c r="C53">
+        <v>417</v>
+      </c>
+      <c r="D53">
+        <v>688.8200000000001</v>
+      </c>
+      <c r="E53">
+        <v>164.56</v>
+      </c>
+      <c r="F53">
+        <v>11354.43</v>
+      </c>
+      <c r="G53">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Congenital Heart Disease Service</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>966.65</v>
+      </c>
+      <c r="C54">
+        <v>483</v>
+      </c>
+      <c r="D54">
+        <v>455.68</v>
+      </c>
+      <c r="E54">
+        <v>161.11</v>
+      </c>
+      <c r="F54">
+        <v>805.54</v>
+      </c>
+      <c r="G54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Respiratory Medicine Service</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>496405.91</v>
+      </c>
+      <c r="C55">
+        <v>573</v>
+      </c>
+      <c r="D55">
+        <v>805.53</v>
+      </c>
+      <c r="E55">
+        <v>198.25</v>
+      </c>
+      <c r="F55">
+        <v>13282.43</v>
+      </c>
+      <c r="G55">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Respiratory Physiology Service</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>29088.77</v>
+      </c>
+      <c r="C56">
+        <v>233</v>
+      </c>
+      <c r="D56">
+        <v>195.66</v>
+      </c>
+      <c r="E56">
+        <v>129.28</v>
+      </c>
+      <c r="F56">
+        <v>1292.83</v>
+      </c>
+      <c r="G56">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Pulmonary Rehabilitation Service</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>750.76</v>
+      </c>
+      <c r="C57">
+        <v>125</v>
+      </c>
+      <c r="D57">
+        <v>90.92</v>
+      </c>
+      <c r="E57">
+        <v>75.08</v>
+      </c>
+      <c r="F57">
+        <v>300.3</v>
+      </c>
+      <c r="G57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>1869.36</v>
+      </c>
+      <c r="C58">
+        <v>374</v>
+      </c>
+      <c r="D58">
+        <v>428.32</v>
+      </c>
+      <c r="E58">
+        <v>93.47</v>
+      </c>
+      <c r="F58">
+        <v>1121.61</v>
+      </c>
+      <c r="G58">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Infectious Diseases Service</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>17343.71</v>
+      </c>
+      <c r="C59">
+        <v>667</v>
+      </c>
+      <c r="D59">
+        <v>629</v>
+      </c>
+      <c r="E59">
+        <v>299.03</v>
+      </c>
+      <c r="F59">
+        <v>2392.24</v>
+      </c>
+      <c r="G59">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Tropical Medicine Service</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>811.04</v>
+      </c>
+      <c r="C60">
+        <v>270</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>270.35</v>
+      </c>
+      <c r="F60">
+        <v>270.35</v>
+      </c>
+      <c r="G60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Genitourinary Medicine Service</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>2330.95</v>
+      </c>
+      <c r="C61">
+        <v>388</v>
+      </c>
+      <c r="D61">
+        <v>247.73</v>
+      </c>
+      <c r="E61">
+        <v>211.9</v>
+      </c>
+      <c r="F61">
+        <v>847.62</v>
+      </c>
+      <c r="G61">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Renal Medicine Service</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>209139.02</v>
+      </c>
+      <c r="C62">
+        <v>807</v>
+      </c>
+      <c r="D62">
+        <v>902.45</v>
+      </c>
+      <c r="E62">
+        <v>218.08</v>
+      </c>
+      <c r="F62">
+        <v>5888.17</v>
+      </c>
+      <c r="G62">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Medical Oncology Service</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>54519.22</v>
+      </c>
+      <c r="C63">
+        <v>747</v>
+      </c>
+      <c r="D63">
+        <v>1264.86</v>
+      </c>
+      <c r="E63">
+        <v>182.95</v>
+      </c>
+      <c r="F63">
+        <v>8964.57</v>
+      </c>
+      <c r="G63">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Nuclear Medicine Service</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>9033.6</v>
+      </c>
+      <c r="C64">
+        <v>301</v>
+      </c>
+      <c r="D64">
+        <v>240.48</v>
+      </c>
+      <c r="E64">
+        <v>164.25</v>
+      </c>
+      <c r="F64">
+        <v>1313.98</v>
+      </c>
+      <c r="G64">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Neurology Service</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>393597.39</v>
+      </c>
+      <c r="C65">
+        <v>517</v>
+      </c>
+      <c r="D65">
+        <v>529.3099999999999</v>
+      </c>
+      <c r="E65">
+        <v>231.53</v>
+      </c>
+      <c r="F65">
+        <v>6019.72</v>
+      </c>
+      <c r="G65">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Clinical Neurophysiology Service</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>96951.96000000001</v>
+      </c>
+      <c r="C66">
+        <v>439</v>
+      </c>
+      <c r="D66">
+        <v>193.14</v>
+      </c>
+      <c r="E66">
+        <v>380.2</v>
+      </c>
+      <c r="F66">
+        <v>1901.02</v>
+      </c>
+      <c r="G66">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Rheumatology Service</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>995267.64</v>
+      </c>
+      <c r="C67">
+        <v>454</v>
+      </c>
+      <c r="D67">
+        <v>545.97</v>
+      </c>
+      <c r="E67">
+        <v>190.08</v>
+      </c>
+      <c r="F67">
+        <v>11024.74</v>
+      </c>
+      <c r="G67">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Paediatric Service</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>627.46</v>
+      </c>
+      <c r="C68">
+        <v>314</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>313.73</v>
+      </c>
+      <c r="F68">
+        <v>313.73</v>
+      </c>
+      <c r="G68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Elderly Medicine Service</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>1155383.12</v>
+      </c>
+      <c r="C69">
+        <v>859</v>
+      </c>
+      <c r="D69">
+        <v>1529.23</v>
+      </c>
+      <c r="E69">
+        <v>360.16</v>
+      </c>
+      <c r="F69">
+        <v>33134.43</v>
+      </c>
+      <c r="G69">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Dental Medicine Service</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>26904.46</v>
+      </c>
+      <c r="C70">
+        <v>464</v>
+      </c>
+      <c r="D70">
+        <v>440.83</v>
+      </c>
+      <c r="E70">
+        <v>206.96</v>
+      </c>
+      <c r="F70">
+        <v>2690.45</v>
+      </c>
+      <c r="G70">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Obstetrics Service</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>774.02</v>
+      </c>
+      <c r="C71">
+        <v>194</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>193.51</v>
+      </c>
+      <c r="F71">
+        <v>193.51</v>
+      </c>
+      <c r="G71">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Gynaecology Service</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>412862.62</v>
+      </c>
+      <c r="C72">
+        <v>457</v>
+      </c>
+      <c r="D72">
+        <v>372.41</v>
+      </c>
+      <c r="E72">
+        <v>204.79</v>
+      </c>
+      <c r="F72">
+        <v>4505.45</v>
+      </c>
+      <c r="G72">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Gynaecological Oncology Service</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>37050.31</v>
+      </c>
+      <c r="C73">
+        <v>322</v>
+      </c>
+      <c r="D73">
+        <v>308.33</v>
+      </c>
+      <c r="E73">
+        <v>186.18</v>
+      </c>
+      <c r="F73">
+        <v>2606.55</v>
+      </c>
+      <c r="G73">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Physiotherapy Service</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>2891056.79</v>
+      </c>
+      <c r="C74">
+        <v>540</v>
+      </c>
+      <c r="D74">
+        <v>556.35</v>
+      </c>
+      <c r="E74">
+        <v>109.16</v>
+      </c>
+      <c r="F74">
+        <v>11898.25</v>
+      </c>
+      <c r="G74">
+        <v>5351</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Occupational Therapy Service</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>385444.31</v>
+      </c>
+      <c r="C75">
+        <v>626</v>
+      </c>
+      <c r="D75">
+        <v>956.04</v>
+      </c>
+      <c r="E75">
+        <v>140.31</v>
+      </c>
+      <c r="F75">
+        <v>11786.43</v>
+      </c>
+      <c r="G75">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Speech and Language Therapy Service</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>50913.4</v>
+      </c>
+      <c r="C76">
+        <v>585</v>
+      </c>
+      <c r="D76">
+        <v>644.35</v>
+      </c>
+      <c r="E76">
+        <v>241.3</v>
+      </c>
+      <c r="F76">
+        <v>4825.91</v>
+      </c>
+      <c r="G76">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Podiatry Service</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>149527.09</v>
+      </c>
+      <c r="C77">
+        <v>402</v>
+      </c>
+      <c r="D77">
+        <v>450.31</v>
+      </c>
+      <c r="E77">
+        <v>99.09</v>
+      </c>
+      <c r="F77">
+        <v>3170.89</v>
+      </c>
+      <c r="G77">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Dietetics Service</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>93077.5</v>
+      </c>
+      <c r="C78">
+        <v>406</v>
+      </c>
+      <c r="D78">
+        <v>522.2</v>
+      </c>
+      <c r="E78">
+        <v>149.64</v>
+      </c>
+      <c r="F78">
+        <v>5686.41</v>
+      </c>
+      <c r="G78">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Orthoptics Service</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>35717.58</v>
+      </c>
+      <c r="C79">
+        <v>201</v>
+      </c>
+      <c r="D79">
+        <v>142.62</v>
+      </c>
+      <c r="E79">
+        <v>108.9</v>
+      </c>
+      <c r="F79">
+        <v>871.16</v>
+      </c>
+      <c r="G79">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Clinical Psychology Service</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>276360.3</v>
+      </c>
+      <c r="C80">
+        <v>531</v>
+      </c>
+      <c r="D80">
+        <v>657.23</v>
+      </c>
+      <c r="E80">
+        <v>327.05</v>
+      </c>
+      <c r="F80">
+        <v>12428.04</v>
+      </c>
+      <c r="G80">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Prosthetics Service</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>644.63</v>
+      </c>
+      <c r="C81">
+        <v>161</v>
+      </c>
+      <c r="D81">
+        <v>62.03</v>
+      </c>
+      <c r="E81">
+        <v>107.44</v>
+      </c>
+      <c r="F81">
+        <v>214.88</v>
+      </c>
+      <c r="G81">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Orthotics Service</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>88005.89</v>
+      </c>
+      <c r="C82">
+        <v>349</v>
+      </c>
+      <c r="D82">
+        <v>273.51</v>
+      </c>
+      <c r="E82">
+        <v>182.96</v>
+      </c>
+      <c r="F82">
+        <v>2195.57</v>
+      </c>
+      <c r="G82">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Optometry Service</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>7548.23</v>
+      </c>
+      <c r="C83">
+        <v>204</v>
+      </c>
+      <c r="D83">
+        <v>125.87</v>
+      </c>
+      <c r="E83">
+        <v>139.78</v>
+      </c>
+      <c r="F83">
+        <v>559.13</v>
+      </c>
+      <c r="G83">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Podiatric Surgery Service</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>6885.15</v>
+      </c>
+      <c r="C84">
+        <v>459</v>
+      </c>
+      <c r="D84">
+        <v>371.56</v>
+      </c>
+      <c r="E84">
+        <v>156.48</v>
+      </c>
+      <c r="F84">
+        <v>1408.33</v>
+      </c>
+      <c r="G84">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Learning Disability Service</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>4301.37</v>
+      </c>
+      <c r="C85">
+        <v>105</v>
+      </c>
+      <c r="D85">
+        <v>180.72</v>
+      </c>
+      <c r="E85">
+        <v>12.88</v>
+      </c>
+      <c r="F85">
+        <v>888.61</v>
+      </c>
+      <c r="G85">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Child and Adolescent Psychiatry Service</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>1082.16</v>
+      </c>
+      <c r="C86">
+        <v>1082</v>
+      </c>
+      <c r="E86">
+        <v>1082.16</v>
+      </c>
+      <c r="F86">
+        <v>1082.16</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Medical Psychotherapy Service</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>5037.57</v>
+      </c>
+      <c r="C87">
+        <v>1679</v>
+      </c>
+      <c r="D87">
+        <v>1454.22</v>
+      </c>
+      <c r="E87">
+        <v>839.59</v>
+      </c>
+      <c r="F87">
+        <v>3358.38</v>
+      </c>
+      <c r="G87">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Old Age Psychiatry Service</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>495031.22</v>
+      </c>
+      <c r="C88">
+        <v>1067</v>
+      </c>
+      <c r="D88">
+        <v>1924.65</v>
+      </c>
+      <c r="E88">
+        <v>348.12</v>
+      </c>
+      <c r="F88">
+        <v>22279.89</v>
+      </c>
+      <c r="G88">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Liaison Psychiatry Service</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>417930.51</v>
+      </c>
+      <c r="C89">
+        <v>1900</v>
+      </c>
+      <c r="D89">
+        <v>4200.87</v>
+      </c>
+      <c r="E89">
+        <v>373.82</v>
+      </c>
+      <c r="F89">
+        <v>42241.63</v>
+      </c>
+      <c r="G89">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Clinical Oncology Service</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>86292.23</v>
+      </c>
+      <c r="C90">
+        <v>649</v>
+      </c>
+      <c r="D90">
+        <v>973.4299999999999</v>
+      </c>
+      <c r="E90">
+        <v>147.26</v>
+      </c>
+      <c r="F90">
+        <v>5743</v>
+      </c>
+      <c r="G90">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Interventional Radiology Service</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>42505.33</v>
+      </c>
+      <c r="C91">
+        <v>169</v>
+      </c>
+      <c r="D91">
+        <v>79</v>
+      </c>
+      <c r="E91">
+        <v>139.82</v>
+      </c>
+      <c r="F91">
+        <v>559.28</v>
+      </c>
+      <c r="G91">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Diagnostic Imaging Service</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>320865.39</v>
+      </c>
+      <c r="C92">
+        <v>109</v>
+      </c>
+      <c r="D92">
+        <v>102.22</v>
+      </c>
+      <c r="E92">
+        <v>56.31</v>
+      </c>
+      <c r="F92">
+        <v>2308.79</v>
+      </c>
+      <c r="G92">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Chemical Pathology Service</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>12605.24</v>
+      </c>
+      <c r="C93">
+        <v>341</v>
+      </c>
+      <c r="D93">
+        <v>227.19</v>
+      </c>
+      <c r="E93">
+        <v>124.8</v>
+      </c>
+      <c r="F93">
+        <v>873.63</v>
+      </c>
+      <c r="G93">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>Audiology Service</t>
         </is>
       </c>
-      <c r="B53">
-        <v>227761.62</v>
-      </c>
-      <c r="C53">
-        <v>289</v>
-      </c>
-      <c r="D53">
-        <v>216.91</v>
-      </c>
-      <c r="E53">
+      <c r="B94">
+        <v>293924.98</v>
+      </c>
+      <c r="C94">
+        <v>292</v>
+      </c>
+      <c r="D94">
+        <v>213.4</v>
+      </c>
+      <c r="E94">
         <v>120.96</v>
       </c>
-      <c r="F53">
+      <c r="F94">
         <v>2540.09</v>
       </c>
-      <c r="G53">
-        <v>787</v>
+      <c r="G94">
+        <v>1006</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_costs_by_tretspef-Users_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_costs_by_tretspef-Users_OMOP.xlsx
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B9">
-        <v>9047683.6</v>
+        <v>9040523.52</v>
       </c>
       <c r="C9">
         <v>544</v>
       </c>
       <c r="D9">
-        <v>418.54</v>
+        <v>418.28</v>
       </c>
       <c r="E9">
         <v>166.51</v>
@@ -588,7 +588,7 @@
         <v>16984.39</v>
       </c>
       <c r="G9">
-        <v>16624</v>
+        <v>16620</v>
       </c>
     </row>
     <row r="10">
